--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5621" uniqueCount="2586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5623" uniqueCount="2588">
   <si>
     <t>__meta = {</t>
   </si>
@@ -6331,13 +6331,19 @@
     <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=7674,nFrame=-1,nTime="2700,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;4500,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=7676,nFrame=-1,nTime="1800,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-1,key="破阵点将·{$3}·常驻",},</t>
+    <t>{nClass=14,nIcon=7674,nFrame=-1,nTime="2700,{$5}{$4}{$6}·{$8}{$7}{$9};4500,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=7676,nFrame=-1,nTime="1800,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},</t>
   </si>
   <si>
     <t>五分钟内只可拾取一次对立阵营首领仓皇撤退留下的物资。</t>
@@ -9171,7 +9177,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1788763055000,</v>
+        <v>nTimeStamp = 1788766659000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -10914,10 +10920,10 @@
         <v>1774</v>
       </c>
       <c r="B3" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="C3" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -10925,10 +10931,10 @@
         <v>1778</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="C4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -10936,10 +10942,10 @@
         <v>1785</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10947,10 +10953,10 @@
         <v>1789</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10958,10 +10964,10 @@
         <v>1793</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -10969,10 +10975,10 @@
         <v>1797</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -10980,10 +10986,10 @@
         <v>1806</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -10991,10 +10997,10 @@
         <v>1810</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11002,10 +11008,10 @@
         <v>1814</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11013,10 +11019,10 @@
         <v>1818</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11024,10 +11030,10 @@
         <v>1822</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11035,10 +11041,10 @@
         <v>1826</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11046,10 +11052,10 @@
         <v>1832</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11057,10 +11063,10 @@
         <v>1836</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11068,10 +11074,10 @@
         <v>1840</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11079,10 +11085,10 @@
         <v>1844</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11090,10 +11096,10 @@
         <v>1850</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11101,10 +11107,10 @@
         <v>1854</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11112,10 +11118,10 @@
         <v>1858</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11123,10 +11129,10 @@
         <v>1862</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11134,10 +11140,10 @@
         <v>1866</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11145,10 +11151,10 @@
         <v>1870</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11156,10 +11162,10 @@
         <v>1878</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11167,10 +11173,10 @@
         <v>1882</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11178,10 +11184,10 @@
         <v>1886</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11189,10 +11195,10 @@
         <v>1890</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11200,10 +11206,10 @@
         <v>1900</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11211,10 +11217,10 @@
         <v>1904</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
     </row>
   </sheetData>
@@ -31939,7 +31945,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE175"/>
+  <dimension ref="A1:AG175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="4" max="4" width="52.125" customWidth="1"/>
@@ -33539,7 +33545,7 @@
       <c r="AA32" s="7"/>
       <c r="AB32" s="7"/>
     </row>
-    <row r="33" customFormat="1" spans="2:31">
+    <row r="33" customFormat="1" spans="2:33">
       <c r="B33" s="7"/>
       <c r="C33" s="4" t="str">
         <f t="shared" si="3"/>
@@ -33608,7 +33614,7 @@
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
     </row>
-    <row r="34" customFormat="1" spans="2:31">
+    <row r="34" customFormat="1" spans="2:33">
       <c r="B34" s="7"/>
       <c r="C34" s="4" t="str">
         <f t="shared" si="3"/>
@@ -33677,7 +33683,7 @@
       <c r="AA34" s="7"/>
       <c r="AB34" s="7"/>
     </row>
-    <row r="35" customFormat="1" spans="2:31">
+    <row r="35" customFormat="1" spans="2:33">
       <c r="B35" s="7"/>
       <c r="C35" s="4" t="str">
         <f t="shared" si="3"/>
@@ -33746,7 +33752,7 @@
       <c r="AA35" s="7"/>
       <c r="AB35" s="7"/>
     </row>
-    <row r="36" customFormat="1" spans="2:31">
+    <row r="36" customFormat="1" spans="2:33">
       <c r="B36" s="7"/>
       <c r="C36" s="4" t="str">
         <f t="shared" si="3"/>
@@ -33815,7 +33821,7 @@
       <c r="AA36" s="7"/>
       <c r="AB36" s="7"/>
     </row>
-    <row r="37" customFormat="1" spans="2:31">
+    <row r="37" customFormat="1" spans="2:33">
       <c r="C37" t="s">
         <v>1974</v>
       </c>
@@ -33847,7 +33853,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="2:31">
+    <row r="38" customFormat="1" spans="2:33">
       <c r="C38" t="s">
         <v>1974</v>
       </c>
@@ -33876,7 +33882,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="2:31">
+    <row r="39" customFormat="1" spans="2:33">
       <c r="C39" t="s">
         <v>1974</v>
       </c>
@@ -33920,7 +33926,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="2:31">
+    <row r="40" customFormat="1" spans="2:33">
       <c r="C40" t="s">
         <v>1974</v>
       </c>
@@ -33952,7 +33958,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="41" customFormat="1" spans="2:31">
+    <row r="41" customFormat="1" spans="2:33">
       <c r="C41" t="s">
         <v>1974</v>
       </c>
@@ -33983,7 +33989,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="2:31">
+    <row r="42" customFormat="1" spans="2:33">
       <c r="C42" t="s">
         <v>1974</v>
       </c>
@@ -34014,7 +34020,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="43" customFormat="1" spans="2:31">
+    <row r="43" customFormat="1" spans="2:33">
       <c r="C43" t="s">
         <v>1974</v>
       </c>
@@ -34044,7 +34050,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="2:31">
+    <row r="44" customFormat="1" spans="2:33">
       <c r="C44" t="s">
         <v>1974</v>
       </c>
@@ -34068,7 +34074,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="2:31">
+    <row r="45" customFormat="1" spans="2:33">
       <c r="C45" t="s">
         <v>1974</v>
       </c>
@@ -34089,7 +34095,7 @@
         <v>{szContent="本周累计从奇袭场奖励堆获得战阶：20000/20000",szTarget="%",szNote="奇袭场·奖励堆·战阶已上限",col={255,255,100,},[14]={bCenterAlarm=true,},},</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="2:31">
+    <row r="46" customFormat="1" spans="2:33">
       <c r="C46" t="s">
         <v>1974</v>
       </c>
@@ -34113,7 +34119,7 @@
         <v>{szContent="^本周累计从(.-)奖励堆获得战阶：(%d-)/(%d+)",szTarget="%",szNote="{$1}·累计奖励堆·[{$2}/{$3}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},},</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="2:31">
+    <row r="47" customFormat="1" spans="2:33">
       <c r="C47" t="s">
         <v>1974</v>
       </c>
@@ -34134,7 +34140,7 @@
       </c>
       <c r="V47" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},{nClass=14,nIcon=7674,nFrame=-1,nTime="2700,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;4500,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二·常驻",},{nClass=14,nIcon=7676,nFrame=-1,nTime="1800,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一·常驻",},{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-1,key="破阵点将·{$3}·常驻",},},},</v>
+        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},{nClass=14,nIcon=7674,nFrame=-1,nTime="2700,{$5}{$4}{$6}·{$8}{$7}{$9};4500,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},{nClass=14,nIcon=7676,nFrame=-1,nTime="1800,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},},},</v>
       </c>
       <c r="W47" t="s">
         <v>2084</v>
@@ -34163,13 +34169,19 @@
       <c r="AE47" t="s">
         <v>2092</v>
       </c>
-    </row>
-    <row r="48" customFormat="1" spans="2:31">
+      <c r="AF47" t="s">
+        <v>2093</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="2:33">
       <c r="D48" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="E48" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="M48" t="s">
         <v>1985</v>
@@ -34179,15 +34191,15 @@
         <v>{szContent="五分钟内只可拾取一次对立阵营首领仓皇撤退留下的物资。",szNote="主场·助战首领堆·拾取间隔",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,szName="首领拾取间隔",nTime=-2,key="首领拾取间隔",},},},</v>
       </c>
       <c r="W48" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="49" spans="1:27">
       <c r="D49" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="E49" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="M49" t="s">
         <v>1985</v>
@@ -34200,15 +34212,15 @@
         <v>{szContent="放置一辆摧城车，本日本阵营还可放置(%d-)辆摧城车。",szNote="放置·摧城车",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=6158,nFrame=1,szName="摧城车·本日剩余·{$1}辆",nTime=10,key="摧城车",},},},</v>
       </c>
       <c r="W49" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="50" spans="1:27">
       <c r="D50" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="E50" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="M50" t="s">
         <v>1985</v>
@@ -34220,92 +34232,92 @@
     </row>
     <row r="51" customFormat="1" spans="1:27">
       <c r="D51" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="E51" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="V51" t="str">
         <f t="shared" si="11"/>
         <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在5分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=300,key="阵营业务",},},},</v>
       </c>
       <c r="W51" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:27">
       <c r="D52" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E52" t="s">
         <v>2104</v>
-      </c>
-      <c r="E52" t="s">
-        <v>2102</v>
       </c>
       <c r="V52" t="str">
         <f t="shared" si="11"/>
         <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在4分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=240,key="阵营业务",},},},</v>
       </c>
       <c r="W52" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:27">
       <c r="D53" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="E53" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="V53" t="str">
         <f t="shared" si="11"/>
         <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在3分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=180,key="阵营业务",},},},</v>
       </c>
       <c r="W53" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:27">
       <c r="D54" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="E54" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="V54" t="str">
         <f t="shared" si="11"/>
         <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在2分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=120,key="阵营业务",},},},</v>
       </c>
       <c r="W54" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:27">
       <c r="D55" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="E55" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="V55" t="str">
         <f t="shared" si="11"/>
         <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在1分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=60,key="阵营业务",},},},</v>
       </c>
       <c r="W55" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:27">
       <c r="D56" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="E56" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="V56" t="str">
         <f t="shared" si="11"/>
         <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将传出场景",szNote="中立侠士·传出场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出场景",nTime=5,key="阵营业务",},},},</v>
       </c>
       <c r="W56" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="57" spans="1:27">
@@ -34325,10 +34337,10 @@
         <v>1974</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="E58" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="F58"/>
       <c r="G58"/>
@@ -34346,7 +34358,7 @@
         <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·内城物资·已刷新",nTime="10,浩气盟·内城物资·已刷新;300,浩气盟·内城物资·拾取剩余;305,浩气盟·内城物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
       </c>
       <c r="W58" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="X58"/>
       <c r="Y58"/>
@@ -34358,10 +34370,10 @@
         <v>1974</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="E59" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="F59"/>
       <c r="G59"/>
@@ -34379,7 +34391,7 @@
         <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·营地物资·已刷新",nTime="10,恶人谷·营地物资·已刷新;300,恶人谷·营地物资·拾取剩余;305,恶人谷·营地物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
       </c>
       <c r="W59" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="X59"/>
       <c r="Y59"/>
@@ -34391,10 +34403,10 @@
         <v>1974</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="E60" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="F60"/>
       <c r="G60"/>
@@ -34412,10 +34424,10 @@
         <v>{szContent="军情速递！浩气盟物资官传来消息，现有一批新物资运至各复活点，望浩气侠士们前来领取，以便增强战斗实力。",szTarget="%",szNote="复活点·物资箱·已刷新",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,szName="进攻方·速战速决·未达成",nTime=10,nRefresh=99999,key="速战速决",},{nClass=14,nIcon=3557,nFrame=6,szName="复活点·物资箱·已经刷新",nTime=10.1,nRefresh=5,key="复活点·物资箱",},},},</v>
       </c>
       <c r="W60" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="X60" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="Y60"/>
       <c r="Z60"/>
@@ -34426,7 +34438,7 @@
         <v>1995</v>
       </c>
       <c r="D61" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="E61" t="str">
         <f t="shared" ref="E61:E76" si="12">K61&amp;"·"&amp;L61&amp;"·"&amp;H61&amp;"·"&amp;"败退"</f>
@@ -34439,19 +34451,19 @@
         <v>1998</v>
       </c>
       <c r="H61" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="I61" t="s">
         <v>1999</v>
       </c>
       <c r="J61" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K61" t="s">
         <v>2001</v>
       </c>
       <c r="L61" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="M61" t="s">
         <v>1981</v>
@@ -34490,7 +34502,7 @@
         <v>1995</v>
       </c>
       <c r="D62" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="E62" t="str">
         <f t="shared" si="12"/>
@@ -34503,19 +34515,19 @@
         <v>1998</v>
       </c>
       <c r="H62" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="I62" t="s">
         <v>1999</v>
       </c>
       <c r="J62" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K62" t="s">
         <v>2001</v>
       </c>
       <c r="L62" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="M62" t="s">
         <v>1981</v>
@@ -34554,7 +34566,7 @@
         <v>1995</v>
       </c>
       <c r="D63" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="E63" t="str">
         <f t="shared" si="12"/>
@@ -34567,19 +34579,19 @@
         <v>1998</v>
       </c>
       <c r="H63" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="I63" t="s">
         <v>1999</v>
       </c>
       <c r="J63" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="K63" t="s">
         <v>2001</v>
       </c>
       <c r="L63" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="M63" t="s">
         <v>1981</v>
@@ -34618,7 +34630,7 @@
         <v>1995</v>
       </c>
       <c r="D64" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="12"/>
@@ -34631,19 +34643,19 @@
         <v>1998</v>
       </c>
       <c r="H64" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="I64" t="s">
         <v>2001</v>
       </c>
       <c r="J64" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="K64" t="s">
         <v>2001</v>
       </c>
       <c r="L64" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="M64" t="s">
         <v>1981</v>
@@ -34682,7 +34694,7 @@
         <v>1998</v>
       </c>
       <c r="D65" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="E65" t="str">
         <f t="shared" si="12"/>
@@ -34695,19 +34707,19 @@
         <v>1995</v>
       </c>
       <c r="H65" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="I65" t="s">
         <v>2001</v>
       </c>
       <c r="J65" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="K65" t="s">
         <v>1999</v>
       </c>
       <c r="L65" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="M65" t="s">
         <v>1977</v>
@@ -34746,7 +34758,7 @@
         <v>1998</v>
       </c>
       <c r="D66" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="E66" t="str">
         <f t="shared" si="12"/>
@@ -34759,19 +34771,19 @@
         <v>1995</v>
       </c>
       <c r="H66" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="I66" t="s">
         <v>2001</v>
       </c>
       <c r="J66" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K66" t="s">
         <v>1999</v>
       </c>
       <c r="L66" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="M66" t="s">
         <v>1977</v>
@@ -34809,7 +34821,7 @@
         <v>1998</v>
       </c>
       <c r="D67" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="E67" t="str">
         <f t="shared" si="12"/>
@@ -34822,19 +34834,19 @@
         <v>1995</v>
       </c>
       <c r="H67" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="I67" t="s">
         <v>2001</v>
       </c>
       <c r="J67" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K67" t="s">
         <v>1999</v>
       </c>
       <c r="L67" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="M67" t="s">
         <v>1977</v>
@@ -34872,7 +34884,7 @@
         <v>1998</v>
       </c>
       <c r="D68" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="E68" t="str">
         <f t="shared" si="12"/>
@@ -34885,19 +34897,19 @@
         <v>1995</v>
       </c>
       <c r="H68" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="I68" t="s">
         <v>2001</v>
       </c>
       <c r="J68" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K68" t="s">
         <v>1999</v>
       </c>
       <c r="L68" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="M68" t="s">
         <v>1977</v>
@@ -34932,7 +34944,7 @@
     </row>
     <row r="69" spans="1:27">
       <c r="C69" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="D69" t="s">
         <v>2031</v>
@@ -34948,19 +34960,19 @@
         <v>1998</v>
       </c>
       <c r="H69" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="I69" t="s">
         <v>1999</v>
       </c>
       <c r="J69" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K69" t="s">
         <v>2001</v>
       </c>
       <c r="L69" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="M69" t="s">
         <v>1981</v>
@@ -34994,7 +35006,7 @@
     </row>
     <row r="70" spans="1:27">
       <c r="C70" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="D70" t="s">
         <v>2031</v>
@@ -35010,19 +35022,19 @@
         <v>1998</v>
       </c>
       <c r="H70" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="I70" t="s">
         <v>1999</v>
       </c>
       <c r="J70" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K70" t="s">
         <v>2001</v>
       </c>
       <c r="L70" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="M70" t="s">
         <v>1981</v>
@@ -35056,7 +35068,7 @@
     </row>
     <row r="71" spans="1:27">
       <c r="C71" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="D71" t="s">
         <v>2031</v>
@@ -35072,19 +35084,19 @@
         <v>1998</v>
       </c>
       <c r="H71" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="I71" t="s">
         <v>1999</v>
       </c>
       <c r="J71" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="K71" t="s">
         <v>2001</v>
       </c>
       <c r="L71" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="M71" t="s">
         <v>1981</v>
@@ -35118,7 +35130,7 @@
     </row>
     <row r="72" spans="1:27">
       <c r="C72" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="D72" t="s">
         <v>2031</v>
@@ -35134,19 +35146,19 @@
         <v>1998</v>
       </c>
       <c r="H72" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="I72" t="s">
         <v>2001</v>
       </c>
       <c r="J72" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="K72" t="s">
         <v>2001</v>
       </c>
       <c r="L72" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="M72" t="s">
         <v>1981</v>
@@ -35180,7 +35192,7 @@
     </row>
     <row r="73" spans="1:27">
       <c r="C73" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="D73" t="s">
         <v>2031</v>
@@ -35196,19 +35208,19 @@
         <v>1995</v>
       </c>
       <c r="H73" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="I73" t="s">
         <v>2001</v>
       </c>
       <c r="J73" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="K73" t="s">
         <v>1999</v>
       </c>
       <c r="L73" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="M73" t="s">
         <v>1977</v>
@@ -35242,7 +35254,7 @@
     </row>
     <row r="74" customFormat="1" spans="1:27">
       <c r="C74" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D74" t="s">
         <v>2031</v>
@@ -35258,19 +35270,19 @@
         <v>1995</v>
       </c>
       <c r="H74" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="I74" t="s">
         <v>2001</v>
       </c>
       <c r="J74" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K74" t="s">
         <v>1999</v>
       </c>
       <c r="L74" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="M74" t="s">
         <v>1977</v>
@@ -35304,7 +35316,7 @@
     </row>
     <row r="75" customFormat="1" spans="1:27">
       <c r="C75" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D75" t="s">
         <v>2031</v>
@@ -35320,19 +35332,19 @@
         <v>1995</v>
       </c>
       <c r="H75" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="I75" t="s">
         <v>2001</v>
       </c>
       <c r="J75" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K75" t="s">
         <v>1999</v>
       </c>
       <c r="L75" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="M75" t="s">
         <v>1977</v>
@@ -35366,7 +35378,7 @@
     </row>
     <row r="76" customFormat="1" spans="1:27">
       <c r="C76" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D76" t="s">
         <v>2031</v>
@@ -35382,19 +35394,19 @@
         <v>1995</v>
       </c>
       <c r="H76" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="I76" t="s">
         <v>2001</v>
       </c>
       <c r="J76" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K76" t="s">
         <v>1999</v>
       </c>
       <c r="L76" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="M76" t="s">
         <v>1977</v>
@@ -35443,10 +35455,10 @@
         <v>1974</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="E78" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="F78"/>
       <c r="G78"/>
@@ -35464,7 +35476,7 @@
         <v>{szContent="军情速递！浩气盟物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="浩气盟·物资车·已运达",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=10449,nFrame=4,szName="浩气盟·营地物资·已刷新",nTime="10,浩气盟·营地物资·刷新;300,浩气盟·营地物资·拾取剩余;305,浩气盟·营地物资·已消失",nRefresh=0,key="浩气·物资车·运达",},},},</v>
       </c>
       <c r="W78" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="X78"/>
       <c r="Y78"/>
@@ -35476,10 +35488,10 @@
         <v>1974</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="E79" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="F79"/>
       <c r="G79"/>
@@ -35497,7 +35509,7 @@
         <v>{szContent="军情速递！恶人谷物资车已运达，车内装有大量物资，望侠士们前来拾取，切莫错过。",szTarget="%",szNote="恶人谷·物资车·已运达",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=10450,nFrame=4,szName="恶人谷·内城物资·已刷新",nTime="10,恶人谷·内城物资·刷新;300,恶人谷·内城物资·拾取剩余;305,恶人谷·内城物资·已消失",nRefresh=0,key="恶人·物资车·运达",},},},</v>
       </c>
       <c r="W79" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="X79"/>
       <c r="Y79"/>
@@ -35509,10 +35521,10 @@
         <v>1974</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="E80" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="F80"/>
       <c r="G80"/>
@@ -35530,10 +35542,10 @@
         <v>{szContent="军情速递！恶人谷物资官传来消息，现有一批新物资运至各复活点，望恶人侠士们前来领取，以便增强战斗实力。",szTarget="%",szNote="复活点·物资箱·已刷新",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=0,szName="进攻方·速战速决·未达成",nTime=10,nRefresh=99999,key="速战速决",},{nClass=14,nIcon=3557,nFrame=6,szName="复活点·物资箱·已经刷新",nTime=10.1,nRefresh=5,key="复活点·物资箱",},},},</v>
       </c>
       <c r="W80" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="X80" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="Y80"/>
       <c r="Z80"/>
@@ -35544,7 +35556,7 @@
         <v>1995</v>
       </c>
       <c r="D81" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" ref="E81:E96" si="16">K81&amp;"·"&amp;L81&amp;"·"&amp;H81&amp;"·"&amp;"败退"</f>
@@ -35557,19 +35569,19 @@
         <v>1998</v>
       </c>
       <c r="H81" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="I81" t="s">
         <v>1999</v>
       </c>
       <c r="J81" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K81" t="s">
         <v>2001</v>
       </c>
       <c r="L81" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="M81" t="s">
         <v>1981</v>
@@ -35608,7 +35620,7 @@
         <v>1995</v>
       </c>
       <c r="D82" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="E82" t="str">
         <f t="shared" si="16"/>
@@ -35621,19 +35633,19 @@
         <v>1998</v>
       </c>
       <c r="H82" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="I82" t="s">
         <v>1999</v>
       </c>
       <c r="J82" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K82" t="s">
         <v>2001</v>
       </c>
       <c r="L82" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="M82" t="s">
         <v>1981</v>
@@ -35672,7 +35684,7 @@
         <v>1995</v>
       </c>
       <c r="D83" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="E83" t="str">
         <f t="shared" si="16"/>
@@ -35685,19 +35697,19 @@
         <v>1998</v>
       </c>
       <c r="H83" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="I83" t="s">
         <v>1999</v>
       </c>
       <c r="J83" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="K83" t="s">
         <v>2001</v>
       </c>
       <c r="L83" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="M83" t="s">
         <v>1981</v>
@@ -35736,7 +35748,7 @@
         <v>1995</v>
       </c>
       <c r="D84" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="E84" t="str">
         <f t="shared" si="16"/>
@@ -35749,19 +35761,19 @@
         <v>1998</v>
       </c>
       <c r="H84" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="I84" t="s">
         <v>1999</v>
       </c>
       <c r="J84" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="K84" t="s">
         <v>2001</v>
       </c>
       <c r="L84" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="M84" t="s">
         <v>1981</v>
@@ -35800,7 +35812,7 @@
         <v>1998</v>
       </c>
       <c r="D85" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="16"/>
@@ -35813,19 +35825,19 @@
         <v>1995</v>
       </c>
       <c r="H85" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="I85" t="s">
         <v>2001</v>
       </c>
       <c r="J85" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="K85" t="s">
         <v>1999</v>
       </c>
       <c r="L85" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="M85" t="s">
         <v>1977</v>
@@ -35864,7 +35876,7 @@
         <v>1998</v>
       </c>
       <c r="D86" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="16"/>
@@ -35877,19 +35889,19 @@
         <v>1995</v>
       </c>
       <c r="H86" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="I86" t="s">
         <v>2001</v>
       </c>
       <c r="J86" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K86" t="s">
         <v>1999</v>
       </c>
       <c r="L86" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="M86" t="s">
         <v>1977</v>
@@ -35927,7 +35939,7 @@
         <v>1998</v>
       </c>
       <c r="D87" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="16"/>
@@ -35940,19 +35952,19 @@
         <v>1995</v>
       </c>
       <c r="H87" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="I87" t="s">
         <v>2001</v>
       </c>
       <c r="J87" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K87" t="s">
         <v>1999</v>
       </c>
       <c r="L87" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="M87" t="s">
         <v>1977</v>
@@ -35990,7 +36002,7 @@
         <v>1998</v>
       </c>
       <c r="D88" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="E88" t="str">
         <f t="shared" si="16"/>
@@ -36003,19 +36015,19 @@
         <v>1995</v>
       </c>
       <c r="H88" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="I88" t="s">
         <v>2001</v>
       </c>
       <c r="J88" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K88" t="s">
         <v>1999</v>
       </c>
       <c r="L88" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="M88" t="s">
         <v>1977</v>
@@ -36050,7 +36062,7 @@
     </row>
     <row r="89" spans="3:27">
       <c r="C89" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="D89" t="s">
         <v>2031</v>
@@ -36066,19 +36078,19 @@
         <v>1998</v>
       </c>
       <c r="H89" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="I89" t="s">
         <v>1999</v>
       </c>
       <c r="J89" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K89" t="s">
         <v>2001</v>
       </c>
       <c r="L89" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="M89" t="s">
         <v>1981</v>
@@ -36112,7 +36124,7 @@
     </row>
     <row r="90" spans="3:27">
       <c r="C90" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="D90" t="s">
         <v>2031</v>
@@ -36128,19 +36140,19 @@
         <v>1998</v>
       </c>
       <c r="H90" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="I90" t="s">
         <v>1999</v>
       </c>
       <c r="J90" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K90" t="s">
         <v>2001</v>
       </c>
       <c r="L90" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="M90" t="s">
         <v>1981</v>
@@ -36174,7 +36186,7 @@
     </row>
     <row r="91" spans="3:27">
       <c r="C91" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="D91" t="s">
         <v>2031</v>
@@ -36190,19 +36202,19 @@
         <v>1998</v>
       </c>
       <c r="H91" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="I91" t="s">
         <v>1999</v>
       </c>
       <c r="J91" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="K91" t="s">
         <v>2001</v>
       </c>
       <c r="L91" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="M91" t="s">
         <v>1981</v>
@@ -36236,7 +36248,7 @@
     </row>
     <row r="92" spans="3:27">
       <c r="C92" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="D92" t="s">
         <v>2031</v>
@@ -36252,19 +36264,19 @@
         <v>1998</v>
       </c>
       <c r="H92" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="I92" t="s">
         <v>1999</v>
       </c>
       <c r="J92" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="K92" t="s">
         <v>2001</v>
       </c>
       <c r="L92" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="M92" t="s">
         <v>1981</v>
@@ -36298,7 +36310,7 @@
     </row>
     <row r="93" spans="3:27">
       <c r="C93" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="D93" t="s">
         <v>2031</v>
@@ -36314,19 +36326,19 @@
         <v>1995</v>
       </c>
       <c r="H93" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="I93" t="s">
         <v>2001</v>
       </c>
       <c r="J93" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="K93" t="s">
         <v>1999</v>
       </c>
       <c r="L93" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="M93" t="s">
         <v>1977</v>
@@ -36360,7 +36372,7 @@
     </row>
     <row r="94" customFormat="1" spans="3:27">
       <c r="C94" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D94" t="s">
         <v>2031</v>
@@ -36376,19 +36388,19 @@
         <v>1995</v>
       </c>
       <c r="H94" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="I94" t="s">
         <v>2001</v>
       </c>
       <c r="J94" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K94" t="s">
         <v>1999</v>
       </c>
       <c r="L94" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="M94" t="s">
         <v>1977</v>
@@ -36422,7 +36434,7 @@
     </row>
     <row r="95" customFormat="1" spans="3:27">
       <c r="C95" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D95" t="s">
         <v>2031</v>
@@ -36438,19 +36450,19 @@
         <v>1995</v>
       </c>
       <c r="H95" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="I95" t="s">
         <v>2001</v>
       </c>
       <c r="J95" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K95" t="s">
         <v>1999</v>
       </c>
       <c r="L95" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="M95" t="s">
         <v>1977</v>
@@ -36484,7 +36496,7 @@
     </row>
     <row r="96" customFormat="1" spans="3:27">
       <c r="C96" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D96" t="s">
         <v>2031</v>
@@ -36500,19 +36512,19 @@
         <v>1995</v>
       </c>
       <c r="H96" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="I96" t="s">
         <v>2001</v>
       </c>
       <c r="J96" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K96" t="s">
         <v>1999</v>
       </c>
       <c r="L96" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="M96" t="s">
         <v>1977</v>
@@ -36546,7 +36558,7 @@
     </row>
     <row r="97" customFormat="1" spans="1:27">
       <c r="A97" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B97">
         <v>-21</v>
@@ -36558,7 +36570,7 @@
     </row>
     <row r="98" customFormat="1" spans="1:27">
       <c r="D98" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="M98" t="s">
         <v>1977</v>
@@ -36568,12 +36580,12 @@
         <v>{szContent="分流活动已开启，大侠可以前往龙门荒漠接取阵营攻防前置任务",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=3536,nFrame=3,szName="龙门·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},},},</v>
       </c>
       <c r="W98" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:27">
       <c r="D99" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="M99" t="s">
         <v>1981</v>
@@ -36583,7 +36595,7 @@
         <v>{szContent="分流活动已开启，大侠可以前往巴陵县接取阵营攻防前置任务",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=3536,nFrame=7,szName="巴陵·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},},},</v>
       </c>
       <c r="W99" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:27">
@@ -36600,7 +36612,7 @@
     </row>
     <row r="101" customFormat="1" spans="1:27">
       <c r="D101" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="M101" t="s">
         <v>1977</v>
@@ -36610,12 +36622,12 @@
         <v>{szContent="分流活动已开启，大侠可以前往龙门荒漠接取阵营攻防前置任务",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=3536,nFrame=3,szName="龙门·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},},},</v>
       </c>
       <c r="W101" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:27">
       <c r="D102" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="M102" t="s">
         <v>1981</v>
@@ -36625,7 +36637,7 @@
         <v>{szContent="分流活动已开启，大侠可以前往巴陵县接取阵营攻防前置任务",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=3536,nFrame=7,szName="巴陵·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},},},</v>
       </c>
       <c r="W102" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="103" spans="1:27">
@@ -36642,7 +36654,7 @@
     </row>
     <row r="104" customFormat="1" spans="1:27">
       <c r="D104" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="M104" t="s">
         <v>1977</v>
@@ -36652,12 +36664,12 @@
         <v>{szContent="分流活动已开启，大侠可以前往龙门荒漠接取阵营攻防前置任务",col={255,100,100,},[14]={},tCountdown={{nClass=14,nIcon=3536,nFrame=3,szName="龙门·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},},},</v>
       </c>
       <c r="W104" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:27">
       <c r="D105" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="M105" t="s">
         <v>1981</v>
@@ -36667,7 +36679,7 @@
         <v>{szContent="分流活动已开启，大侠可以前往巴陵县接取阵营攻防前置任务",col={100,100,255,},[14]={},tCountdown={{nClass=14,nIcon=3536,nFrame=7,szName="巴陵·攻防前置分流",nTime=30,nRefresh=1800,key="分流活动",},},},</v>
       </c>
       <c r="W105" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:27">
@@ -36687,23 +36699,23 @@
         <v>1704</v>
       </c>
       <c r="D107" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="E107" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="V107" t="str">
         <f t="shared" si="19"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W107" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="X107" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y107" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:27">
@@ -36711,23 +36723,23 @@
         <v>1704</v>
       </c>
       <c r="D108" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="E108" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="V108" t="str">
         <f t="shared" si="19"/>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W108" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="X108" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y108" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:27">
@@ -36735,17 +36747,17 @@
         <v>1704</v>
       </c>
       <c r="D109" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="E109" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="V109" t="str">
         <f t="shared" si="19"/>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W109" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:27">
@@ -36753,23 +36765,23 @@
         <v>1704</v>
       </c>
       <c r="D110" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="E110" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="V110" t="str">
         <f t="shared" si="19"/>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W110" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="X110" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="Y110" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:27">
@@ -36777,10 +36789,10 @@
         <v>1974</v>
       </c>
       <c r="D111" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="E111" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="S111">
         <v>1</v>
@@ -36790,16 +36802,16 @@
         <v>{szContent="尔等鼠辈！谁敢与我一战！",szTarget="%",szNote="据点攻防·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime="2,据点攻防·正式开始;10,建议关闭·江湖身份",nRefresh=2,key="阵营活动",},{nClass=14,nIcon=13,szName="绣球花",nTime=-1,key="绣球花",},{nClass=14,nIcon=13,szName="郁金香",nTime=-1,key="郁金香",},{nClass=14,nIcon=13,szName="牵牛花",nTime=-1,key="牵牛花",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W111" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="X111" s="5" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="Y111" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Z111" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:27">
@@ -36807,10 +36819,10 @@
         <v>1974</v>
       </c>
       <c r="D112" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="E112" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="M112" t="s">
         <v>1985</v>
@@ -36823,19 +36835,19 @@
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W112" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="X112" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="Y112" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="Z112" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="AA112" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:27">
@@ -36843,7 +36855,7 @@
         <v>1974</v>
       </c>
       <c r="D113" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="E113"/>
       <c r="M113" t="s">
@@ -36858,10 +36870,10 @@
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W113" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="X113" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:27">
@@ -36869,7 +36881,7 @@
         <v>1974</v>
       </c>
       <c r="D114" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="E114"/>
       <c r="M114" t="s">
@@ -36884,10 +36896,10 @@
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W114" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="X114" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:27">
@@ -36895,10 +36907,10 @@
         <v>1974</v>
       </c>
       <c r="D115" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="E115" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="M115" t="s">
         <v>1474</v>
@@ -36915,7 +36927,7 @@
         <v>{szContent="您因消极怠战,扰乱阵营秩序，被阵营督查官请离当前地图，但同时给予250点贡献积分！",szTarget="%",szNote="阵营督查官·请离据点攻防",col={255,50,255,},[14]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,bHold=true,nTime=30,szName="阵营督查·请离据点攻防",key="挂机检测",},},},</v>
       </c>
       <c r="W115" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:27">
@@ -36923,10 +36935,10 @@
         <v>1974</v>
       </c>
       <c r="D116" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="E116" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="M116" t="s">
         <v>1474</v>
@@ -36942,18 +36954,18 @@
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;65,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W116" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="X116" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:27">
       <c r="C117" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="D117" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="E117"/>
       <c r="M117" t="s">
@@ -36967,21 +36979,21 @@
         <v>{szContent="好嘞，老夫开始收货了。本次特产转为(%d-)个(.-)，(.-)[，]-您辛苦了！",szTarget="据点总管",col={255,255,100,},bReg=true,[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=374,nFrame=6,szName="{$2}·{$1}{$3}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
       </c>
       <c r="W117" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="X117" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:27">
       <c r="C118" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="D118" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="E118" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="M118" t="s">
         <v>1714</v>
@@ -37001,10 +37013,10 @@
         <v>{szContent="已为.-补.-%[(.+)%].-(%d-)个.-消耗(%d+%.?%d-)金",szTarget="据点总管",szNote="补货·[{$1}]·{$2}",col={100,255,100,},bReg=true,[14]={bCenterAlarm=true,bScreenHead=true,},tCountdown={{nClass=14,nIcon=13,nFrame=6,szName="阵营模式",nTime=-2,key="阵营模式",},{nClass=14,nIcon=135,nFrame=6,szName="补货·[{$1}]·{$2}",nTime=10,nRefresh=600,key="阵营模式",},},},</v>
       </c>
       <c r="W118" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="X118" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:27">
@@ -37012,10 +37024,10 @@
         <v>1974</v>
       </c>
       <c r="D119" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E119" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="M119" t="s">
         <v>1985</v>
@@ -37032,7 +37044,7 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W119" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:27">
@@ -37040,10 +37052,10 @@
         <v>1974</v>
       </c>
       <c r="D120" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="E120" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="M120" t="s">
         <v>1985</v>
@@ -37060,27 +37072,27 @@
         <v>{szContent="^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！",szTarget="%",szNote="[{$1}]·{$2}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},},},</v>
       </c>
       <c r="W120" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="X120" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="Y120" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="Z120" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="AA120" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:27">
       <c r="D121" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="E121" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="M121" t="s">
         <v>1985</v>
@@ -37096,12 +37108,12 @@
         <v>{szContent="身负据点大旗，当心被夺！",szNote="[{$me}]·扛起大旗",col={255,255,100,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},},},</v>
       </c>
       <c r="W121" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:27">
       <c r="D122" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="E122"/>
       <c r="M122" t="s">
@@ -37112,15 +37124,15 @@
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W122" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:27">
       <c r="D123" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="E123" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="M123" t="s">
         <v>1474</v>
@@ -37145,15 +37157,15 @@
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W123" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="124" spans="1:27">
       <c r="D124" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="E124" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="M124" t="s">
         <v>1474</v>
@@ -37166,15 +37178,15 @@
         <v>{szContent="侠士对抗类装分过低，请前往分流场景或黑戈壁参与。",szNote="据点攻防·装分过低",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·装分过低",key="挂机检测",},},},</v>
       </c>
       <c r="W124" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="125" spans="1:27">
       <c r="D125" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="E125" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="M125" t="s">
         <v>1474</v>
@@ -37187,15 +37199,15 @@
         <v>{szContent="因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！",szNote="据点攻防·禁止参与",col={255,50,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},},},</v>
       </c>
       <c r="W125" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="126" spans="1:27">
       <c r="D126" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="E126" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="M126" t="s">
         <v>1474</v>
@@ -37228,13 +37240,13 @@
     </row>
     <row r="128" customFormat="1" spans="1:27">
       <c r="C128" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D128" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="E128" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="M128" t="s">
         <v>1981</v>
@@ -37247,7 +37259,7 @@
         <v>{szContent="增援已至武王城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·武王城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},},},</v>
       </c>
       <c r="W128" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="129" spans="1:23">
@@ -37264,13 +37276,13 @@
     </row>
     <row r="130" customFormat="1" spans="1:23">
       <c r="C130" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D130" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="E130" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="M130" t="s">
         <v>1977</v>
@@ -37283,7 +37295,7 @@
         <v>{szContent="增援已至凛风堡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·凛风堡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},},},</v>
       </c>
       <c r="W130" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:23">
@@ -37300,13 +37312,13 @@
     </row>
     <row r="132" customFormat="1" spans="1:23">
       <c r="C132" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D132" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="E132" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="M132" t="s">
         <v>1981</v>
@@ -37319,18 +37331,18 @@
         <v>{szContent="增援已至盘龙坞，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·盘龙坞",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},},},</v>
       </c>
       <c r="W132" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:23">
       <c r="C133" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D133" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="E133" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="M133" t="s">
         <v>1981</v>
@@ -37343,7 +37355,7 @@
         <v>{szContent="增援已至逐鹿坪，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·逐鹿坪",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},},},</v>
       </c>
       <c r="W133" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="134" spans="1:23">
@@ -37360,13 +37372,13 @@
     </row>
     <row r="135" customFormat="1" spans="1:23">
       <c r="C135" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D135" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="E135" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="M135" t="s">
         <v>1977</v>
@@ -37379,18 +37391,18 @@
         <v>{szContent="增援已至龙门镇，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·龙门镇",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},},},</v>
       </c>
       <c r="W135" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:23">
       <c r="C136" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D136" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="E136" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="M136" t="s">
         <v>1977</v>
@@ -37403,7 +37415,7 @@
         <v>{szContent="增援已至飞沙关，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·飞沙关",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},},},</v>
       </c>
       <c r="W136" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="137" spans="1:23">
@@ -37420,13 +37432,13 @@
     </row>
     <row r="138" customFormat="1" spans="1:23">
       <c r="C138" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D138" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="E138" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="M138" t="s">
         <v>1981</v>
@@ -37439,18 +37451,18 @@
         <v>{szContent="增援已至红莲岗，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·红莲岗",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},},},</v>
       </c>
       <c r="W138" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="139" customFormat="1" spans="1:23">
       <c r="C139" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D139" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="E139" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="M139" t="s">
         <v>1981</v>
@@ -37463,7 +37475,7 @@
         <v>{szContent="增援已至秋雨堡，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·秋雨堡",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},},},</v>
       </c>
       <c r="W139" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="140" spans="1:23">
@@ -37480,13 +37492,13 @@
     </row>
     <row r="141" customFormat="1" spans="1:23">
       <c r="C141" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D141" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="E141" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="M141" t="s">
         <v>1977</v>
@@ -37499,18 +37511,18 @@
         <v>{szContent="增援已至神池岭，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·神池岭",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},},},</v>
       </c>
       <c r="W141" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:23">
       <c r="C142" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D142" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="E142" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="M142" t="s">
         <v>1977</v>
@@ -37523,7 +37535,7 @@
         <v>{szContent="增援已至烈日岗，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·烈日岗",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},},},</v>
       </c>
       <c r="W142" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="143" spans="1:23">
@@ -37540,13 +37552,13 @@
     </row>
     <row r="144" customFormat="1" spans="1:23">
       <c r="C144" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D144" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="E144" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="M144" t="s">
         <v>1981</v>
@@ -37559,18 +37571,18 @@
         <v>{szContent="增援已至大理山城，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·大理山城",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},},},</v>
       </c>
       <c r="W144" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="145" customFormat="1" spans="1:27">
       <c r="C145" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D145" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="E145" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="M145" t="s">
         <v>1981</v>
@@ -37583,7 +37595,7 @@
         <v>{szContent="增援已至千岩关，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·千岩关",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},},},</v>
       </c>
       <c r="W145" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="146" spans="1:27">
@@ -37600,13 +37612,13 @@
     </row>
     <row r="147" customFormat="1" spans="1:27">
       <c r="C147" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D147" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="E147" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="M147" t="s">
         <v>1977</v>
@@ -37619,18 +37631,18 @@
         <v>{szContent="增援已至扶风郡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·扶风郡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},},},</v>
       </c>
       <c r="W147" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="148" customFormat="1" spans="1:27">
       <c r="C148" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D148" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="E148" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="M148" t="s">
         <v>1977</v>
@@ -37643,7 +37655,7 @@
         <v>{szContent="增援已至世外坡，速速进攻！",szTarget="恶人谷督廷卫",szNote="恶人·兵符增援·世外坡",col={255,100,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},},},</v>
       </c>
       <c r="W148" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="149" spans="1:27">
@@ -37663,23 +37675,23 @@
         <v>1704</v>
       </c>
       <c r="D150" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="E150" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="V150" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W150" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="X150" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y150" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="151" customFormat="1" spans="1:27">
@@ -37687,23 +37699,23 @@
         <v>1704</v>
       </c>
       <c r="D151" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="E151" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="V151" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W151" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="X151" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y151" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="152" customFormat="1" spans="1:27">
@@ -37711,17 +37723,17 @@
         <v>1704</v>
       </c>
       <c r="D152" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="E152" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="V152" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W152" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:27">
@@ -37729,29 +37741,29 @@
         <v>1704</v>
       </c>
       <c r="D153" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="E153" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="V153" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W153" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="X153" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="Y153" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="154" customFormat="1" spans="1:27">
       <c r="C154" s="5"/>
       <c r="D154" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="E154"/>
       <c r="M154" t="s">
@@ -37762,16 +37774,16 @@
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W154" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="155" customFormat="1" spans="1:27">
       <c r="C155" s="5"/>
       <c r="D155" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="E155" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="M155" t="s">
         <v>1474</v>
@@ -37796,7 +37808,7 @@
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W155" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="156" customFormat="1" spans="1:27">
@@ -37804,10 +37816,10 @@
         <v>1974</v>
       </c>
       <c r="D156" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="E156" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="M156" t="s">
         <v>1474</v>
@@ -37826,10 +37838,10 @@
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W156" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="X156" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="157" customFormat="1" spans="1:27">
@@ -37837,10 +37849,10 @@
         <v>1974</v>
       </c>
       <c r="D157" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E157" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="M157" t="s">
         <v>1985</v>
@@ -37856,7 +37868,7 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W157" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="158" customFormat="1" spans="1:27">
@@ -37864,10 +37876,10 @@
         <v>1974</v>
       </c>
       <c r="D158" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="E158" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="M158" t="s">
         <v>1985</v>
@@ -37880,19 +37892,19 @@
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W158" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="X158" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="Y158" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="Z158" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="AA158" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="159" customFormat="1" spans="1:27">
@@ -37900,7 +37912,7 @@
         <v>1974</v>
       </c>
       <c r="D159" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="E159"/>
       <c r="M159" t="s">
@@ -37914,10 +37926,10 @@
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W159" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="X159" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:27">
@@ -37925,7 +37937,7 @@
         <v>1974</v>
       </c>
       <c r="D160" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="E160"/>
       <c r="M160" t="s">
@@ -37939,10 +37951,10 @@
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W160" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="X160" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="161" customFormat="1" spans="1:27">
@@ -37950,10 +37962,10 @@
         <v>1974</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="E161" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="M161" t="s">
         <v>1985</v>
@@ -37969,13 +37981,13 @@
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W161" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="X161" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="Y161" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="162" spans="1:27">
@@ -37995,23 +38007,23 @@
         <v>1704</v>
       </c>
       <c r="D163" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="E163" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="V163" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W163" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="X163" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y163" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="164" customFormat="1" spans="1:27">
@@ -38019,23 +38031,23 @@
         <v>1704</v>
       </c>
       <c r="D164" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="E164" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="V164" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W164" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="X164" s="5" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y164" s="5" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="165" customFormat="1" spans="1:27">
@@ -38043,17 +38055,17 @@
         <v>1704</v>
       </c>
       <c r="D165" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="E165" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="V165" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W165" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="166" customFormat="1" spans="1:27">
@@ -38061,29 +38073,29 @@
         <v>1704</v>
       </c>
       <c r="D166" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="E166" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="V166" t="str">
         <f t="shared" si="20"/>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W166" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="X166" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="Y166" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:27">
       <c r="C167" s="5"/>
       <c r="D167" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="E167"/>
       <c r="M167" t="s">
@@ -38094,16 +38106,16 @@
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W167" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:27">
       <c r="C168" s="5"/>
       <c r="D168" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="E168" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="M168" t="s">
         <v>1474</v>
@@ -38128,7 +38140,7 @@
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W168" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:27">
@@ -38136,10 +38148,10 @@
         <v>1974</v>
       </c>
       <c r="D169" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="E169" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="M169" t="s">
         <v>1474</v>
@@ -38158,10 +38170,10 @@
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W169" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="X169" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:27">
@@ -38169,10 +38181,10 @@
         <v>1974</v>
       </c>
       <c r="D170" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E170" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="M170" t="s">
         <v>1985</v>
@@ -38188,7 +38200,7 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W170" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:27">
@@ -38196,10 +38208,10 @@
         <v>1974</v>
       </c>
       <c r="D171" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="E171" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="M171" t="s">
         <v>1985</v>
@@ -38212,19 +38224,19 @@
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W171" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="X171" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="Y171" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="Z171" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="AA171" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:27">
@@ -38232,7 +38244,7 @@
         <v>1974</v>
       </c>
       <c r="D172" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="E172"/>
       <c r="M172" t="s">
@@ -38246,10 +38258,10 @@
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W172" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="X172" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:27">
@@ -38257,7 +38269,7 @@
         <v>1974</v>
       </c>
       <c r="D173" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="E173"/>
       <c r="M173" t="s">
@@ -38271,10 +38283,10 @@
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W173" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="X173" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="174" customFormat="1" spans="1:27">
@@ -38282,10 +38294,10 @@
         <v>1974</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="E174" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="M174" t="s">
         <v>1985</v>
@@ -38301,13 +38313,13 @@
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W174" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="X174" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="Y174" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="175" spans="1:27">
@@ -38374,10 +38386,10 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="F1" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="G1" t="s">
         <v>1952</v>
@@ -38419,7 +38431,7 @@
         <v>1963</v>
       </c>
       <c r="T1" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:33">
@@ -38436,16 +38448,16 @@
     </row>
     <row r="3" customFormat="1" spans="1:33">
       <c r="C3" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="D3" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="E3" t="s">
         <v>1995</v>
       </c>
       <c r="F3" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="G3" t="s">
         <v>2001</v>
@@ -38483,16 +38495,16 @@
     </row>
     <row r="4" customFormat="1" spans="1:33">
       <c r="C4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="D4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="E4" t="s">
         <v>1998</v>
       </c>
       <c r="F4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="G4" t="s">
         <v>1999</v>
@@ -38530,10 +38542,10 @@
     </row>
     <row r="5" customFormat="1" spans="1:33">
       <c r="C5" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D5" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="K5" t="s">
         <v>1985</v>
@@ -38549,15 +38561,15 @@
         <v>{szContent="侠士 [{$me}] 在拾取复活点物资时意外获得了[便携装置·神机车]。",szNote="获得·便携装置·神机车",col={255,255,100,},bSearch=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=134,nFrame=0,szName="获得·[便携装置·神机车]",nTime=10,nRefresh=1,key="交互事件",},},},</v>
       </c>
       <c r="U5" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:33">
       <c r="C6" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="D6" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="K6" t="s">
         <v>1985</v>
@@ -38570,18 +38582,18 @@
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U6" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="C7" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="D7" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="K7" t="s">
         <v>1985</v>
@@ -38594,18 +38606,18 @@
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U7" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="8" spans="1:33">
       <c r="C8" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D8" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="K8" t="s">
         <v>1985</v>
@@ -38615,21 +38627,21 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U8" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9" spans="1:33">
       <c r="C9" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D9" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="K9" t="s">
         <v>1985</v>
@@ -38645,51 +38657,51 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U9" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="V9" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="W9" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="X9" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="Y9" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="Z9" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="AA9" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="AB9" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="AC9" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="AD9" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="AE9" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="AF9" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:33">
       <c r="C10" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="D10" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="K10" t="s">
         <v>1985</v>
@@ -38699,39 +38711,39 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="主战场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U10" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="V10" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="W10" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="X10" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="Y10" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="Z10" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="AA10" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="AB10" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="C11" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D11" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="K11" t="s">
         <v>1985</v>
@@ -38741,39 +38753,39 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="奇袭场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U11" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="V11" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="W11" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="X11" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="Y11" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="Z11" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="AA11" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="AB11" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="C12" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D12" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="K12" t="s">
         <v>1981</v>
@@ -38783,15 +38795,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U12" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="C13" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D13" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="K13" t="s">
         <v>1977</v>
@@ -38801,15 +38813,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U13" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="C14" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D14" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="K14" t="s">
         <v>1985</v>
@@ -38819,15 +38831,15 @@
         <v>{szContent="驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n",szNote="阵营事件·本周战平",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U14" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="15" spans="1:33">
       <c r="C15" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="D15" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -38837,13 +38849,13 @@
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},},},</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="W15" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -38860,40 +38872,40 @@
     </row>
     <row r="17" spans="1:26">
       <c r="C17" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D17" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="T17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=7674,nTime=-2,szName="破阵点将·一·常驻",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,nTime=-2,szName="破阵点将·二·常驻",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U17" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="V17" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="W17" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="X17" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="Y17" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="Z17" s="5" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:26">
       <c r="C18" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="D18" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="K18" t="s">
         <v>1985</v>
@@ -38906,24 +38918,24 @@
         <v>{szContent="伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U18" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="V18" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="W18" s="5" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="X18" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="19" spans="1:26">
       <c r="C19" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="D19" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="K19" t="s">
         <v>1985</v>
@@ -38936,19 +38948,19 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="V19" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="W19" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="Y19" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -38965,40 +38977,40 @@
     </row>
     <row r="21" spans="1:26">
       <c r="C21" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="D21" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="T21" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=7674,nTime=-2,szName="破阵点将·一·常驻",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,nTime=-2,szName="破阵点将·二·常驻",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U21" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="V21" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="W21" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="X21" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="Y21" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="Z21" s="5" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:26">
       <c r="C22" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="D22" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="K22" t="s">
         <v>1985</v>
@@ -39011,24 +39023,24 @@
         <v>{szContent="韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U22" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="V22" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="W22" s="5" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="X22" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="C23" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="D23" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="K23" t="s">
         <v>1985</v>
@@ -39041,24 +39053,24 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="V23" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="W23" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="Y23" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:26">
       <c r="A24" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="B24">
         <v>-1</v>
@@ -39070,7 +39082,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:26">
       <c r="C25" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="D25"/>
       <c r="K25" t="s">
@@ -39081,18 +39093,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U25" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="V25" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="W25" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="C26" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="K26" t="s">
         <v>1977</v>
@@ -39102,18 +39114,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U26" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="V26" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="W26" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="C27" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="K27" t="s">
         <v>1981</v>
@@ -39123,12 +39135,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U27" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="C28" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="K28" t="s">
         <v>1981</v>
@@ -39138,12 +39150,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U28" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="C29" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="K29" t="s">
         <v>1977</v>
@@ -39153,12 +39165,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U29" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="30" spans="1:26">
       <c r="C30" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="K30" t="s">
         <v>1977</v>
@@ -39168,12 +39180,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U30" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="31" spans="1:26">
       <c r="C31" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="K31" t="s">
         <v>1985</v>
@@ -39183,12 +39195,12 @@
         <v>{szContent="据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="U31" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="32" spans="1:26">
       <c r="C32" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="K32" t="s">
         <v>1985</v>
@@ -39198,15 +39210,15 @@
         <v>{szContent="为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},},},</v>
       </c>
       <c r="U32" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="C33" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="D33" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="K33" t="s">
         <v>1985</v>
@@ -39219,7 +39231,7 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U33" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -39236,10 +39248,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:22">
       <c r="C35" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="D35" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="K35" t="s">
         <v>1985</v>
@@ -39249,15 +39261,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U35" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:22">
       <c r="C36" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D36" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="K36" t="s">
         <v>1985</v>
@@ -39267,15 +39279,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U36" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:22">
       <c r="C37" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D37" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="K37" t="s">
         <v>1985</v>
@@ -39285,18 +39297,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U37" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="V37" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:22">
       <c r="C38" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D38" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="K38" t="s">
         <v>1985</v>
@@ -39306,15 +39318,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U38" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:22">
       <c r="C39" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="D39" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="K39" t="s">
         <v>1985</v>
@@ -39324,18 +39336,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U39" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="V39" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:22">
       <c r="C40" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D40" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="K40" t="s">
         <v>1985</v>
@@ -39345,18 +39357,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U40" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:22">
       <c r="C41" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D41" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="K41" t="s">
         <v>1985</v>
@@ -39366,16 +39378,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U41" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="V41" s="7"/>
     </row>
     <row r="42" customFormat="1" spans="1:22">
       <c r="C42" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D42" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="K42" t="s">
         <v>1985</v>
@@ -39385,16 +39397,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U42" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="V42" s="7"/>
     </row>
     <row r="43" customFormat="1" spans="1:22">
       <c r="C43" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D43" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="K43" t="s">
         <v>1981</v>
@@ -39404,15 +39416,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U43" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:22">
       <c r="C44" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D44" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="K44" t="s">
         <v>1981</v>
@@ -39422,15 +39434,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U44" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:22">
       <c r="C45" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D45" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="K45" t="s">
         <v>1981</v>
@@ -39440,15 +39452,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U45" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:22">
       <c r="C46" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D46" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="K46" t="s">
         <v>1977</v>
@@ -39458,15 +39470,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U46" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:22">
       <c r="C47" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D47" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="K47" t="s">
         <v>1977</v>
@@ -39476,15 +39488,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U47" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:22">
       <c r="C48" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="D48" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="K48" t="s">
         <v>1977</v>
@@ -39494,15 +39506,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U48" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="49" spans="1:26">
       <c r="C49" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="D49" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="K49" t="s">
         <v>1985</v>
@@ -39515,15 +39527,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U49" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="50" spans="1:26">
       <c r="C50" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D50" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="K50" t="s">
         <v>1981</v>
@@ -39533,15 +39545,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U50" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="51" spans="1:26">
       <c r="C51" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D51" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="K51" t="s">
         <v>1977</v>
@@ -39551,15 +39563,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U51" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="52" spans="1:26">
       <c r="C52" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D52" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="K52" t="s">
         <v>1985</v>
@@ -39572,30 +39584,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U52" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V52" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="W52" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="X52" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="Y52" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="Z52" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="53" spans="1:26">
       <c r="C53" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D53" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="K53" t="s">
         <v>1985</v>
@@ -39608,19 +39620,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U53" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="V53" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="W53" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="X53" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="Y53" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" spans="1:26">
@@ -39637,10 +39649,10 @@
     </row>
     <row r="55" spans="1:26">
       <c r="C55" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="D55" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="K55" t="s">
         <v>1985</v>
@@ -39650,15 +39662,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U55" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D56" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="K56" t="s">
         <v>1985</v>
@@ -39668,15 +39680,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:26">
       <c r="C57" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D57" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="K57" t="s">
         <v>1985</v>
@@ -39686,15 +39698,15 @@
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:26">
       <c r="C58" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D58" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="K58" t="s">
         <v>1985</v>
@@ -39704,18 +39716,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U58" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="V58" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="D59" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="K59" t="s">
         <v>1985</v>
@@ -39725,18 +39737,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="V59" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:26">
       <c r="C60" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D60" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="K60" t="s">
         <v>1985</v>
@@ -39746,24 +39758,24 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="V60" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="W60" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:26">
       <c r="C61" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D61" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="K61" t="s">
         <v>1981</v>
@@ -39773,15 +39785,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U61" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:26">
       <c r="C62" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D62" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="K62" t="s">
         <v>1981</v>
@@ -39791,15 +39803,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U62" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
       <c r="C63" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D63" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="K63" t="s">
         <v>1981</v>
@@ -39809,15 +39821,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U63" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:26">
       <c r="C64" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D64" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="K64" t="s">
         <v>1977</v>
@@ -39827,15 +39839,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U64" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
       <c r="C65" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D65" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="K65" t="s">
         <v>1977</v>
@@ -39845,15 +39857,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U65" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="D66" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="K66" t="s">
         <v>1977</v>
@@ -39863,15 +39875,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
       <c r="C67" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="D67" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="K67" t="s">
         <v>1985</v>
@@ -39884,15 +39896,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U67" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:26">
       <c r="C68" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D68" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="K68" t="s">
         <v>1985</v>
@@ -39902,16 +39914,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U68" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="V68" s="7"/>
     </row>
     <row r="69" spans="1:26">
       <c r="C69" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D69" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="K69" t="s">
         <v>1985</v>
@@ -39921,21 +39933,21 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="V69" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="W69" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="70" spans="1:26">
       <c r="C70" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="D70" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="K70" t="s">
         <v>1985</v>
@@ -39950,10 +39962,10 @@
     </row>
     <row r="71" spans="1:26">
       <c r="C71" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D71" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="K71" t="s">
         <v>1981</v>
@@ -39963,15 +39975,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U71" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="72" spans="1:26">
       <c r="C72" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D72" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="K72" t="s">
         <v>1977</v>
@@ -39981,15 +39993,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U72" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D73" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="K73" t="s">
         <v>1985</v>
@@ -40002,30 +40014,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V73" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="W73" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="X73" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="Y73" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="Z73" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D74" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="K74" t="s">
         <v>1985</v>
@@ -40038,19 +40050,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="V74" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="W74" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="X74" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="Y74" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:26">
@@ -40067,10 +40079,10 @@
     </row>
     <row r="76" customFormat="1" spans="1:26">
       <c r="C76" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="D76" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="K76" t="s">
         <v>1985</v>
@@ -40083,24 +40095,24 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U76" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="V76" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="W76" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="X76" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="Y76" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
       <c r="A77" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B77">
         <v>-21</v>
@@ -40112,10 +40124,10 @@
     </row>
     <row r="78" customFormat="1" spans="1:26">
       <c r="C78" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="D78" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="K78" t="s">
         <v>1985</v>
@@ -40125,15 +40137,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U78" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:26">
       <c r="C79" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D79" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="K79" t="s">
         <v>1985</v>
@@ -40143,15 +40155,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U79" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:26">
       <c r="C80" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D80" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="K80" t="s">
         <v>1985</v>
@@ -40161,18 +40173,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U80" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="V80" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="3:26">
       <c r="C81" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D81" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="K81" t="s">
         <v>1985</v>
@@ -40182,15 +40194,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U81" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="3:26">
       <c r="C82" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="D82" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="K82" t="s">
         <v>1985</v>
@@ -40200,18 +40212,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U82" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="V82" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="3:26">
       <c r="C83" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D83" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="K83" t="s">
         <v>1985</v>
@@ -40221,18 +40233,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U83" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="V83" s="3" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="3:26">
       <c r="C84" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D84" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="K84" t="s">
         <v>1981</v>
@@ -40242,15 +40254,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U84" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="3:26">
       <c r="C85" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D85" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="K85" t="s">
         <v>1981</v>
@@ -40260,15 +40272,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U85" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="3:26">
       <c r="C86" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D86" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="K86" t="s">
         <v>1981</v>
@@ -40278,15 +40290,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U86" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="3:26">
       <c r="C87" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D87" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="K87" t="s">
         <v>1977</v>
@@ -40296,15 +40308,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U87" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="3:26">
       <c r="C88" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D88" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="K88" t="s">
         <v>1977</v>
@@ -40314,15 +40326,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U88" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="3:26">
       <c r="C89" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="D89" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="K89" t="s">
         <v>1977</v>
@@ -40332,15 +40344,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="3:26">
       <c r="C90" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="D90" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="K90" t="s">
         <v>1985</v>
@@ -40353,15 +40365,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U90" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="3:26">
       <c r="C91" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D91" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="K91" t="s">
         <v>1985</v>
@@ -40371,16 +40383,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U91" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="V91" s="7"/>
     </row>
     <row r="92" customFormat="1" spans="3:26">
       <c r="C92" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D92" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="K92" t="s">
         <v>1985</v>
@@ -40390,16 +40402,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U92" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="V92" s="7"/>
     </row>
     <row r="93" customFormat="1" spans="3:26">
       <c r="C93" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D93" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="K93" t="s">
         <v>1981</v>
@@ -40409,15 +40421,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U93" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="3:26">
       <c r="C94" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D94" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="K94" t="s">
         <v>1977</v>
@@ -40427,15 +40439,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U94" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="3:26">
       <c r="C95" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D95" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="K95" t="s">
         <v>1985</v>
@@ -40448,30 +40460,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U95" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V95" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="W95" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="X95" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="Y95" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="Z95" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="3:26">
       <c r="C96" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D96" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="K96" t="s">
         <v>1985</v>
@@ -40484,24 +40496,24 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U96" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="V96" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="W96" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="X96" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="Y96" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:22">
       <c r="A97" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="B97">
         <v>-3</v>
@@ -40513,7 +40525,7 @@
     </row>
     <row r="98" customFormat="1" spans="1:22">
       <c r="C98" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="K98" t="s">
         <v>1977</v>
@@ -40523,12 +40535,12 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U98" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:22">
       <c r="C99" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="K99" t="s">
         <v>1981</v>
@@ -40538,7 +40550,7 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U99" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:22">
@@ -40555,10 +40567,10 @@
     </row>
     <row r="101" customFormat="1" spans="1:22">
       <c r="C101" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D101" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="K101" t="s">
         <v>1985</v>
@@ -40568,16 +40580,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U101" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="V101" s="7"/>
     </row>
     <row r="102" customFormat="1" spans="1:22">
       <c r="C102" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D102" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="K102" t="s">
         <v>1985</v>
@@ -40587,16 +40599,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U102" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="V102" s="7"/>
     </row>
     <row r="103" customFormat="1" spans="1:22">
       <c r="C103" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D103" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="K103" t="s">
         <v>1985</v>
@@ -40606,18 +40618,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U103" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="V103" s="3" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:22">
       <c r="C104" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D104" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="K104" t="s">
         <v>1981</v>
@@ -40627,15 +40639,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U104" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:22">
       <c r="C105" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D105" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="K105" t="s">
         <v>1981</v>
@@ -40645,15 +40657,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U105" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:22">
       <c r="C106" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D106" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="K106" t="s">
         <v>1981</v>
@@ -40663,15 +40675,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U106" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:22">
       <c r="C107" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D107" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="K107" t="s">
         <v>1977</v>
@@ -40681,15 +40693,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U107" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:22">
       <c r="C108" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D108" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="K108" t="s">
         <v>1977</v>
@@ -40699,15 +40711,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U108" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:22">
       <c r="C109" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="D109" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="K109" t="s">
         <v>1977</v>
@@ -40717,15 +40729,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U109" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:22">
       <c r="C110" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="D110" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="K110" t="s">
         <v>1985</v>
@@ -40738,15 +40750,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U110" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:22">
       <c r="C111" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="D111" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="K111" t="s">
         <v>1981</v>
@@ -40756,15 +40768,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U111" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:22">
       <c r="C112" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D112" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="K112" t="s">
         <v>1977</v>
@@ -40774,15 +40786,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U112" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:34">
       <c r="C113" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D113" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="K113" t="s">
         <v>1985</v>
@@ -40795,30 +40807,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U113" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V113" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="W113" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="X113" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="Y113" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="Z113" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:34">
       <c r="C114" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D114" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="K114" t="s">
         <v>1985</v>
@@ -40831,27 +40843,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U114" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="V114" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="W114" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="X114" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="Y114" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:34">
       <c r="C115" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D115" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="K115" t="s">
         <v>1985</v>
@@ -40867,27 +40879,27 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U115" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="V115" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="W115" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="X115" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="Y115" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:34">
       <c r="C116" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="D116" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="K116" t="s">
         <v>1985</v>
@@ -40897,15 +40909,15 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U116" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:34">
       <c r="C117" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="D117" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="K117" t="s">
         <v>1985</v>
@@ -40915,7 +40927,7 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U117" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:34">
@@ -40932,13 +40944,13 @@
     </row>
     <row r="119" customFormat="1" spans="1:34">
       <c r="C119" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D119" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G119" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="K119" t="s">
         <v>1985</v>
@@ -40951,7 +40963,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U119" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V119" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G119&amp;"·浩气大旗"&amp;""",},"</f>
@@ -40962,19 +40974,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X119" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="Y119" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="Z119" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AA119" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AB119" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AC119" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G119&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G119&amp;"·浩气大旗"""&amp;",},"</f>
@@ -40987,10 +40999,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:34">
       <c r="C120" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D120" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K120" t="s">
         <v>1985</v>
@@ -41003,16 +41015,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U120" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="V120" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="W120" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="X120" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="121" spans="1:34">
@@ -41029,13 +41041,13 @@
     </row>
     <row r="122" customFormat="1" spans="1:34">
       <c r="C122" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D122" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G122" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="K122" t="s">
         <v>1985</v>
@@ -41048,7 +41060,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U122" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V122" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G122&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41059,19 +41071,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
       </c>
       <c r="X122" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="Y122" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="Z122" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AA122" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AB122" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AC122" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G122&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G122&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41084,10 +41096,10 @@
     </row>
     <row r="123" spans="1:34">
       <c r="C123" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D123" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K123" t="s">
         <v>1985</v>
@@ -41100,16 +41112,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U123" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="V123" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="W123" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="X123" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -41126,16 +41138,16 @@
     </row>
     <row r="125" customFormat="1" spans="1:34">
       <c r="C125" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D125" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G125" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="H125" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="K125" t="s">
         <v>1985</v>
@@ -41148,7 +41160,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U125" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V125" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G125&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41167,19 +41179,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z125" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA125" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB125" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC125" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD125" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE125" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G125&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G125&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41200,10 +41212,10 @@
     </row>
     <row r="126" spans="1:34">
       <c r="C126" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D126" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K126" t="s">
         <v>1985</v>
@@ -41216,22 +41228,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U126" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="V126" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="W126" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X126" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y126" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="Z126" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="127" spans="1:34">
@@ -41248,16 +41260,16 @@
     </row>
     <row r="128" customFormat="1" spans="1:34">
       <c r="C128" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D128" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G128" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="H128" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="K128" t="s">
         <v>1985</v>
@@ -41270,7 +41282,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U128" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V128" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G128&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41289,19 +41301,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z128" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA128" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB128" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC128" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD128" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE128" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G128&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G128&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41322,10 +41334,10 @@
     </row>
     <row r="129" spans="1:34">
       <c r="C129" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D129" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K129" t="s">
         <v>1985</v>
@@ -41338,22 +41350,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U129" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="V129" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="W129" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X129" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y129" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="Z129" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="130" spans="1:34">
@@ -41370,16 +41382,16 @@
     </row>
     <row r="131" customFormat="1" spans="1:34">
       <c r="C131" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D131" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G131" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="H131" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="K131" t="s">
         <v>1985</v>
@@ -41392,7 +41404,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V131" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G131&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41411,19 +41423,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z131" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA131" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB131" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC131" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD131" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE131" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G131&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G131&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41444,10 +41456,10 @@
     </row>
     <row r="132" spans="1:34">
       <c r="C132" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D132" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K132" t="s">
         <v>1985</v>
@@ -41460,22 +41472,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U132" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="V132" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="W132" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X132" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y132" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="Z132" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="133" spans="1:34">
@@ -41492,16 +41504,16 @@
     </row>
     <row r="134" customFormat="1" spans="1:34">
       <c r="C134" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D134" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G134" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="H134" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="K134" t="s">
         <v>1985</v>
@@ -41514,7 +41526,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U134" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V134" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G134&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41533,19 +41545,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z134" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA134" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB134" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC134" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD134" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE134" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G134&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G134&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41566,10 +41578,10 @@
     </row>
     <row r="135" spans="1:34">
       <c r="C135" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D135" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K135" t="s">
         <v>1985</v>
@@ -41582,22 +41594,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U135" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="V135" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="W135" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X135" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y135" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="Z135" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -41614,16 +41626,16 @@
     </row>
     <row r="137" customFormat="1" spans="1:34">
       <c r="C137" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D137" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G137" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="H137" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="K137" t="s">
         <v>1985</v>
@@ -41636,7 +41648,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U137" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V137" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G137&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41655,19 +41667,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z137" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA137" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB137" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC137" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD137" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE137" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G137&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G137&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41688,10 +41700,10 @@
     </row>
     <row r="138" spans="1:34">
       <c r="C138" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D138" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K138" t="s">
         <v>1985</v>
@@ -41704,22 +41716,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U138" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="V138" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="W138" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X138" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y138" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="Z138" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="139" spans="1:34">
@@ -41736,16 +41748,16 @@
     </row>
     <row r="140" customFormat="1" spans="1:34">
       <c r="C140" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D140" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G140" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="H140" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="K140" t="s">
         <v>1985</v>
@@ -41758,7 +41770,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U140" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V140" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G140&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41777,19 +41789,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z140" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA140" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB140" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC140" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD140" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE140" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G140&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G140&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41810,10 +41822,10 @@
     </row>
     <row r="141" spans="1:34">
       <c r="C141" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D141" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K141" t="s">
         <v>1985</v>
@@ -41826,22 +41838,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U141" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="V141" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="W141" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X141" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y141" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="Z141" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -41858,16 +41870,16 @@
     </row>
     <row r="143" customFormat="1" spans="1:34">
       <c r="C143" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D143" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G143" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="H143" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="K143" t="s">
         <v>1985</v>
@@ -41880,7 +41892,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U143" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V143" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G143&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41899,19 +41911,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z143" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA143" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB143" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC143" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD143" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE143" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G143&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G143&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41932,10 +41944,10 @@
     </row>
     <row r="144" spans="1:34">
       <c r="C144" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D144" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K144" t="s">
         <v>1985</v>
@@ -41948,22 +41960,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U144" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="V144" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="W144" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X144" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y144" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="Z144" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="145" spans="1:34">
@@ -41980,16 +41992,16 @@
     </row>
     <row r="146" customFormat="1" spans="1:34">
       <c r="C146" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D146" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G146" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="H146" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="K146" t="s">
         <v>1985</v>
@@ -42002,7 +42014,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U146" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V146" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G146&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42021,19 +42033,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z146" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA146" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB146" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC146" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD146" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE146" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G146&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G146&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42054,10 +42066,10 @@
     </row>
     <row r="147" spans="1:34">
       <c r="C147" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D147" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K147" t="s">
         <v>1985</v>
@@ -42070,22 +42082,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U147" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="V147" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="W147" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X147" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y147" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="Z147" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -42102,16 +42114,16 @@
     </row>
     <row r="149" customFormat="1" spans="1:34">
       <c r="C149" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D149" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G149" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="H149" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="K149" t="s">
         <v>1985</v>
@@ -42124,7 +42136,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U149" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V149" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G149&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42143,19 +42155,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z149" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA149" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB149" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC149" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD149" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE149" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G149&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G149&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42176,10 +42188,10 @@
     </row>
     <row r="150" spans="1:34">
       <c r="C150" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D150" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K150" t="s">
         <v>1985</v>
@@ -42192,22 +42204,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U150" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="V150" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="W150" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X150" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y150" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="Z150" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="151" spans="1:34">
@@ -42224,16 +42236,16 @@
     </row>
     <row r="152" customFormat="1" spans="1:34">
       <c r="C152" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D152" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G152" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="H152" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="K152" t="s">
         <v>1985</v>
@@ -42246,7 +42258,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U152" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V152" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G152&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42265,19 +42277,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z152" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA152" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB152" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC152" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD152" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE152" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G152&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G152&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42298,10 +42310,10 @@
     </row>
     <row r="153" spans="1:34">
       <c r="C153" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D153" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K153" t="s">
         <v>1985</v>
@@ -42314,22 +42326,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U153" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="V153" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="W153" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X153" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y153" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="Z153" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -42346,16 +42358,16 @@
     </row>
     <row r="155" customFormat="1" spans="1:34">
       <c r="C155" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D155" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G155" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H155" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="K155" t="s">
         <v>1985</v>
@@ -42368,7 +42380,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U155" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V155" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G155&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42387,19 +42399,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z155" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA155" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB155" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC155" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD155" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE155" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G155&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G155&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42420,10 +42432,10 @@
     </row>
     <row r="156" spans="1:34">
       <c r="C156" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D156" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K156" t="s">
         <v>1985</v>
@@ -42436,22 +42448,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U156" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="V156" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="W156" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X156" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y156" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="Z156" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="157" spans="1:34">
@@ -42468,16 +42480,16 @@
     </row>
     <row r="158" customFormat="1" spans="1:34">
       <c r="C158" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D158" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G158" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H158" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="K158" t="s">
         <v>1985</v>
@@ -42490,7 +42502,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U158" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V158" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G158&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42509,19 +42521,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
       </c>
       <c r="Z158" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="AA158" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="AB158" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="AC158" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="AD158" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="AE158" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G158&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G158&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42542,10 +42554,10 @@
     </row>
     <row r="159" spans="1:34">
       <c r="C159" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D159" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K159" t="s">
         <v>1985</v>
@@ -42558,22 +42570,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U159" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="V159" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="W159" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X159" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y159" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="Z159" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="160" spans="1:34">
@@ -42590,16 +42602,16 @@
     </row>
     <row r="161" spans="1:26">
       <c r="C161" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="D161" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G161" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="H161" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="K161" t="s">
         <v>1985</v>
@@ -42612,30 +42624,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U161" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V161" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="W161" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="X161" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="Y161" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="Z161" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="162" spans="1:26">
       <c r="C162" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D162" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K162" t="s">
         <v>1985</v>
@@ -42648,30 +42660,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U162" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="V162" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="W162" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X162" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y162" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="Z162" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:26">
       <c r="C163" s="5" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="D163" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="K163" t="s">
         <v>1985</v>
@@ -42684,19 +42696,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U163" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="V163" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="W163" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="X163" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="Y163" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="164" spans="1:26">
@@ -42713,16 +42725,16 @@
     </row>
     <row r="165" spans="1:26">
       <c r="C165" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="D165" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G165" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="H165" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="K165" t="s">
         <v>1985</v>
@@ -42735,30 +42747,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U165" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="V165" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="W165" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="X165" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="Y165" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="Z165" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="166" spans="1:26">
       <c r="C166" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="D166" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="K166" t="s">
         <v>1985</v>
@@ -42771,30 +42783,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="V166" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="W166" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="X166" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="Y166" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="Z166" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:26">
       <c r="C167" s="5" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="D167" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="K167" t="s">
         <v>1985</v>
@@ -42807,19 +42819,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U167" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="V167" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="W167" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="X167" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="Y167" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="168" spans="1:26">

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5638" uniqueCount="2597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5646" uniqueCount="2597">
   <si>
     <t>__meta = {</t>
   </si>
@@ -6763,7 +6763,7 @@
     <t>{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},</t>
   </si>
   <si>
-    <t>据点之战在即，为公平起见，侠士将在30秒后被传出本图，据点帮会25名(PVP服为40名)拥有地图优先进入权的玩家将不会被传送出去。</t>
+    <t>据点之战在即，为公平起见，侠士将在30秒后被传出本图，据点帮会25名拥有地图优先进入权的玩家将不会被传送出去。</t>
   </si>
   <si>
     <t>据点攻防·场景清图</t>
@@ -9204,7 +9204,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1790094835000,</v>
+        <v>nTimeStamp = 1790249735000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -34318,9 +34318,12 @@
       <c r="E51" t="s">
         <v>2107</v>
       </c>
+      <c r="M51" t="s">
+        <v>1988</v>
+      </c>
       <c r="V51" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="攻防之战在即，为公平起见，侠士将在30秒后被传出本图，攻防排队将在12点30分或18点30分开始，请做好准备。",szTarget="%",szNote="阵营攻防·场景清图",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="攻防清图·出图剩余",nTime="30,攻防清图·出图剩余;32,阵营攻防·清图传出",nRefresh=1,key="挂机检测",},},},</v>
+        <v>{szContent="攻防之战在即，为公平起见，侠士将在30秒后被传出本图，攻防排队将在12点30分或18点30分开始，请做好准备。",szTarget="%",szNote="阵营攻防·场景清图",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="攻防清图·出图剩余",nTime="30,攻防清图·出图剩余;32,阵营攻防·清图传出",nRefresh=1,key="挂机检测",},},},</v>
       </c>
       <c r="W51" t="s">
         <v>2108</v>
@@ -34333,9 +34336,12 @@
       <c r="E52" t="s">
         <v>2110</v>
       </c>
+      <c r="M52" t="s">
+        <v>1988</v>
+      </c>
       <c r="V52" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在5分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=300,key="阵营业务",},},},</v>
+        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在5分钟后传出场景",szNote="中立侠士·请离场景",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=300,key="阵营业务",},},},</v>
       </c>
       <c r="W52" t="s">
         <v>2111</v>
@@ -34348,9 +34354,12 @@
       <c r="E53" t="s">
         <v>2110</v>
       </c>
+      <c r="M53" t="s">
+        <v>1988</v>
+      </c>
       <c r="V53" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在4分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=240,key="阵营业务",},},},</v>
+        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在4分钟后传出场景",szNote="中立侠士·请离场景",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=240,key="阵营业务",},},},</v>
       </c>
       <c r="W53" t="s">
         <v>2113</v>
@@ -34363,9 +34372,12 @@
       <c r="E54" t="s">
         <v>2110</v>
       </c>
+      <c r="M54" t="s">
+        <v>1988</v>
+      </c>
       <c r="V54" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在3分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=180,key="阵营业务",},},},</v>
+        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在3分钟后传出场景",szNote="中立侠士·请离场景",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=180,key="阵营业务",},},},</v>
       </c>
       <c r="W54" t="s">
         <v>2115</v>
@@ -34378,9 +34390,12 @@
       <c r="E55" t="s">
         <v>2110</v>
       </c>
+      <c r="M55" t="s">
+        <v>1988</v>
+      </c>
       <c r="V55" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在2分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=120,key="阵营业务",},},},</v>
+        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在2分钟后传出场景",szNote="中立侠士·请离场景",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=120,key="阵营业务",},},},</v>
       </c>
       <c r="W55" t="s">
         <v>2117</v>
@@ -34393,9 +34408,12 @@
       <c r="E56" t="s">
         <v>2110</v>
       </c>
+      <c r="M56" t="s">
+        <v>1988</v>
+      </c>
       <c r="V56" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在1分钟后传出场景",szNote="中立侠士·请离场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=60,key="阵营业务",},},},</v>
+        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将在1分钟后传出场景",szNote="中立侠士·请离场景",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出剩余",nTime=60,key="阵营业务",},},},</v>
       </c>
       <c r="W56" t="s">
         <v>2119</v>
@@ -34408,9 +34426,12 @@
       <c r="E57" t="s">
         <v>2121</v>
       </c>
+      <c r="M57" t="s">
+        <v>1988</v>
+      </c>
       <c r="V57" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将传出场景",szNote="中立侠士·传出场景",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出场景",nTime=5,key="阵营业务",},},},</v>
+        <v>{szContent="阵营业务繁忙，中立侠士只能停留30分钟，您将传出场景",szNote="中立侠士·传出场景",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="中立侠士·传出场景",nTime=5,key="阵营业务",},},},</v>
       </c>
       <c r="W57" t="s">
         <v>2122</v>
@@ -37308,9 +37329,12 @@
       <c r="E127" t="s">
         <v>2235</v>
       </c>
+      <c r="M127" t="s">
+        <v>1988</v>
+      </c>
       <c r="V127" t="str">
         <f t="shared" si="19"/>
-        <v>{szContent="据点之战在即，为公平起见，侠士将在30秒后被传出本图，据点帮会25名(PVP服为40名)拥有地图优先进入权的玩家将不会被传送出去。",szTarget="%",szNote="据点攻防·场景清图",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="攻防清图·出图剩余",nTime="30,攻防清图·出图剩余;32,据点攻防·清图传出",nRefresh=1,key="挂机检测",},},},</v>
+        <v>{szContent="据点之战在即，为公平起见，侠士将在30秒后被传出本图，据点帮会25名拥有地图优先进入权的玩家将不会被传送出去。",szTarget="%",szNote="据点攻防·场景清图",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="攻防清图·出图剩余",nTime="30,攻防清图·出图剩余;32,据点攻防·清图传出",nRefresh=1,key="挂机检测",},},},</v>
       </c>
       <c r="W127" t="s">
         <v>2236</v>
@@ -41514,7 +41538,7 @@
         <v>1</v>
       </c>
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T162" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T131:T168" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
@@ -42806,7 +42830,7 @@
         <v>1</v>
       </c>
       <c r="T163" t="str">
-        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(C163),ISBLANK(L163),ISBLANK(M163),OR(ISBLANK(B162)=FALSE,ISBLANK(C162)=FALSE,ISBLANK(L162)=FALSE,ISBLANK(M162)=FALSE)),"},},}",IF(ISBLANK(C163),"","{szContent="""&amp;C163&amp;""","&amp;IF(D163&lt;&gt;"","szNote="""&amp;D163&amp;""",","")&amp;IF(K163&lt;&gt;"","col={"&amp;K163&amp;"},","")&amp;IF(L163&gt;0,"bSearch=true,","")&amp;IF(M163&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N163&gt;0,"szVoice="""&amp;N163&amp;""",","")&amp;IF(O163&gt;0,"bTeamChannel=true,","")&amp;IF(P163&gt;0,"bWhisperChannel=true,","")&amp;IF(Q163&gt;0,"bCenterAlarm=true,","")&amp;IF(R163&gt;0,"bScreenHead=true,","")&amp;IF(S163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U163:AAF163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U163" t="s">
@@ -42833,7 +42857,7 @@
         <v>656</v>
       </c>
       <c r="T164" t="str">
-        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(C164),ISBLANK(L164),ISBLANK(M164),OR(ISBLANK(B163)=FALSE,ISBLANK(C163)=FALSE,ISBLANK(L163)=FALSE,ISBLANK(M163)=FALSE)),"},},}",IF(ISBLANK(C164),"","{szContent="""&amp;C164&amp;""","&amp;IF(D164&lt;&gt;"","szNote="""&amp;D164&amp;""",","")&amp;IF(K164&lt;&gt;"","col={"&amp;K164&amp;"},","")&amp;IF(L164&gt;0,"bSearch=true,","")&amp;IF(M164&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N164&gt;0,"szVoice="""&amp;N164&amp;""",","")&amp;IF(O164&gt;0,"bTeamChannel=true,","")&amp;IF(P164&gt;0,"bWhisperChannel=true,","")&amp;IF(Q164&gt;0,"bCenterAlarm=true,","")&amp;IF(R164&gt;0,"bScreenHead=true,","")&amp;IF(S164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U164:AAF164)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>},[656]={</v>
       </c>
     </row>
@@ -42857,7 +42881,7 @@
         <v>1</v>
       </c>
       <c r="T165" t="str">
-        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(C165),ISBLANK(L165),ISBLANK(M165),OR(ISBLANK(B164)=FALSE,ISBLANK(C164)=FALSE,ISBLANK(L164)=FALSE,ISBLANK(M164)=FALSE)),"},},}",IF(ISBLANK(C165),"","{szContent="""&amp;C165&amp;""","&amp;IF(D165&lt;&gt;"","szNote="""&amp;D165&amp;""",","")&amp;IF(K165&lt;&gt;"","col={"&amp;K165&amp;"},","")&amp;IF(L165&gt;0,"bSearch=true,","")&amp;IF(M165&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N165&gt;0,"szVoice="""&amp;N165&amp;""",","")&amp;IF(O165&gt;0,"bTeamChannel=true,","")&amp;IF(P165&gt;0,"bWhisperChannel=true,","")&amp;IF(Q165&gt;0,"bCenterAlarm=true,","")&amp;IF(R165&gt;0,"bScreenHead=true,","")&amp;IF(S165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U165:AAF165)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U165" t="s">
@@ -42893,7 +42917,7 @@
         <v>1</v>
       </c>
       <c r="T166" t="str">
-        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(C166),ISBLANK(L166),ISBLANK(M166),OR(ISBLANK(B165)=FALSE,ISBLANK(C165)=FALSE,ISBLANK(L165)=FALSE,ISBLANK(M165)=FALSE)),"},},}",IF(ISBLANK(C166),"","{szContent="""&amp;C166&amp;""","&amp;IF(D166&lt;&gt;"","szNote="""&amp;D166&amp;""",","")&amp;IF(K166&lt;&gt;"","col={"&amp;K166&amp;"},","")&amp;IF(L166&gt;0,"bSearch=true,","")&amp;IF(M166&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N166&gt;0,"szVoice="""&amp;N166&amp;""",","")&amp;IF(O166&gt;0,"bTeamChannel=true,","")&amp;IF(P166&gt;0,"bWhisperChannel=true,","")&amp;IF(Q166&gt;0,"bCenterAlarm=true,","")&amp;IF(R166&gt;0,"bScreenHead=true,","")&amp;IF(S166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U166:AAF166)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
@@ -42929,7 +42953,7 @@
         <v>1</v>
       </c>
       <c r="T167" t="str">
-        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(C167),ISBLANK(L167),ISBLANK(M167),OR(ISBLANK(B166)=FALSE,ISBLANK(C166)=FALSE,ISBLANK(L166)=FALSE,ISBLANK(M166)=FALSE)),"},},}",IF(ISBLANK(C167),"","{szContent="""&amp;C167&amp;""","&amp;IF(D167&lt;&gt;"","szNote="""&amp;D167&amp;""",","")&amp;IF(K167&lt;&gt;"","col={"&amp;K167&amp;"},","")&amp;IF(L167&gt;0,"bSearch=true,","")&amp;IF(M167&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N167&gt;0,"szVoice="""&amp;N167&amp;""",","")&amp;IF(O167&gt;0,"bTeamChannel=true,","")&amp;IF(P167&gt;0,"bWhisperChannel=true,","")&amp;IF(Q167&gt;0,"bCenterAlarm=true,","")&amp;IF(R167&gt;0,"bScreenHead=true,","")&amp;IF(S167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U167:AAF167)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U167" t="s">
@@ -42950,7 +42974,7 @@
     </row>
     <row r="168" spans="1:26">
       <c r="T168" t="str">
-        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(C168),ISBLANK(L168),ISBLANK(M168),OR(ISBLANK(B167)=FALSE,ISBLANK(C167)=FALSE,ISBLANK(L167)=FALSE,ISBLANK(M167)=FALSE)),"},},}",IF(ISBLANK(C168),"","{szContent="""&amp;C168&amp;""","&amp;IF(D168&lt;&gt;"","szNote="""&amp;D168&amp;""",","")&amp;IF(K168&lt;&gt;"","col={"&amp;K168&amp;"},","")&amp;IF(L168&gt;0,"bSearch=true,","")&amp;IF(M168&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N168&gt;0,"szVoice="""&amp;N168&amp;""",","")&amp;IF(O168&gt;0,"bTeamChannel=true,","")&amp;IF(P168&gt;0,"bWhisperChannel=true,","")&amp;IF(Q168&gt;0,"bCenterAlarm=true,","")&amp;IF(R168&gt;0,"bScreenHead=true,","")&amp;IF(S168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U168:AAF168)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="4"/>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -4714,7 +4714,7 @@
     <t>{nClass=1,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},</t>
   </si>
   <si>
-    <t>{nClass=1,nIcon=7674,szName="破阵点将·一·常驻",nTime=-2,nRefresh=5,key="破阵点将·一·常驻",},{nClass=1,nIcon=7676,szName="破阵点将·二·常驻",nTime=-2,nRefresh=5,key="破阵点将·二·常驻",},</t>
+    <t>{nClass=1,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,nRefresh=5,key="破阵点将·一·常驻",},{nClass=1,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,nRefresh=5,key="破阵点将·二·常驻",},</t>
   </si>
   <si>
     <t>攻防场景特殊规则</t>
@@ -7099,7 +7099,7 @@
     <t>你已进入地图【浩气盟】。</t>
   </si>
   <si>
-    <t>{nClass=20,nIcon=7674,nTime=-2,szName="破阵点将·一·常驻",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,nTime=-2,szName="破阵点将·二·常驻",nRefresh=99999,key="破阵点将·二·常驻",},</t>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},</t>
@@ -9204,7 +9204,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1790249735000,</v>
+        <v>nTimeStamp = 1790531077000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="AN14" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29721,nLevel=1,nScrutinyType=1,szNote="业务繁忙·中立侠士",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=99999,key="通用事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=1,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},{nClass=1,nIcon=7674,szName="破阵点将·一·常驻",nTime=-2,nRefresh=5,key="破阵点将·一·常驻",},{nClass=1,nIcon=7676,szName="破阵点将·二·常驻",nTime=-2,nRefresh=5,key="破阵点将·二·常驻",},},},</v>
+        <v>{dwID=29721,nLevel=1,nScrutinyType=1,szNote="业务繁忙·中立侠士",col={255,255,0,},[1]={},[2]={},tCountdown={{nClass=1,nIcon=13,szName="通用事件",nTime=-1,nRefresh=99999,key="通用事件",},{nClass=2,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=1,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},{nClass=1,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,nRefresh=5,key="破阵点将·一·常驻",},{nClass=1,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,nRefresh=5,key="破阵点将·二·常驻",},},},</v>
       </c>
       <c r="AO14" t="s">
         <v>1548</v>
@@ -37408,7 +37408,7 @@
         <v>30</v>
       </c>
       <c r="V131" t="str">
-        <f t="shared" ref="V131:V162" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V131:V177" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
         <v>},[30]={</v>
       </c>
     </row>
@@ -38115,7 +38115,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W163" t="s">
@@ -38136,7 +38136,7 @@
         <v>656</v>
       </c>
       <c r="V164" t="str">
-        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(D164),ISBLANK(N164),ISBLANK(O164),OR(ISBLANK(B163)=FALSE,ISBLANK(D163)=FALSE,ISBLANK(N163)=FALSE,ISBLANK(O163)=FALSE)),"},},}",IF(ISBLANK(D164),"","{szContent="""&amp;D164&amp;""","&amp;IF(C164&lt;&gt;"","szTarget="""&amp;C164&amp;""",","")&amp;IF(E164&lt;&gt;"","szNote="""&amp;E164&amp;""",","")&amp;IF(M164&lt;&gt;"","col={"&amp;M164&amp;"},","")&amp;IF(N164&gt;0,"bSearch=true,","")&amp;IF(O164&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P164&gt;0,"szVoice="""&amp;P164&amp;""",","")&amp;IF(Q164&gt;0,"bTeamChannel=true,","")&amp;IF(R164&gt;0,"bWhisperChannel=true,","")&amp;IF(S164&gt;0,"bCenterAlarm=true,","")&amp;IF(T164&gt;0,"bScreenHead=true,","")&amp;IF(U164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W164:AAH164)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>},[656]={</v>
       </c>
     </row>
@@ -38151,7 +38151,7 @@
         <v>2166</v>
       </c>
       <c r="V165" t="str">
-        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(D165),ISBLANK(N165),ISBLANK(O165),OR(ISBLANK(B164)=FALSE,ISBLANK(D164)=FALSE,ISBLANK(N164)=FALSE,ISBLANK(O164)=FALSE)),"},},}",IF(ISBLANK(D165),"","{szContent="""&amp;D165&amp;""","&amp;IF(C165&lt;&gt;"","szTarget="""&amp;C165&amp;""",","")&amp;IF(E165&lt;&gt;"","szNote="""&amp;E165&amp;""",","")&amp;IF(M165&lt;&gt;"","col={"&amp;M165&amp;"},","")&amp;IF(N165&gt;0,"bSearch=true,","")&amp;IF(O165&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P165&gt;0,"szVoice="""&amp;P165&amp;""",","")&amp;IF(Q165&gt;0,"bTeamChannel=true,","")&amp;IF(R165&gt;0,"bWhisperChannel=true,","")&amp;IF(S165&gt;0,"bCenterAlarm=true,","")&amp;IF(T165&gt;0,"bScreenHead=true,","")&amp;IF(U165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W165:AAH165)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W165" t="s">
@@ -38175,7 +38175,7 @@
         <v>2171</v>
       </c>
       <c r="V166" t="str">
-        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(D166),ISBLANK(N166),ISBLANK(O166),OR(ISBLANK(B165)=FALSE,ISBLANK(D165)=FALSE,ISBLANK(N165)=FALSE,ISBLANK(O165)=FALSE)),"},},}",IF(ISBLANK(D166),"","{szContent="""&amp;D166&amp;""","&amp;IF(C166&lt;&gt;"","szTarget="""&amp;C166&amp;""",","")&amp;IF(E166&lt;&gt;"","szNote="""&amp;E166&amp;""",","")&amp;IF(M166&lt;&gt;"","col={"&amp;M166&amp;"},","")&amp;IF(N166&gt;0,"bSearch=true,","")&amp;IF(O166&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P166&gt;0,"szVoice="""&amp;P166&amp;""",","")&amp;IF(Q166&gt;0,"bTeamChannel=true,","")&amp;IF(R166&gt;0,"bWhisperChannel=true,","")&amp;IF(S166&gt;0,"bCenterAlarm=true,","")&amp;IF(T166&gt;0,"bScreenHead=true,","")&amp;IF(U166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W166:AAH166)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W166" t="s">
@@ -38199,7 +38199,7 @@
         <v>2174</v>
       </c>
       <c r="V167" t="str">
-        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(D167),ISBLANK(N167),ISBLANK(O167),OR(ISBLANK(B166)=FALSE,ISBLANK(D166)=FALSE,ISBLANK(N166)=FALSE,ISBLANK(O166)=FALSE)),"},},}",IF(ISBLANK(D167),"","{szContent="""&amp;D167&amp;""","&amp;IF(C167&lt;&gt;"","szTarget="""&amp;C167&amp;""",","")&amp;IF(E167&lt;&gt;"","szNote="""&amp;E167&amp;""",","")&amp;IF(M167&lt;&gt;"","col={"&amp;M167&amp;"},","")&amp;IF(N167&gt;0,"bSearch=true,","")&amp;IF(O167&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P167&gt;0,"szVoice="""&amp;P167&amp;""",","")&amp;IF(Q167&gt;0,"bTeamChannel=true,","")&amp;IF(R167&gt;0,"bWhisperChannel=true,","")&amp;IF(S167&gt;0,"bCenterAlarm=true,","")&amp;IF(T167&gt;0,"bScreenHead=true,","")&amp;IF(U167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W167:AAH167)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W167" t="s">
@@ -38217,7 +38217,7 @@
         <v>2176</v>
       </c>
       <c r="V168" t="str">
-        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(D168),ISBLANK(N168),ISBLANK(O168),OR(ISBLANK(B167)=FALSE,ISBLANK(D167)=FALSE,ISBLANK(N167)=FALSE,ISBLANK(O167)=FALSE)),"},},}",IF(ISBLANK(D168),"","{szContent="""&amp;D168&amp;""","&amp;IF(C168&lt;&gt;"","szTarget="""&amp;C168&amp;""",","")&amp;IF(E168&lt;&gt;"","szNote="""&amp;E168&amp;""",","")&amp;IF(M168&lt;&gt;"","col={"&amp;M168&amp;"},","")&amp;IF(N168&gt;0,"bSearch=true,","")&amp;IF(O168&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P168&gt;0,"szVoice="""&amp;P168&amp;""",","")&amp;IF(Q168&gt;0,"bTeamChannel=true,","")&amp;IF(R168&gt;0,"bWhisperChannel=true,","")&amp;IF(S168&gt;0,"bCenterAlarm=true,","")&amp;IF(T168&gt;0,"bScreenHead=true,","")&amp;IF(U168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W168:AAH168)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W168" t="s">
@@ -38240,7 +38240,7 @@
         <v>1988</v>
       </c>
       <c r="V169" t="str">
-        <f>IF(ISBLANK(B169)=FALSE,IF(ISBLANK(B168),"},["&amp;B169&amp;"]={","["&amp;B169&amp;"]={"),IF(AND(ISBLANK(B169),ISBLANK(D169),ISBLANK(N169),ISBLANK(O169),OR(ISBLANK(B168)=FALSE,ISBLANK(D168)=FALSE,ISBLANK(N168)=FALSE,ISBLANK(O168)=FALSE)),"},},}",IF(ISBLANK(D169),"","{szContent="""&amp;D169&amp;""","&amp;IF(C169&lt;&gt;"","szTarget="""&amp;C169&amp;""",","")&amp;IF(E169&lt;&gt;"","szNote="""&amp;E169&amp;""",","")&amp;IF(M169&lt;&gt;"","col={"&amp;M169&amp;"},","")&amp;IF(N169&gt;0,"bSearch=true,","")&amp;IF(O169&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P169&gt;0,"szVoice="""&amp;P169&amp;""",","")&amp;IF(Q169&gt;0,"bTeamChannel=true,","")&amp;IF(R169&gt;0,"bWhisperChannel=true,","")&amp;IF(S169&gt;0,"bCenterAlarm=true,","")&amp;IF(T169&gt;0,"bScreenHead=true,","")&amp;IF(U169&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W169&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W169:AAH169)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W169" t="s">
@@ -38274,7 +38274,7 @@
         <v>1</v>
       </c>
       <c r="V170" t="str">
-        <f>IF(ISBLANK(B170)=FALSE,IF(ISBLANK(B169),"},["&amp;B170&amp;"]={","["&amp;B170&amp;"]={"),IF(AND(ISBLANK(B170),ISBLANK(D170),ISBLANK(N170),ISBLANK(O170),OR(ISBLANK(B169)=FALSE,ISBLANK(D169)=FALSE,ISBLANK(N169)=FALSE,ISBLANK(O169)=FALSE)),"},},}",IF(ISBLANK(D170),"","{szContent="""&amp;D170&amp;""","&amp;IF(C170&lt;&gt;"","szTarget="""&amp;C170&amp;""",","")&amp;IF(E170&lt;&gt;"","szNote="""&amp;E170&amp;""",","")&amp;IF(M170&lt;&gt;"","col={"&amp;M170&amp;"},","")&amp;IF(N170&gt;0,"bSearch=true,","")&amp;IF(O170&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P170&gt;0,"szVoice="""&amp;P170&amp;""",","")&amp;IF(Q170&gt;0,"bTeamChannel=true,","")&amp;IF(R170&gt;0,"bWhisperChannel=true,","")&amp;IF(S170&gt;0,"bCenterAlarm=true,","")&amp;IF(T170&gt;0,"bScreenHead=true,","")&amp;IF(U170&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W170&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W170:AAH170)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W170" t="s">
@@ -38304,7 +38304,7 @@
         <v>1</v>
       </c>
       <c r="V171" t="str">
-        <f>IF(ISBLANK(B171)=FALSE,IF(ISBLANK(B170),"},["&amp;B171&amp;"]={","["&amp;B171&amp;"]={"),IF(AND(ISBLANK(B171),ISBLANK(D171),ISBLANK(N171),ISBLANK(O171),OR(ISBLANK(B170)=FALSE,ISBLANK(D170)=FALSE,ISBLANK(N170)=FALSE,ISBLANK(O170)=FALSE)),"},},}",IF(ISBLANK(D171),"","{szContent="""&amp;D171&amp;""","&amp;IF(C171&lt;&gt;"","szTarget="""&amp;C171&amp;""",","")&amp;IF(E171&lt;&gt;"","szNote="""&amp;E171&amp;""",","")&amp;IF(M171&lt;&gt;"","col={"&amp;M171&amp;"},","")&amp;IF(N171&gt;0,"bSearch=true,","")&amp;IF(O171&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P171&gt;0,"szVoice="""&amp;P171&amp;""",","")&amp;IF(Q171&gt;0,"bTeamChannel=true,","")&amp;IF(R171&gt;0,"bWhisperChannel=true,","")&amp;IF(S171&gt;0,"bCenterAlarm=true,","")&amp;IF(T171&gt;0,"bScreenHead=true,","")&amp;IF(U171&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W171&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W171:AAH171)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W171" t="s">
@@ -38334,7 +38334,7 @@
         <v>1</v>
       </c>
       <c r="V172" t="str">
-        <f>IF(ISBLANK(B172)=FALSE,IF(ISBLANK(B171),"},["&amp;B172&amp;"]={","["&amp;B172&amp;"]={"),IF(AND(ISBLANK(B172),ISBLANK(D172),ISBLANK(N172),ISBLANK(O172),OR(ISBLANK(B171)=FALSE,ISBLANK(D171)=FALSE,ISBLANK(N171)=FALSE,ISBLANK(O171)=FALSE)),"},},}",IF(ISBLANK(D172),"","{szContent="""&amp;D172&amp;""","&amp;IF(C172&lt;&gt;"","szTarget="""&amp;C172&amp;""",","")&amp;IF(E172&lt;&gt;"","szNote="""&amp;E172&amp;""",","")&amp;IF(M172&lt;&gt;"","col={"&amp;M172&amp;"},","")&amp;IF(N172&gt;0,"bSearch=true,","")&amp;IF(O172&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P172&gt;0,"szVoice="""&amp;P172&amp;""",","")&amp;IF(Q172&gt;0,"bTeamChannel=true,","")&amp;IF(R172&gt;0,"bWhisperChannel=true,","")&amp;IF(S172&gt;0,"bCenterAlarm=true,","")&amp;IF(T172&gt;0,"bScreenHead=true,","")&amp;IF(U172&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W172&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W172:AAH172)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W172" t="s">
@@ -38358,7 +38358,7 @@
         <v>1</v>
       </c>
       <c r="V173" t="str">
-        <f>IF(ISBLANK(B173)=FALSE,IF(ISBLANK(B172),"},["&amp;B173&amp;"]={","["&amp;B173&amp;"]={"),IF(AND(ISBLANK(B173),ISBLANK(D173),ISBLANK(N173),ISBLANK(O173),OR(ISBLANK(B172)=FALSE,ISBLANK(D172)=FALSE,ISBLANK(N172)=FALSE,ISBLANK(O172)=FALSE)),"},},}",IF(ISBLANK(D173),"","{szContent="""&amp;D173&amp;""","&amp;IF(C173&lt;&gt;"","szTarget="""&amp;C173&amp;""",","")&amp;IF(E173&lt;&gt;"","szNote="""&amp;E173&amp;""",","")&amp;IF(M173&lt;&gt;"","col={"&amp;M173&amp;"},","")&amp;IF(N173&gt;0,"bSearch=true,","")&amp;IF(O173&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P173&gt;0,"szVoice="""&amp;P173&amp;""",","")&amp;IF(Q173&gt;0,"bTeamChannel=true,","")&amp;IF(R173&gt;0,"bWhisperChannel=true,","")&amp;IF(S173&gt;0,"bCenterAlarm=true,","")&amp;IF(T173&gt;0,"bScreenHead=true,","")&amp;IF(U173&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W173&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W173:AAH173)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W173" t="s">
@@ -38392,7 +38392,7 @@
         <v>1</v>
       </c>
       <c r="V174" t="str">
-        <f>IF(ISBLANK(B174)=FALSE,IF(ISBLANK(B173),"},["&amp;B174&amp;"]={","["&amp;B174&amp;"]={"),IF(AND(ISBLANK(B174),ISBLANK(D174),ISBLANK(N174),ISBLANK(O174),OR(ISBLANK(B173)=FALSE,ISBLANK(D173)=FALSE,ISBLANK(N173)=FALSE,ISBLANK(O173)=FALSE)),"},},}",IF(ISBLANK(D174),"","{szContent="""&amp;D174&amp;""","&amp;IF(C174&lt;&gt;"","szTarget="""&amp;C174&amp;""",","")&amp;IF(E174&lt;&gt;"","szNote="""&amp;E174&amp;""",","")&amp;IF(M174&lt;&gt;"","col={"&amp;M174&amp;"},","")&amp;IF(N174&gt;0,"bSearch=true,","")&amp;IF(O174&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P174&gt;0,"szVoice="""&amp;P174&amp;""",","")&amp;IF(Q174&gt;0,"bTeamChannel=true,","")&amp;IF(R174&gt;0,"bWhisperChannel=true,","")&amp;IF(S174&gt;0,"bCenterAlarm=true,","")&amp;IF(T174&gt;0,"bScreenHead=true,","")&amp;IF(U174&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W174&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W174:AAH174)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W174" t="s">
@@ -38417,7 +38417,7 @@
         <v>1</v>
       </c>
       <c r="V175" t="str">
-        <f>IF(ISBLANK(B175)=FALSE,IF(ISBLANK(B174),"},["&amp;B175&amp;"]={","["&amp;B175&amp;"]={"),IF(AND(ISBLANK(B175),ISBLANK(D175),ISBLANK(N175),ISBLANK(O175),OR(ISBLANK(B174)=FALSE,ISBLANK(D174)=FALSE,ISBLANK(N174)=FALSE,ISBLANK(O174)=FALSE)),"},},}",IF(ISBLANK(D175),"","{szContent="""&amp;D175&amp;""","&amp;IF(C175&lt;&gt;"","szTarget="""&amp;C175&amp;""",","")&amp;IF(E175&lt;&gt;"","szNote="""&amp;E175&amp;""",","")&amp;IF(M175&lt;&gt;"","col={"&amp;M175&amp;"},","")&amp;IF(N175&gt;0,"bSearch=true,","")&amp;IF(O175&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P175&gt;0,"szVoice="""&amp;P175&amp;""",","")&amp;IF(Q175&gt;0,"bTeamChannel=true,","")&amp;IF(R175&gt;0,"bWhisperChannel=true,","")&amp;IF(S175&gt;0,"bCenterAlarm=true,","")&amp;IF(T175&gt;0,"bScreenHead=true,","")&amp;IF(U175&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W175&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W175:AAH175)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W175" t="s">
@@ -38447,7 +38447,7 @@
         <v>1</v>
       </c>
       <c r="V176" t="str">
-        <f>IF(ISBLANK(B176)=FALSE,IF(ISBLANK(B175),"},["&amp;B176&amp;"]={","["&amp;B176&amp;"]={"),IF(AND(ISBLANK(B176),ISBLANK(D176),ISBLANK(N176),ISBLANK(O176),OR(ISBLANK(B175)=FALSE,ISBLANK(D175)=FALSE,ISBLANK(N175)=FALSE,ISBLANK(O175)=FALSE)),"},},}",IF(ISBLANK(D176),"","{szContent="""&amp;D176&amp;""","&amp;IF(C176&lt;&gt;"","szTarget="""&amp;C176&amp;""",","")&amp;IF(E176&lt;&gt;"","szNote="""&amp;E176&amp;""",","")&amp;IF(M176&lt;&gt;"","col={"&amp;M176&amp;"},","")&amp;IF(N176&gt;0,"bSearch=true,","")&amp;IF(O176&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P176&gt;0,"szVoice="""&amp;P176&amp;""",","")&amp;IF(Q176&gt;0,"bTeamChannel=true,","")&amp;IF(R176&gt;0,"bWhisperChannel=true,","")&amp;IF(S176&gt;0,"bCenterAlarm=true,","")&amp;IF(T176&gt;0,"bScreenHead=true,","")&amp;IF(U176&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W176&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W176:AAH176)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W176" t="s">
@@ -38462,7 +38462,7 @@
     </row>
     <row r="177" spans="22:22">
       <c r="V177" t="str">
-        <f>IF(ISBLANK(B177)=FALSE,IF(ISBLANK(B176),"},["&amp;B177&amp;"]={","["&amp;B177&amp;"]={"),IF(AND(ISBLANK(B177),ISBLANK(D177),ISBLANK(N177),ISBLANK(O177),OR(ISBLANK(B176)=FALSE,ISBLANK(D176)=FALSE,ISBLANK(N176)=FALSE,ISBLANK(O176)=FALSE)),"},},}",IF(ISBLANK(D177),"","{szContent="""&amp;D177&amp;""","&amp;IF(C177&lt;&gt;"","szTarget="""&amp;C177&amp;""",","")&amp;IF(E177&lt;&gt;"","szNote="""&amp;E177&amp;""",","")&amp;IF(M177&lt;&gt;"","col={"&amp;M177&amp;"},","")&amp;IF(N177&gt;0,"bSearch=true,","")&amp;IF(O177&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P177&gt;0,"szVoice="""&amp;P177&amp;""",","")&amp;IF(Q177&gt;0,"bTeamChannel=true,","")&amp;IF(R177&gt;0,"bWhisperChannel=true,","")&amp;IF(S177&gt;0,"bCenterAlarm=true,","")&amp;IF(T177&gt;0,"bScreenHead=true,","")&amp;IF(U177&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W177&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W177:AAH177)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>},},}</v>
       </c>
     </row>
@@ -39017,7 +39017,7 @@
       </c>
       <c r="T17" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=7674,nTime=-2,szName="破阵点将·一·常驻",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,nTime=-2,szName="破阵点将·二·常驻",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
+        <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U17" t="s">
         <v>2346</v>
@@ -39122,7 +39122,7 @@
       </c>
       <c r="T21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=7674,nTime=-2,szName="破阵点将·一·常驻",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,nTime=-2,szName="破阵点将·二·常驻",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
+        <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U21" t="s">
         <v>2346</v>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -6382,10 +6382,10 @@
     <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=7674,nFrame=-1,nTime="2700.01,{$5}{$4}{$6}·{$8}{$7}{$9};4500.01,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=7676,nFrame=-1,nTime="1800.1,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},</t>
+    <t>{nClass=14,nIcon=7674,nFrame=-1,nTime="2700.1,{$5}{$4}{$6}·{$8}{$7}{$9};4500.1,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=7676,nFrame=-1,nTime="1800.14,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},</t>
   </si>
   <si>
     <t>{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},</t>
@@ -9246,7 +9246,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1790936210000,</v>
+        <v>nTimeStamp = 1791119599000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -34596,7 +34596,7 @@
       </c>
       <c r="V47" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},{nClass=14,nIcon=7674,nFrame=-1,nTime="2700.01,{$5}{$4}{$6}·{$8}{$7}{$9};4500.01,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},{nClass=14,nIcon=7676,nFrame=-1,nTime="1800.1,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},},},</v>
+        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},{nClass=14,nIcon=7674,nFrame=-1,nTime="2700.1,{$5}{$4}{$6}·{$8}{$7}{$9};4500.1,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},{nClass=14,nIcon=7676,nFrame=-1,nTime="1800.14,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},},},</v>
       </c>
       <c r="W47" t="s">
         <v>2101</v>
@@ -37786,7 +37786,7 @@
         <v>30</v>
       </c>
       <c r="V131" t="str">
-        <f t="shared" ref="V131:V177" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V131:V162" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
         <v>},[30]={</v>
       </c>
     </row>
@@ -38493,7 +38493,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W163" t="s">
@@ -38514,7 +38514,7 @@
         <v>656</v>
       </c>
       <c r="V164" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(D164),ISBLANK(N164),ISBLANK(O164),OR(ISBLANK(B163)=FALSE,ISBLANK(D163)=FALSE,ISBLANK(N163)=FALSE,ISBLANK(O163)=FALSE)),"},},}",IF(ISBLANK(D164),"","{szContent="""&amp;D164&amp;""","&amp;IF(C164&lt;&gt;"","szTarget="""&amp;C164&amp;""",","")&amp;IF(E164&lt;&gt;"","szNote="""&amp;E164&amp;""",","")&amp;IF(M164&lt;&gt;"","col={"&amp;M164&amp;"},","")&amp;IF(N164&gt;0,"bSearch=true,","")&amp;IF(O164&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P164&gt;0,"szVoice="""&amp;P164&amp;""",","")&amp;IF(Q164&gt;0,"bTeamChannel=true,","")&amp;IF(R164&gt;0,"bWhisperChannel=true,","")&amp;IF(S164&gt;0,"bCenterAlarm=true,","")&amp;IF(T164&gt;0,"bScreenHead=true,","")&amp;IF(U164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W164:AAH164)&amp;"},","")&amp;"},")))</f>
         <v>},[656]={</v>
       </c>
     </row>
@@ -38529,7 +38529,7 @@
         <v>2180</v>
       </c>
       <c r="V165" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(D165),ISBLANK(N165),ISBLANK(O165),OR(ISBLANK(B164)=FALSE,ISBLANK(D164)=FALSE,ISBLANK(N164)=FALSE,ISBLANK(O164)=FALSE)),"},},}",IF(ISBLANK(D165),"","{szContent="""&amp;D165&amp;""","&amp;IF(C165&lt;&gt;"","szTarget="""&amp;C165&amp;""",","")&amp;IF(E165&lt;&gt;"","szNote="""&amp;E165&amp;""",","")&amp;IF(M165&lt;&gt;"","col={"&amp;M165&amp;"},","")&amp;IF(N165&gt;0,"bSearch=true,","")&amp;IF(O165&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P165&gt;0,"szVoice="""&amp;P165&amp;""",","")&amp;IF(Q165&gt;0,"bTeamChannel=true,","")&amp;IF(R165&gt;0,"bWhisperChannel=true,","")&amp;IF(S165&gt;0,"bCenterAlarm=true,","")&amp;IF(T165&gt;0,"bScreenHead=true,","")&amp;IF(U165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W165:AAH165)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W165" t="s">
@@ -38553,7 +38553,7 @@
         <v>2185</v>
       </c>
       <c r="V166" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(D166),ISBLANK(N166),ISBLANK(O166),OR(ISBLANK(B165)=FALSE,ISBLANK(D165)=FALSE,ISBLANK(N165)=FALSE,ISBLANK(O165)=FALSE)),"},},}",IF(ISBLANK(D166),"","{szContent="""&amp;D166&amp;""","&amp;IF(C166&lt;&gt;"","szTarget="""&amp;C166&amp;""",","")&amp;IF(E166&lt;&gt;"","szNote="""&amp;E166&amp;""",","")&amp;IF(M166&lt;&gt;"","col={"&amp;M166&amp;"},","")&amp;IF(N166&gt;0,"bSearch=true,","")&amp;IF(O166&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P166&gt;0,"szVoice="""&amp;P166&amp;""",","")&amp;IF(Q166&gt;0,"bTeamChannel=true,","")&amp;IF(R166&gt;0,"bWhisperChannel=true,","")&amp;IF(S166&gt;0,"bCenterAlarm=true,","")&amp;IF(T166&gt;0,"bScreenHead=true,","")&amp;IF(U166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W166:AAH166)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W166" t="s">
@@ -38577,7 +38577,7 @@
         <v>2188</v>
       </c>
       <c r="V167" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(D167),ISBLANK(N167),ISBLANK(O167),OR(ISBLANK(B166)=FALSE,ISBLANK(D166)=FALSE,ISBLANK(N166)=FALSE,ISBLANK(O166)=FALSE)),"},},}",IF(ISBLANK(D167),"","{szContent="""&amp;D167&amp;""","&amp;IF(C167&lt;&gt;"","szTarget="""&amp;C167&amp;""",","")&amp;IF(E167&lt;&gt;"","szNote="""&amp;E167&amp;""",","")&amp;IF(M167&lt;&gt;"","col={"&amp;M167&amp;"},","")&amp;IF(N167&gt;0,"bSearch=true,","")&amp;IF(O167&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P167&gt;0,"szVoice="""&amp;P167&amp;""",","")&amp;IF(Q167&gt;0,"bTeamChannel=true,","")&amp;IF(R167&gt;0,"bWhisperChannel=true,","")&amp;IF(S167&gt;0,"bCenterAlarm=true,","")&amp;IF(T167&gt;0,"bScreenHead=true,","")&amp;IF(U167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W167:AAH167)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W167" t="s">
@@ -38595,7 +38595,7 @@
         <v>2190</v>
       </c>
       <c r="V168" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(D168),ISBLANK(N168),ISBLANK(O168),OR(ISBLANK(B167)=FALSE,ISBLANK(D167)=FALSE,ISBLANK(N167)=FALSE,ISBLANK(O167)=FALSE)),"},},}",IF(ISBLANK(D168),"","{szContent="""&amp;D168&amp;""","&amp;IF(C168&lt;&gt;"","szTarget="""&amp;C168&amp;""",","")&amp;IF(E168&lt;&gt;"","szNote="""&amp;E168&amp;""",","")&amp;IF(M168&lt;&gt;"","col={"&amp;M168&amp;"},","")&amp;IF(N168&gt;0,"bSearch=true,","")&amp;IF(O168&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P168&gt;0,"szVoice="""&amp;P168&amp;""",","")&amp;IF(Q168&gt;0,"bTeamChannel=true,","")&amp;IF(R168&gt;0,"bWhisperChannel=true,","")&amp;IF(S168&gt;0,"bCenterAlarm=true,","")&amp;IF(T168&gt;0,"bScreenHead=true,","")&amp;IF(U168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W168:AAH168)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W168" t="s">
@@ -38618,7 +38618,7 @@
         <v>2002</v>
       </c>
       <c r="V169" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B169)=FALSE,IF(ISBLANK(B168),"},["&amp;B169&amp;"]={","["&amp;B169&amp;"]={"),IF(AND(ISBLANK(B169),ISBLANK(D169),ISBLANK(N169),ISBLANK(O169),OR(ISBLANK(B168)=FALSE,ISBLANK(D168)=FALSE,ISBLANK(N168)=FALSE,ISBLANK(O168)=FALSE)),"},},}",IF(ISBLANK(D169),"","{szContent="""&amp;D169&amp;""","&amp;IF(C169&lt;&gt;"","szTarget="""&amp;C169&amp;""",","")&amp;IF(E169&lt;&gt;"","szNote="""&amp;E169&amp;""",","")&amp;IF(M169&lt;&gt;"","col={"&amp;M169&amp;"},","")&amp;IF(N169&gt;0,"bSearch=true,","")&amp;IF(O169&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P169&gt;0,"szVoice="""&amp;P169&amp;""",","")&amp;IF(Q169&gt;0,"bTeamChannel=true,","")&amp;IF(R169&gt;0,"bWhisperChannel=true,","")&amp;IF(S169&gt;0,"bCenterAlarm=true,","")&amp;IF(T169&gt;0,"bScreenHead=true,","")&amp;IF(U169&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W169&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W169:AAH169)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W169" t="s">
@@ -38652,7 +38652,7 @@
         <v>1</v>
       </c>
       <c r="V170" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B170)=FALSE,IF(ISBLANK(B169),"},["&amp;B170&amp;"]={","["&amp;B170&amp;"]={"),IF(AND(ISBLANK(B170),ISBLANK(D170),ISBLANK(N170),ISBLANK(O170),OR(ISBLANK(B169)=FALSE,ISBLANK(D169)=FALSE,ISBLANK(N169)=FALSE,ISBLANK(O169)=FALSE)),"},},}",IF(ISBLANK(D170),"","{szContent="""&amp;D170&amp;""","&amp;IF(C170&lt;&gt;"","szTarget="""&amp;C170&amp;""",","")&amp;IF(E170&lt;&gt;"","szNote="""&amp;E170&amp;""",","")&amp;IF(M170&lt;&gt;"","col={"&amp;M170&amp;"},","")&amp;IF(N170&gt;0,"bSearch=true,","")&amp;IF(O170&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P170&gt;0,"szVoice="""&amp;P170&amp;""",","")&amp;IF(Q170&gt;0,"bTeamChannel=true,","")&amp;IF(R170&gt;0,"bWhisperChannel=true,","")&amp;IF(S170&gt;0,"bCenterAlarm=true,","")&amp;IF(T170&gt;0,"bScreenHead=true,","")&amp;IF(U170&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W170&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W170:AAH170)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W170" t="s">
@@ -38682,7 +38682,7 @@
         <v>1</v>
       </c>
       <c r="V171" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B171)=FALSE,IF(ISBLANK(B170),"},["&amp;B171&amp;"]={","["&amp;B171&amp;"]={"),IF(AND(ISBLANK(B171),ISBLANK(D171),ISBLANK(N171),ISBLANK(O171),OR(ISBLANK(B170)=FALSE,ISBLANK(D170)=FALSE,ISBLANK(N170)=FALSE,ISBLANK(O170)=FALSE)),"},},}",IF(ISBLANK(D171),"","{szContent="""&amp;D171&amp;""","&amp;IF(C171&lt;&gt;"","szTarget="""&amp;C171&amp;""",","")&amp;IF(E171&lt;&gt;"","szNote="""&amp;E171&amp;""",","")&amp;IF(M171&lt;&gt;"","col={"&amp;M171&amp;"},","")&amp;IF(N171&gt;0,"bSearch=true,","")&amp;IF(O171&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P171&gt;0,"szVoice="""&amp;P171&amp;""",","")&amp;IF(Q171&gt;0,"bTeamChannel=true,","")&amp;IF(R171&gt;0,"bWhisperChannel=true,","")&amp;IF(S171&gt;0,"bCenterAlarm=true,","")&amp;IF(T171&gt;0,"bScreenHead=true,","")&amp;IF(U171&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W171&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W171:AAH171)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W171" t="s">
@@ -38712,7 +38712,7 @@
         <v>1</v>
       </c>
       <c r="V172" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B172)=FALSE,IF(ISBLANK(B171),"},["&amp;B172&amp;"]={","["&amp;B172&amp;"]={"),IF(AND(ISBLANK(B172),ISBLANK(D172),ISBLANK(N172),ISBLANK(O172),OR(ISBLANK(B171)=FALSE,ISBLANK(D171)=FALSE,ISBLANK(N171)=FALSE,ISBLANK(O171)=FALSE)),"},},}",IF(ISBLANK(D172),"","{szContent="""&amp;D172&amp;""","&amp;IF(C172&lt;&gt;"","szTarget="""&amp;C172&amp;""",","")&amp;IF(E172&lt;&gt;"","szNote="""&amp;E172&amp;""",","")&amp;IF(M172&lt;&gt;"","col={"&amp;M172&amp;"},","")&amp;IF(N172&gt;0,"bSearch=true,","")&amp;IF(O172&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P172&gt;0,"szVoice="""&amp;P172&amp;""",","")&amp;IF(Q172&gt;0,"bTeamChannel=true,","")&amp;IF(R172&gt;0,"bWhisperChannel=true,","")&amp;IF(S172&gt;0,"bCenterAlarm=true,","")&amp;IF(T172&gt;0,"bScreenHead=true,","")&amp;IF(U172&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W172&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W172:AAH172)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W172" t="s">
@@ -38736,7 +38736,7 @@
         <v>1</v>
       </c>
       <c r="V173" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B173)=FALSE,IF(ISBLANK(B172),"},["&amp;B173&amp;"]={","["&amp;B173&amp;"]={"),IF(AND(ISBLANK(B173),ISBLANK(D173),ISBLANK(N173),ISBLANK(O173),OR(ISBLANK(B172)=FALSE,ISBLANK(D172)=FALSE,ISBLANK(N172)=FALSE,ISBLANK(O172)=FALSE)),"},},}",IF(ISBLANK(D173),"","{szContent="""&amp;D173&amp;""","&amp;IF(C173&lt;&gt;"","szTarget="""&amp;C173&amp;""",","")&amp;IF(E173&lt;&gt;"","szNote="""&amp;E173&amp;""",","")&amp;IF(M173&lt;&gt;"","col={"&amp;M173&amp;"},","")&amp;IF(N173&gt;0,"bSearch=true,","")&amp;IF(O173&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P173&gt;0,"szVoice="""&amp;P173&amp;""",","")&amp;IF(Q173&gt;0,"bTeamChannel=true,","")&amp;IF(R173&gt;0,"bWhisperChannel=true,","")&amp;IF(S173&gt;0,"bCenterAlarm=true,","")&amp;IF(T173&gt;0,"bScreenHead=true,","")&amp;IF(U173&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W173&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W173:AAH173)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W173" t="s">
@@ -38770,7 +38770,7 @@
         <v>1</v>
       </c>
       <c r="V174" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B174)=FALSE,IF(ISBLANK(B173),"},["&amp;B174&amp;"]={","["&amp;B174&amp;"]={"),IF(AND(ISBLANK(B174),ISBLANK(D174),ISBLANK(N174),ISBLANK(O174),OR(ISBLANK(B173)=FALSE,ISBLANK(D173)=FALSE,ISBLANK(N173)=FALSE,ISBLANK(O173)=FALSE)),"},},}",IF(ISBLANK(D174),"","{szContent="""&amp;D174&amp;""","&amp;IF(C174&lt;&gt;"","szTarget="""&amp;C174&amp;""",","")&amp;IF(E174&lt;&gt;"","szNote="""&amp;E174&amp;""",","")&amp;IF(M174&lt;&gt;"","col={"&amp;M174&amp;"},","")&amp;IF(N174&gt;0,"bSearch=true,","")&amp;IF(O174&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P174&gt;0,"szVoice="""&amp;P174&amp;""",","")&amp;IF(Q174&gt;0,"bTeamChannel=true,","")&amp;IF(R174&gt;0,"bWhisperChannel=true,","")&amp;IF(S174&gt;0,"bCenterAlarm=true,","")&amp;IF(T174&gt;0,"bScreenHead=true,","")&amp;IF(U174&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W174&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W174:AAH174)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W174" t="s">
@@ -38795,7 +38795,7 @@
         <v>1</v>
       </c>
       <c r="V175" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B175)=FALSE,IF(ISBLANK(B174),"},["&amp;B175&amp;"]={","["&amp;B175&amp;"]={"),IF(AND(ISBLANK(B175),ISBLANK(D175),ISBLANK(N175),ISBLANK(O175),OR(ISBLANK(B174)=FALSE,ISBLANK(D174)=FALSE,ISBLANK(N174)=FALSE,ISBLANK(O174)=FALSE)),"},},}",IF(ISBLANK(D175),"","{szContent="""&amp;D175&amp;""","&amp;IF(C175&lt;&gt;"","szTarget="""&amp;C175&amp;""",","")&amp;IF(E175&lt;&gt;"","szNote="""&amp;E175&amp;""",","")&amp;IF(M175&lt;&gt;"","col={"&amp;M175&amp;"},","")&amp;IF(N175&gt;0,"bSearch=true,","")&amp;IF(O175&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P175&gt;0,"szVoice="""&amp;P175&amp;""",","")&amp;IF(Q175&gt;0,"bTeamChannel=true,","")&amp;IF(R175&gt;0,"bWhisperChannel=true,","")&amp;IF(S175&gt;0,"bCenterAlarm=true,","")&amp;IF(T175&gt;0,"bScreenHead=true,","")&amp;IF(U175&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W175&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W175:AAH175)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W175" t="s">
@@ -38825,7 +38825,7 @@
         <v>1</v>
       </c>
       <c r="V176" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B176)=FALSE,IF(ISBLANK(B175),"},["&amp;B176&amp;"]={","["&amp;B176&amp;"]={"),IF(AND(ISBLANK(B176),ISBLANK(D176),ISBLANK(N176),ISBLANK(O176),OR(ISBLANK(B175)=FALSE,ISBLANK(D175)=FALSE,ISBLANK(N175)=FALSE,ISBLANK(O175)=FALSE)),"},},}",IF(ISBLANK(D176),"","{szContent="""&amp;D176&amp;""","&amp;IF(C176&lt;&gt;"","szTarget="""&amp;C176&amp;""",","")&amp;IF(E176&lt;&gt;"","szNote="""&amp;E176&amp;""",","")&amp;IF(M176&lt;&gt;"","col={"&amp;M176&amp;"},","")&amp;IF(N176&gt;0,"bSearch=true,","")&amp;IF(O176&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P176&gt;0,"szVoice="""&amp;P176&amp;""",","")&amp;IF(Q176&gt;0,"bTeamChannel=true,","")&amp;IF(R176&gt;0,"bWhisperChannel=true,","")&amp;IF(S176&gt;0,"bCenterAlarm=true,","")&amp;IF(T176&gt;0,"bScreenHead=true,","")&amp;IF(U176&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W176&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W176:AAH176)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W176" t="s">
@@ -38840,7 +38840,7 @@
     </row>
     <row r="177" spans="22:22">
       <c r="V177" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B177)=FALSE,IF(ISBLANK(B176),"},["&amp;B177&amp;"]={","["&amp;B177&amp;"]={"),IF(AND(ISBLANK(B177),ISBLANK(D177),ISBLANK(N177),ISBLANK(O177),OR(ISBLANK(B176)=FALSE,ISBLANK(D176)=FALSE,ISBLANK(N176)=FALSE,ISBLANK(O176)=FALSE)),"},},}",IF(ISBLANK(D177),"","{szContent="""&amp;D177&amp;""","&amp;IF(C177&lt;&gt;"","szTarget="""&amp;C177&amp;""",","")&amp;IF(E177&lt;&gt;"","szNote="""&amp;E177&amp;""",","")&amp;IF(M177&lt;&gt;"","col={"&amp;M177&amp;"},","")&amp;IF(N177&gt;0,"bSearch=true,","")&amp;IF(O177&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P177&gt;0,"szVoice="""&amp;P177&amp;""",","")&amp;IF(Q177&gt;0,"bTeamChannel=true,","")&amp;IF(R177&gt;0,"bWhisperChannel=true,","")&amp;IF(S177&gt;0,"bCenterAlarm=true,","")&amp;IF(T177&gt;0,"bScreenHead=true,","")&amp;IF(U177&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W177&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W177:AAH177)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5688" uniqueCount="2611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5689" uniqueCount="2612">
   <si>
     <t>__meta = {</t>
   </si>
@@ -6376,27 +6376,27 @@
     <t>{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},</t>
   </si>
   <si>
+    <t>{nClass=14,nIcon=7674,nFrame=-1,nTime="2700,{$5}{$4}{$6}·{$8}{$7}{$9};4500,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=7676,nFrame=-1,nTime="1800,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},</t>
+  </si>
+  <si>
     <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},</t>
   </si>
   <si>
     <t>{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},</t>
   </si>
   <si>
-    <t>{nClass=14,nIcon=7674,nFrame=-1,nTime="2700.1,{$5}{$4}{$6}·{$8}{$7}{$9};4500.1,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=7676,nFrame=-1,nTime="1800.14,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},</t>
-  </si>
-  <si>
     <t>五分钟内只可拾取一次对立阵营首领仓皇撤退留下的物资。</t>
   </si>
   <si>
@@ -7133,6 +7133,9 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},</t>
   </si>
   <si>
     <t>{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},</t>
@@ -9246,7 +9249,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1791119599000,</v>
+        <v>nTimeStamp = 1791637824000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -10989,10 +10992,10 @@
         <v>1775</v>
       </c>
       <c r="B3" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C3" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11000,10 +11003,10 @@
         <v>1781</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C4" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11011,10 +11014,10 @@
         <v>1790</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11022,10 +11025,10 @@
         <v>1794</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11033,10 +11036,10 @@
         <v>1800</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11044,10 +11047,10 @@
         <v>1804</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -11055,10 +11058,10 @@
         <v>1815</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11066,10 +11069,10 @@
         <v>1819</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11077,10 +11080,10 @@
         <v>1825</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11088,10 +11091,10 @@
         <v>1829</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11099,10 +11102,10 @@
         <v>1833</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11110,10 +11113,10 @@
         <v>1837</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11121,10 +11124,10 @@
         <v>1843</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11132,10 +11135,10 @@
         <v>1847</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11143,10 +11146,10 @@
         <v>1851</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11154,10 +11157,10 @@
         <v>1855</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11165,10 +11168,10 @@
         <v>1861</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11176,10 +11179,10 @@
         <v>1865</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11187,10 +11190,10 @@
         <v>1871</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11198,10 +11201,10 @@
         <v>1875</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11209,10 +11212,10 @@
         <v>1879</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11220,10 +11223,10 @@
         <v>1883</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11231,10 +11234,10 @@
         <v>1893</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11242,10 +11245,10 @@
         <v>1897</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11253,10 +11256,10 @@
         <v>1901</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11264,10 +11267,10 @@
         <v>1905</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11275,10 +11278,10 @@
         <v>1917</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11286,10 +11289,10 @@
         <v>1921</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
     </row>
   </sheetData>
@@ -34596,7 +34599,7 @@
       </c>
       <c r="V47" t="str">
         <f t="shared" si="11"/>
-        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},{nClass=14,nIcon=7674,nFrame=-1,nTime="2700.1,{$5}{$4}{$6}·{$8}{$7}{$9};4500.1,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},{nClass=14,nIcon=7676,nFrame=-1,nTime="1800.14,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},},},</v>
+        <v>{szContent="^本场攻防“(.-)”“(.-)·(.-)”已结束，(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分；(.-)存活首领及拥有据点数为(%d-)，获得(%d-)分。请再接再厉！",szTarget="%",szNote="{$2}·{$3}·[{$4}{$5}·{$6}]:[{$7}{$8}·{$9}]",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=2401,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=14,nIcon=2397,nFrame=-1,nTime=-1,szName="破阵点将·一",nRefresh=2,key="破阵点将·一",},{nClass=14,nIcon=2398,nFrame=-1,nTime=-1,szName="破阵点将·二",nRefresh=2,key="破阵点将·二",},{nClass=14,nIcon=2396,nFrame=-1,nTime=-2,szName="{$2}·{$3}",key="{$2}·{$3}",},{nClass=14,nIcon=7674,nFrame=-1,nTime="2700,{$5}{$4}{$6}·{$8}{$7}{$9};4500,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·一·常驻",},{nClass=14,nIcon=7676,nFrame=-1,nTime="1800,{$5}{$4}{$6}·{$8}{$7}{$9}",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=0,key="破阵点将·二·常驻",},{nClass=14,nIcon=13,szName="破阵点将·{$3}",nTime=-2,nRefresh=99999,key="破阵点将·{$3}·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·一·常驻",},{nClass=14,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,key="破阵点将·二·常驻",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;840,阶段·物资车2·出发剩余;850,阶段·物资车2·正在出发;900,阶段·首领出战·助战剩余;905,阶段·首领出战·助战结束;2695,阶段·破阵点将2·结算剩余;2705,阶段·破阵点将2·正在结算;2710,阶段·物资车3·正在出发;4500,阶段·本场攻防·结束剩余;4505,阶段·本场攻防·正在结算;4510,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·一",},{nClass=14,nIcon=2401,nFrame=-1,nTime="60,{$4}{$5}·{$6}分·{$7}{$8}·{$9}分;1800,阶段·本场攻防·结束剩余;1805,阶段·本场攻防·正在结算;1810,阶段·本场攻防·已经结束",szName="{$4}{$5}·{$6}分·{$7}{$8}·{$9}分",nRefresh=1,key="破阵点将·二",},},},</v>
       </c>
       <c r="W47" t="s">
         <v>2101</v>
@@ -39362,7 +39365,7 @@
       </c>
       <c r="T15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},},},</v>
+        <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},{nClass=20,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},},},</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>2356</v>
@@ -39372,6 +39375,9 @@
       </c>
       <c r="W15" t="s">
         <v>2358</v>
+      </c>
+      <c r="X15" t="s">
+        <v>2359</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -39388,7 +39394,7 @@
     </row>
     <row r="17" spans="1:26">
       <c r="C17" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="D17" t="s">
         <v>2355</v>
@@ -39398,19 +39404,19 @@
         <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U17" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="V17" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="W17" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="X17" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="Y17" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="Z17" s="5" t="s">
         <v>2357</v>
@@ -39418,10 +39424,10 @@
     </row>
     <row r="18" customFormat="1" spans="1:26">
       <c r="C18" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="D18" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="K18" t="s">
         <v>2002</v>
@@ -39434,24 +39440,24 @@
         <v>{szContent="伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U18" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="V18" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="W18" s="5" t="s">
         <v>2356</v>
       </c>
       <c r="X18" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="19" spans="1:26">
       <c r="C19" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="D19" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="K19" t="s">
         <v>2002</v>
@@ -39464,19 +39470,19 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="V19" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="W19" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="X19" s="5" t="s">
         <v>2356</v>
       </c>
       <c r="Y19" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -39493,7 +39499,7 @@
     </row>
     <row r="21" spans="1:26">
       <c r="C21" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="D21" t="s">
         <v>2355</v>
@@ -39503,19 +39509,19 @@
         <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U21" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="V21" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="W21" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="X21" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="Y21" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="Z21" s="5" t="s">
         <v>2357</v>
@@ -39523,10 +39529,10 @@
     </row>
     <row r="22" customFormat="1" spans="1:26">
       <c r="C22" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="D22" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="K22" t="s">
         <v>2002</v>
@@ -39539,24 +39545,24 @@
         <v>{szContent="韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U22" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="V22" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="W22" s="5" t="s">
         <v>2356</v>
       </c>
       <c r="X22" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="C23" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="D23" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="K23" t="s">
         <v>2002</v>
@@ -39569,24 +39575,24 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="V23" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="W23" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="X23" s="5" t="s">
         <v>2356</v>
       </c>
       <c r="Y23" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:26">
       <c r="A24" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="B24">
         <v>-1</v>
@@ -39598,7 +39604,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:26">
       <c r="C25" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D25"/>
       <c r="K25" t="s">
@@ -39609,18 +39615,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U25" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="V25" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="W25" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="C26" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="K26" t="s">
         <v>1994</v>
@@ -39630,18 +39636,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U26" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="V26" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="W26" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="C27" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="K27" t="s">
         <v>1998</v>
@@ -39651,12 +39657,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U27" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="C28" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="K28" t="s">
         <v>1998</v>
@@ -39666,12 +39672,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U28" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="C29" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="K29" t="s">
         <v>1994</v>
@@ -39681,12 +39687,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U29" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="30" spans="1:26">
       <c r="C30" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="K30" t="s">
         <v>1994</v>
@@ -39696,12 +39702,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U30" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="31" spans="1:26">
       <c r="C31" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="K31" t="s">
         <v>2002</v>
@@ -39711,12 +39717,12 @@
         <v>{szContent="据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="U31" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="32" spans="1:26">
       <c r="C32" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="K32" t="s">
         <v>2002</v>
@@ -39726,15 +39732,15 @@
         <v>{szContent="为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},},},</v>
       </c>
       <c r="U32" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="C33" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="D33" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="K33" t="s">
         <v>2002</v>
@@ -39747,7 +39753,7 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U33" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -39764,10 +39770,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:22">
       <c r="C35" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="D35" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="K35" t="s">
         <v>2002</v>
@@ -39777,15 +39783,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U35" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:22">
       <c r="C36" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="D36" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="K36" t="s">
         <v>2002</v>
@@ -39795,15 +39801,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U36" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:22">
       <c r="C37" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="D37" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="K37" t="s">
         <v>2002</v>
@@ -39813,18 +39819,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U37" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="V37" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:22">
       <c r="C38" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D38" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="K38" t="s">
         <v>2002</v>
@@ -39834,15 +39840,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U38" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:22">
       <c r="C39" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="D39" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="K39" t="s">
         <v>2002</v>
@@ -39852,18 +39858,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U39" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="V39" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:22">
       <c r="C40" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="D40" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="K40" t="s">
         <v>2002</v>
@@ -39873,10 +39879,10 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U40" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:22">
@@ -39900,10 +39906,10 @@
     </row>
     <row r="42" customFormat="1" spans="1:22">
       <c r="C42" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D42" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="K42" t="s">
         <v>2002</v>
@@ -39913,16 +39919,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U42" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="V42" s="7"/>
     </row>
     <row r="43" customFormat="1" spans="1:22">
       <c r="C43" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D43" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="K43" t="s">
         <v>1998</v>
@@ -39932,15 +39938,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U43" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:22">
       <c r="C44" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D44" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="K44" t="s">
         <v>1998</v>
@@ -39950,15 +39956,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U44" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:22">
       <c r="C45" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="D45" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="K45" t="s">
         <v>1998</v>
@@ -39968,15 +39974,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U45" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:22">
       <c r="C46" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="D46" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="K46" t="s">
         <v>1994</v>
@@ -39986,15 +39992,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U46" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:22">
       <c r="C47" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="D47" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="K47" t="s">
         <v>1994</v>
@@ -40004,15 +40010,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U47" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:22">
       <c r="C48" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="D48" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="K48" t="s">
         <v>1994</v>
@@ -40022,15 +40028,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U48" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="49" spans="1:26">
       <c r="C49" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D49" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="K49" t="s">
         <v>2002</v>
@@ -40043,7 +40049,7 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U49" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="50" spans="1:26">
@@ -40084,10 +40090,10 @@
     </row>
     <row r="52" spans="1:26">
       <c r="C52" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D52" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="K52" t="s">
         <v>2002</v>
@@ -40100,30 +40106,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U52" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V52" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="W52" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="X52" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="Y52" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z52" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="53" spans="1:26">
       <c r="C53" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D53" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="K53" t="s">
         <v>2002</v>
@@ -40136,19 +40142,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U53" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="V53" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="W53" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="X53" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="Y53" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" spans="1:26">
@@ -40165,10 +40171,10 @@
     </row>
     <row r="55" spans="1:26">
       <c r="C55" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="D55" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="K55" t="s">
         <v>2002</v>
@@ -40178,15 +40184,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U55" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="D56" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="K56" t="s">
         <v>2002</v>
@@ -40196,12 +40202,12 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:26">
       <c r="C57" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="D57" t="s">
         <v>2195</v>
@@ -40214,15 +40220,15 @@
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:26">
       <c r="C58" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="D58" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="K58" t="s">
         <v>2002</v>
@@ -40232,18 +40238,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U58" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="V58" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="D59" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="K59" t="s">
         <v>2002</v>
@@ -40253,18 +40259,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="V59" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:26">
       <c r="C60" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="D60" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="K60" t="s">
         <v>2002</v>
@@ -40274,24 +40280,24 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="V60" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="W60" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:26">
       <c r="C61" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D61" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="K61" t="s">
         <v>1998</v>
@@ -40301,15 +40307,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U61" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:26">
       <c r="C62" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D62" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="K62" t="s">
         <v>1998</v>
@@ -40319,15 +40325,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U62" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
       <c r="C63" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="D63" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="K63" t="s">
         <v>1998</v>
@@ -40337,15 +40343,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U63" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:26">
       <c r="C64" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="D64" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="K64" t="s">
         <v>1994</v>
@@ -40355,15 +40361,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U64" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
       <c r="C65" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="D65" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="K65" t="s">
         <v>1994</v>
@@ -40373,15 +40379,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U65" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="D66" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="K66" t="s">
         <v>1994</v>
@@ -40391,15 +40397,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
       <c r="C67" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D67" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="K67" t="s">
         <v>2002</v>
@@ -40412,7 +40418,7 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U67" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:26">
@@ -40436,10 +40442,10 @@
     </row>
     <row r="69" spans="1:26">
       <c r="C69" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D69" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="K69" t="s">
         <v>2002</v>
@@ -40449,7 +40455,7 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="V69" s="4" t="s">
         <v>2322</v>
@@ -40460,10 +40466,10 @@
     </row>
     <row r="70" spans="1:26">
       <c r="C70" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="D70" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="K70" t="s">
         <v>2002</v>
@@ -40514,10 +40520,10 @@
     </row>
     <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D73" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="K73" t="s">
         <v>2002</v>
@@ -40530,30 +40536,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V73" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="W73" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="X73" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="Y73" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z73" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D74" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="K74" t="s">
         <v>2002</v>
@@ -40566,19 +40572,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="V74" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="W74" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="X74" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="Y74" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:26">
@@ -40595,10 +40601,10 @@
     </row>
     <row r="76" customFormat="1" spans="1:26">
       <c r="C76" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D76" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="K76" t="s">
         <v>2002</v>
@@ -40611,19 +40617,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U76" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="V76" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="W76" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="X76" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="Y76" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
@@ -40640,10 +40646,10 @@
     </row>
     <row r="78" customFormat="1" spans="1:26">
       <c r="C78" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="D78" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="K78" t="s">
         <v>2002</v>
@@ -40653,15 +40659,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U78" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:26">
       <c r="C79" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="D79" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="K79" t="s">
         <v>2002</v>
@@ -40671,15 +40677,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U79" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:26">
       <c r="C80" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="D80" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="K80" t="s">
         <v>2002</v>
@@ -40689,18 +40695,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U80" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="V80" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="3:26">
       <c r="C81" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D81" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="K81" t="s">
         <v>2002</v>
@@ -40710,15 +40716,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U81" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="3:26">
       <c r="C82" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="D82" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="K82" t="s">
         <v>2002</v>
@@ -40728,18 +40734,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U82" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="V82" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="3:26">
       <c r="C83" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="D83" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="K83" t="s">
         <v>2002</v>
@@ -40749,18 +40755,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U83" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="V83" s="3" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="3:26">
       <c r="C84" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D84" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="K84" t="s">
         <v>1998</v>
@@ -40770,15 +40776,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U84" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="3:26">
       <c r="C85" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D85" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="K85" t="s">
         <v>1998</v>
@@ -40788,15 +40794,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U85" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="3:26">
       <c r="C86" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="D86" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="K86" t="s">
         <v>1998</v>
@@ -40806,15 +40812,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U86" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="3:26">
       <c r="C87" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="D87" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="K87" t="s">
         <v>1994</v>
@@ -40824,15 +40830,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U87" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="3:26">
       <c r="C88" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="D88" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="K88" t="s">
         <v>1994</v>
@@ -40842,15 +40848,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U88" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="3:26">
       <c r="C89" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="D89" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="K89" t="s">
         <v>1994</v>
@@ -40860,15 +40866,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="3:26">
       <c r="C90" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D90" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="K90" t="s">
         <v>2002</v>
@@ -40881,7 +40887,7 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U90" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="3:26">
@@ -40905,10 +40911,10 @@
     </row>
     <row r="92" customFormat="1" spans="3:26">
       <c r="C92" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D92" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="K92" t="s">
         <v>2002</v>
@@ -40918,7 +40924,7 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U92" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="V92" s="7"/>
     </row>
@@ -40960,10 +40966,10 @@
     </row>
     <row r="95" customFormat="1" spans="3:26">
       <c r="C95" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D95" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="K95" t="s">
         <v>2002</v>
@@ -40976,30 +40982,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U95" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V95" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="W95" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="X95" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="Y95" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z95" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="3:26">
       <c r="C96" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D96" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="K96" t="s">
         <v>2002</v>
@@ -41012,24 +41018,24 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U96" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="V96" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="W96" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="X96" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="Y96" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:22">
       <c r="A97" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="B97">
         <v>-3</v>
@@ -41041,7 +41047,7 @@
     </row>
     <row r="98" customFormat="1" spans="1:22">
       <c r="C98" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="K98" t="s">
         <v>1994</v>
@@ -41051,12 +41057,12 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U98" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:22">
       <c r="C99" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="K99" t="s">
         <v>1998</v>
@@ -41066,7 +41072,7 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U99" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:22">
@@ -41102,10 +41108,10 @@
     </row>
     <row r="102" customFormat="1" spans="1:22">
       <c r="C102" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D102" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="K102" t="s">
         <v>2002</v>
@@ -41115,16 +41121,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U102" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="V102" s="7"/>
     </row>
     <row r="103" customFormat="1" spans="1:22">
       <c r="C103" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="D103" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="K103" t="s">
         <v>2002</v>
@@ -41134,18 +41140,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U103" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="V103" s="3" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:22">
       <c r="C104" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D104" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="K104" t="s">
         <v>1998</v>
@@ -41155,15 +41161,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U104" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:22">
       <c r="C105" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D105" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="K105" t="s">
         <v>1998</v>
@@ -41173,15 +41179,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U105" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:22">
       <c r="C106" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="D106" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="K106" t="s">
         <v>1998</v>
@@ -41191,15 +41197,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U106" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:22">
       <c r="C107" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="D107" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="K107" t="s">
         <v>1994</v>
@@ -41209,15 +41215,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U107" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:22">
       <c r="C108" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="D108" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="K108" t="s">
         <v>1994</v>
@@ -41227,15 +41233,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U108" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:22">
       <c r="C109" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="D109" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="K109" t="s">
         <v>1994</v>
@@ -41245,15 +41251,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U109" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:22">
       <c r="C110" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D110" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="K110" t="s">
         <v>2002</v>
@@ -41266,7 +41272,7 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U110" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:22">
@@ -41307,10 +41313,10 @@
     </row>
     <row r="113" customFormat="1" spans="1:34">
       <c r="C113" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D113" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="K113" t="s">
         <v>2002</v>
@@ -41323,30 +41329,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U113" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V113" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="W113" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="X113" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="Y113" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z113" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:34">
       <c r="C114" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D114" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="K114" t="s">
         <v>2002</v>
@@ -41359,19 +41365,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U114" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="V114" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="W114" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="X114" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="Y114" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:34">
@@ -41404,18 +41410,18 @@
         <v>2328</v>
       </c>
       <c r="X115" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="Y115" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:34">
       <c r="C116" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="D116" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="K116" t="s">
         <v>2002</v>
@@ -41425,15 +41431,15 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U116" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:34">
       <c r="C117" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="D117" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="K117" t="s">
         <v>2002</v>
@@ -41443,7 +41449,7 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U117" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:34">
@@ -41460,13 +41466,13 @@
     </row>
     <row r="119" customFormat="1" spans="1:34">
       <c r="C119" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D119" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G119" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="K119" t="s">
         <v>2002</v>
@@ -41479,7 +41485,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U119" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V119" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G119&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41490,19 +41496,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X119" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="Y119" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="Z119" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AA119" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AB119" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AC119" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G119&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G119&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41515,10 +41521,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:34">
       <c r="C120" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D120" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K120" t="s">
         <v>2002</v>
@@ -41531,16 +41537,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U120" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="V120" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="W120" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="X120" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="121" spans="1:34">
@@ -41557,13 +41563,13 @@
     </row>
     <row r="122" customFormat="1" spans="1:34">
       <c r="C122" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D122" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G122" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K122" t="s">
         <v>2002</v>
@@ -41576,7 +41582,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U122" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V122" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G122&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41587,19 +41593,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
       </c>
       <c r="X122" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="Y122" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="Z122" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AA122" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AB122" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AC122" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G122&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G122&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41612,10 +41618,10 @@
     </row>
     <row r="123" spans="1:34">
       <c r="C123" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D123" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K123" t="s">
         <v>2002</v>
@@ -41628,16 +41634,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U123" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="V123" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="W123" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="X123" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -41654,16 +41660,16 @@
     </row>
     <row r="125" customFormat="1" spans="1:34">
       <c r="C125" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D125" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G125" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="H125" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="K125" t="s">
         <v>2002</v>
@@ -41676,7 +41682,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U125" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V125" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G125&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41695,19 +41701,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z125" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA125" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB125" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC125" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD125" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE125" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G125&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G125&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41728,10 +41734,10 @@
     </row>
     <row r="126" spans="1:34">
       <c r="C126" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D126" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K126" t="s">
         <v>2002</v>
@@ -41744,22 +41750,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U126" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="V126" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="W126" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X126" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y126" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="Z126" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="127" spans="1:34">
@@ -41776,16 +41782,16 @@
     </row>
     <row r="128" customFormat="1" spans="1:34">
       <c r="C128" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D128" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G128" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="H128" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="K128" t="s">
         <v>2002</v>
@@ -41798,7 +41804,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U128" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V128" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G128&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41817,19 +41823,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z128" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA128" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB128" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC128" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD128" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE128" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G128&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G128&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41850,10 +41856,10 @@
     </row>
     <row r="129" spans="1:34">
       <c r="C129" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D129" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K129" t="s">
         <v>2002</v>
@@ -41866,22 +41872,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U129" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="V129" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="W129" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X129" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y129" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="Z129" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="130" spans="1:34">
@@ -41898,16 +41904,16 @@
     </row>
     <row r="131" customFormat="1" spans="1:34">
       <c r="C131" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D131" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G131" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="H131" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="K131" t="s">
         <v>2002</v>
@@ -41916,11 +41922,11 @@
         <v>1</v>
       </c>
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T168" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="T131:T162" si="4">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(C131),ISBLANK(L131),ISBLANK(M131),OR(ISBLANK(B130)=FALSE,ISBLANK(C130)=FALSE,ISBLANK(L130)=FALSE,ISBLANK(M130)=FALSE)),"},},}",IF(ISBLANK(C131),"","{szContent="""&amp;C131&amp;""","&amp;IF(D131&lt;&gt;"","szNote="""&amp;D131&amp;""",","")&amp;IF(K131&lt;&gt;"","col={"&amp;K131&amp;"},","")&amp;IF(L131&gt;0,"bSearch=true,","")&amp;IF(M131&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N131&gt;0,"szVoice="""&amp;N131&amp;""",","")&amp;IF(O131&gt;0,"bTeamChannel=true,","")&amp;IF(P131&gt;0,"bWhisperChannel=true,","")&amp;IF(Q131&gt;0,"bCenterAlarm=true,","")&amp;IF(R131&gt;0,"bScreenHead=true,","")&amp;IF(S131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U131:AAF131)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V131" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G131&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41939,19 +41945,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z131" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA131" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB131" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC131" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD131" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE131" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G131&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G131&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41972,10 +41978,10 @@
     </row>
     <row r="132" spans="1:34">
       <c r="C132" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D132" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K132" t="s">
         <v>2002</v>
@@ -41988,22 +41994,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U132" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="V132" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="W132" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X132" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y132" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="Z132" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="133" spans="1:34">
@@ -42020,16 +42026,16 @@
     </row>
     <row r="134" customFormat="1" spans="1:34">
       <c r="C134" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D134" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G134" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="H134" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="K134" t="s">
         <v>2002</v>
@@ -42042,7 +42048,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U134" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V134" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G134&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42061,19 +42067,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z134" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA134" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB134" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC134" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD134" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE134" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G134&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G134&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42094,10 +42100,10 @@
     </row>
     <row r="135" spans="1:34">
       <c r="C135" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D135" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K135" t="s">
         <v>2002</v>
@@ -42110,22 +42116,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U135" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="V135" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="W135" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X135" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y135" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="Z135" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -42142,16 +42148,16 @@
     </row>
     <row r="137" customFormat="1" spans="1:34">
       <c r="C137" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D137" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G137" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="H137" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="K137" t="s">
         <v>2002</v>
@@ -42164,7 +42170,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U137" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V137" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G137&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42183,19 +42189,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z137" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA137" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB137" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC137" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD137" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE137" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G137&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G137&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42216,10 +42222,10 @@
     </row>
     <row r="138" spans="1:34">
       <c r="C138" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D138" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K138" t="s">
         <v>2002</v>
@@ -42232,22 +42238,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U138" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="V138" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="W138" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X138" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y138" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="Z138" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="139" spans="1:34">
@@ -42264,16 +42270,16 @@
     </row>
     <row r="140" customFormat="1" spans="1:34">
       <c r="C140" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D140" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G140" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="H140" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="K140" t="s">
         <v>2002</v>
@@ -42286,7 +42292,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U140" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V140" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G140&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42305,19 +42311,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z140" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA140" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB140" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC140" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD140" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE140" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G140&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G140&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42338,10 +42344,10 @@
     </row>
     <row r="141" spans="1:34">
       <c r="C141" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D141" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K141" t="s">
         <v>2002</v>
@@ -42354,22 +42360,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U141" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="V141" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="W141" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X141" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y141" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="Z141" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -42386,16 +42392,16 @@
     </row>
     <row r="143" customFormat="1" spans="1:34">
       <c r="C143" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D143" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G143" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="H143" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="K143" t="s">
         <v>2002</v>
@@ -42408,7 +42414,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U143" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V143" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G143&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42427,19 +42433,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z143" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA143" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB143" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC143" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD143" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE143" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G143&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G143&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42460,10 +42466,10 @@
     </row>
     <row r="144" spans="1:34">
       <c r="C144" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D144" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K144" t="s">
         <v>2002</v>
@@ -42476,22 +42482,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U144" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="V144" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="W144" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X144" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y144" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="Z144" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="145" spans="1:34">
@@ -42508,16 +42514,16 @@
     </row>
     <row r="146" customFormat="1" spans="1:34">
       <c r="C146" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D146" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G146" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="H146" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="K146" t="s">
         <v>2002</v>
@@ -42530,7 +42536,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U146" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V146" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G146&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42549,19 +42555,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z146" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA146" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB146" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC146" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD146" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE146" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G146&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G146&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42582,10 +42588,10 @@
     </row>
     <row r="147" spans="1:34">
       <c r="C147" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D147" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K147" t="s">
         <v>2002</v>
@@ -42598,22 +42604,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U147" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="V147" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="W147" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X147" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y147" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="Z147" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -42630,16 +42636,16 @@
     </row>
     <row r="149" customFormat="1" spans="1:34">
       <c r="C149" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D149" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G149" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="H149" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="K149" t="s">
         <v>2002</v>
@@ -42652,7 +42658,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U149" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V149" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G149&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42671,19 +42677,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z149" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA149" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB149" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC149" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD149" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE149" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G149&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G149&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42704,10 +42710,10 @@
     </row>
     <row r="150" spans="1:34">
       <c r="C150" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D150" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K150" t="s">
         <v>2002</v>
@@ -42720,22 +42726,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U150" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="V150" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="W150" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X150" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y150" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="Z150" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="151" spans="1:34">
@@ -42752,16 +42758,16 @@
     </row>
     <row r="152" customFormat="1" spans="1:34">
       <c r="C152" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D152" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G152" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="H152" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="K152" t="s">
         <v>2002</v>
@@ -42774,7 +42780,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U152" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V152" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G152&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42793,19 +42799,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z152" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA152" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB152" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC152" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD152" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE152" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G152&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G152&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42826,10 +42832,10 @@
     </row>
     <row r="153" spans="1:34">
       <c r="C153" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D153" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K153" t="s">
         <v>2002</v>
@@ -42842,22 +42848,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U153" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="V153" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="W153" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X153" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y153" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="Z153" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -42874,16 +42880,16 @@
     </row>
     <row r="155" customFormat="1" spans="1:34">
       <c r="C155" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D155" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G155" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="H155" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="K155" t="s">
         <v>2002</v>
@@ -42896,7 +42902,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U155" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V155" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G155&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42915,19 +42921,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z155" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA155" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB155" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC155" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD155" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE155" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G155&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G155&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42948,10 +42954,10 @@
     </row>
     <row r="156" spans="1:34">
       <c r="C156" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D156" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K156" t="s">
         <v>2002</v>
@@ -42964,22 +42970,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U156" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="V156" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="W156" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X156" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y156" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="Z156" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="157" spans="1:34">
@@ -42996,16 +43002,16 @@
     </row>
     <row r="158" customFormat="1" spans="1:34">
       <c r="C158" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D158" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G158" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="H158" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="K158" t="s">
         <v>2002</v>
@@ -43018,7 +43024,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U158" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V158" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G158&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43037,19 +43043,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
       </c>
       <c r="Z158" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="AA158" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="AB158" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="AC158" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="AD158" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="AE158" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G158&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G158&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43070,10 +43076,10 @@
     </row>
     <row r="159" spans="1:34">
       <c r="C159" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D159" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K159" t="s">
         <v>2002</v>
@@ -43086,22 +43092,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U159" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="V159" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="W159" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X159" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y159" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="Z159" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="160" spans="1:34">
@@ -43118,16 +43124,16 @@
     </row>
     <row r="161" spans="1:26">
       <c r="C161" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="D161" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G161" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="H161" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="K161" t="s">
         <v>2002</v>
@@ -43140,30 +43146,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U161" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V161" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="W161" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="X161" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="Y161" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z161" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="162" spans="1:26">
       <c r="C162" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D162" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K162" t="s">
         <v>2002</v>
@@ -43176,30 +43182,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U162" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="V162" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="W162" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X162" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y162" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="Z162" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:26">
       <c r="C163" s="5" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D163" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="K163" t="s">
         <v>2002</v>
@@ -43208,23 +43214,23 @@
         <v>1</v>
       </c>
       <c r="T163" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(C163),ISBLANK(L163),ISBLANK(M163),OR(ISBLANK(B162)=FALSE,ISBLANK(C162)=FALSE,ISBLANK(L162)=FALSE,ISBLANK(M162)=FALSE)),"},},}",IF(ISBLANK(C163),"","{szContent="""&amp;C163&amp;""","&amp;IF(D163&lt;&gt;"","szNote="""&amp;D163&amp;""",","")&amp;IF(K163&lt;&gt;"","col={"&amp;K163&amp;"},","")&amp;IF(L163&gt;0,"bSearch=true,","")&amp;IF(M163&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N163&gt;0,"szVoice="""&amp;N163&amp;""",","")&amp;IF(O163&gt;0,"bTeamChannel=true,","")&amp;IF(P163&gt;0,"bWhisperChannel=true,","")&amp;IF(Q163&gt;0,"bCenterAlarm=true,","")&amp;IF(R163&gt;0,"bScreenHead=true,","")&amp;IF(S163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U163:AAF163)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U163" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="V163" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="W163" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="X163" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="Y163" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="164" spans="1:26">
@@ -43235,22 +43241,22 @@
         <v>656</v>
       </c>
       <c r="T164" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(C164),ISBLANK(L164),ISBLANK(M164),OR(ISBLANK(B163)=FALSE,ISBLANK(C163)=FALSE,ISBLANK(L163)=FALSE,ISBLANK(M163)=FALSE)),"},},}",IF(ISBLANK(C164),"","{szContent="""&amp;C164&amp;""","&amp;IF(D164&lt;&gt;"","szNote="""&amp;D164&amp;""",","")&amp;IF(K164&lt;&gt;"","col={"&amp;K164&amp;"},","")&amp;IF(L164&gt;0,"bSearch=true,","")&amp;IF(M164&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N164&gt;0,"szVoice="""&amp;N164&amp;""",","")&amp;IF(O164&gt;0,"bTeamChannel=true,","")&amp;IF(P164&gt;0,"bWhisperChannel=true,","")&amp;IF(Q164&gt;0,"bCenterAlarm=true,","")&amp;IF(R164&gt;0,"bScreenHead=true,","")&amp;IF(S164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U164:AAF164)&amp;"},","")&amp;"},")))</f>
         <v>},[656]={</v>
       </c>
     </row>
     <row r="165" spans="1:26">
       <c r="C165" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="D165" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="G165" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="H165" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="K165" t="s">
         <v>2002</v>
@@ -43259,34 +43265,34 @@
         <v>1</v>
       </c>
       <c r="T165" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(C165),ISBLANK(L165),ISBLANK(M165),OR(ISBLANK(B164)=FALSE,ISBLANK(C164)=FALSE,ISBLANK(L164)=FALSE,ISBLANK(M164)=FALSE)),"},},}",IF(ISBLANK(C165),"","{szContent="""&amp;C165&amp;""","&amp;IF(D165&lt;&gt;"","szNote="""&amp;D165&amp;""",","")&amp;IF(K165&lt;&gt;"","col={"&amp;K165&amp;"},","")&amp;IF(L165&gt;0,"bSearch=true,","")&amp;IF(M165&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N165&gt;0,"szVoice="""&amp;N165&amp;""",","")&amp;IF(O165&gt;0,"bTeamChannel=true,","")&amp;IF(P165&gt;0,"bWhisperChannel=true,","")&amp;IF(Q165&gt;0,"bCenterAlarm=true,","")&amp;IF(R165&gt;0,"bScreenHead=true,","")&amp;IF(S165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U165:AAF165)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U165" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="V165" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="W165" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="X165" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="Y165" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z165" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="166" spans="1:26">
       <c r="C166" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="D166" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K166" t="s">
         <v>2002</v>
@@ -43295,34 +43301,34 @@
         <v>1</v>
       </c>
       <c r="T166" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(C166),ISBLANK(L166),ISBLANK(M166),OR(ISBLANK(B165)=FALSE,ISBLANK(C165)=FALSE,ISBLANK(L165)=FALSE,ISBLANK(M165)=FALSE)),"},},}",IF(ISBLANK(C166),"","{szContent="""&amp;C166&amp;""","&amp;IF(D166&lt;&gt;"","szNote="""&amp;D166&amp;""",","")&amp;IF(K166&lt;&gt;"","col={"&amp;K166&amp;"},","")&amp;IF(L166&gt;0,"bSearch=true,","")&amp;IF(M166&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N166&gt;0,"szVoice="""&amp;N166&amp;""",","")&amp;IF(O166&gt;0,"bTeamChannel=true,","")&amp;IF(P166&gt;0,"bWhisperChannel=true,","")&amp;IF(Q166&gt;0,"bCenterAlarm=true,","")&amp;IF(R166&gt;0,"bScreenHead=true,","")&amp;IF(S166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U166:AAF166)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="V166" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="W166" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="X166" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="Y166" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="Z166" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:26">
       <c r="C167" s="5" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D167" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="K167" t="s">
         <v>2002</v>
@@ -43331,28 +43337,28 @@
         <v>1</v>
       </c>
       <c r="T167" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(C167),ISBLANK(L167),ISBLANK(M167),OR(ISBLANK(B166)=FALSE,ISBLANK(C166)=FALSE,ISBLANK(L166)=FALSE,ISBLANK(M166)=FALSE)),"},},}",IF(ISBLANK(C167),"","{szContent="""&amp;C167&amp;""","&amp;IF(D167&lt;&gt;"","szNote="""&amp;D167&amp;""",","")&amp;IF(K167&lt;&gt;"","col={"&amp;K167&amp;"},","")&amp;IF(L167&gt;0,"bSearch=true,","")&amp;IF(M167&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N167&gt;0,"szVoice="""&amp;N167&amp;""",","")&amp;IF(O167&gt;0,"bTeamChannel=true,","")&amp;IF(P167&gt;0,"bWhisperChannel=true,","")&amp;IF(Q167&gt;0,"bCenterAlarm=true,","")&amp;IF(R167&gt;0,"bScreenHead=true,","")&amp;IF(S167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U167:AAF167)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U167" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="V167" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="W167" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="X167" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="Y167" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="168" spans="1:26">
       <c r="T168" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(C168),ISBLANK(L168),ISBLANK(M168),OR(ISBLANK(B167)=FALSE,ISBLANK(C167)=FALSE,ISBLANK(L167)=FALSE,ISBLANK(M167)=FALSE)),"},},}",IF(ISBLANK(C168),"","{szContent="""&amp;C168&amp;""","&amp;IF(D168&lt;&gt;"","szNote="""&amp;D168&amp;""",","")&amp;IF(K168&lt;&gt;"","col={"&amp;K168&amp;"},","")&amp;IF(L168&gt;0,"bSearch=true,","")&amp;IF(M168&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(N168&gt;0,"szVoice="""&amp;N168&amp;""",","")&amp;IF(O168&gt;0,"bTeamChannel=true,","")&amp;IF(P168&gt;0,"bWhisperChannel=true,","")&amp;IF(Q168&gt;0,"bCenterAlarm=true,","")&amp;IF(R168&gt;0,"bScreenHead=true,","")&amp;IF(S168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(U168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,U168:AAF168)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5689" uniqueCount="2612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5689" uniqueCount="2615">
   <si>
     <t>__meta = {</t>
   </si>
@@ -7039,6 +7039,477 @@
     <t>{$1}·{$2}·{$3}</t>
   </si>
   <si>
+    <t>{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=0,key="大攻防·奇袭场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=0,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,nRefresh=10,key="大攻防·{$1}",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,nRefresh=0,key="大攻防·奇袭场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,nRefresh=0,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},</t>
+  </si>
+  <si>
+    <t>本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n</t>
+  </si>
+  <si>
+    <t>主战场·平局</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n</t>
+  </si>
+  <si>
+    <t>奇袭场·平局</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},</t>
+  </si>
+  <si>
+    <t>本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n</t>
+  </si>
+  <si>
+    <t>浩气盟·本周胜利</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n</t>
+  </si>
+  <si>
+    <t>恶人谷·本周胜利</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n</t>
+  </si>
+  <si>
+    <t>阵营事件·本周战平</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>[团队监控]数据加载成功</t>
+  </si>
+  <si>
+    <t>关闭刷马等计时条</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},</t>
+  </si>
+  <si>
+    <t>{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},</t>
+  </si>
+  <si>
+    <t>你已进入地图【浩气盟】。</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},</t>
+  </si>
+  <si>
+    <t>伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n</t>
+  </si>
+  <si>
+    <t>奇袭攻防·正式开启</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},</t>
+  </si>
+  <si>
+    <t>王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n</t>
+  </si>
+  <si>
+    <t>主场攻防·正式开启</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},</t>
+  </si>
+  <si>
+    <t>你已进入地图【恶人谷】。</t>
+  </si>
+  <si>
+    <t>韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n</t>
+  </si>
+  <si>
+    <t>谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n</t>
+  </si>
+  <si>
+    <t>通用地图</t>
+  </si>
+  <si>
+    <t>阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},</t>
+  </si>
+  <si>
+    <t>阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},</t>
+  </si>
+  <si>
+    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！</t>
+  </si>
+  <si>
+    <t>祭天·{$1}·[{$2}]·{$4}</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},</t>
+  </si>
+  <si>
+    <t>阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n</t>
+  </si>
+  <si>
+    <t>阵营攻防·奇袭场·开启分线</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},</t>
+  </si>
+  <si>
+    <t>阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n</t>
+  </si>
+  <si>
+    <t>阵营攻防·奇袭场·未开分线</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},</t>
+  </si>
+  <si>
+    <t>逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n</t>
+  </si>
+  <si>
+    <t>据点攻防·阴山大草原·开启分线·5分钟</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},</t>
+  </si>
+  <si>
+    <t>前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n</t>
+  </si>
+  <si>
+    <t>据点攻防·阴山大草原</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},</t>
+  </si>
+  <si>
+    <t>阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n</t>
+  </si>
+  <si>
+    <t>据点攻防·阴山大草原·分线·正式开始</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},</t>
+  </si>
+  <si>
+    <t>据点争夺已结束，所有交通已恢复。\n</t>
+  </si>
+  <si>
+    <t>据点攻防·已经结束</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},</t>
+  </si>
+  <si>
+    <t>正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·拍卖掉落</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·浩气盟·险胜</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·浩气盟·大胜</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·浩气盟·完胜</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·恶人谷·险胜</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·恶人谷·大胜</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·恶人谷·完胜</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n</t>
+  </si>
+  <si>
+    <t>据点攻防·平局</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺</t>
+  </si>
+  <si>
+    <t>{$3}·{$1}大旗被夺</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},</t>
+  </si>
+  <si>
+    <t>([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！</t>
+  </si>
+  <si>
+    <t>{$3}·{$1}占领</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},</t>
+  </si>
+  <si>
+    <t>前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},</t>
+  </si>
+  <si>
+    <t>本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n</t>
+  </si>
+  <si>
+    <t>据点攻防·进入前1200名</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},</t>
+  </si>
+  <si>
+    <t>^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫</t>
+  </si>
+  <si>
+    <t>{$1}·{$2}劫粮</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},</t>
+  </si>
+  <si>
+    <t>秘境地图</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},</t>
+  </si>
+  <si>
     <t>{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},</t>
   </si>
   <si>
@@ -7046,468 +7517,6 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},</t>
-  </si>
-  <si>
-    <t>本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n</t>
-  </si>
-  <si>
-    <t>主战场·平局</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},</t>
-  </si>
-  <si>
-    <t>本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n</t>
-  </si>
-  <si>
-    <t>奇袭场·平局</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},</t>
-  </si>
-  <si>
-    <t>本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n</t>
-  </si>
-  <si>
-    <t>浩气盟·本周胜利</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n</t>
-  </si>
-  <si>
-    <t>恶人谷·本周胜利</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n</t>
-  </si>
-  <si>
-    <t>阵营事件·本周战平</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>[团队监控]数据加载成功</t>
-  </si>
-  <si>
-    <t>关闭刷马等计时条</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},</t>
-  </si>
-  <si>
-    <t>{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},</t>
-  </si>
-  <si>
-    <t>你已进入地图【浩气盟】。</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},</t>
-  </si>
-  <si>
-    <t>伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n</t>
-  </si>
-  <si>
-    <t>奇袭攻防·正式开启</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},</t>
-  </si>
-  <si>
-    <t>王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n</t>
-  </si>
-  <si>
-    <t>主场攻防·正式开启</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},</t>
-  </si>
-  <si>
-    <t>你已进入地图【恶人谷】。</t>
-  </si>
-  <si>
-    <t>韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n</t>
-  </si>
-  <si>
-    <t>谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n</t>
-  </si>
-  <si>
-    <t>通用地图</t>
-  </si>
-  <si>
-    <t>阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},</t>
-  </si>
-  <si>
-    <t>阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},</t>
-  </si>
-  <si>
-    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！</t>
-  </si>
-  <si>
-    <t>祭天·{$1}·[{$2}]·{$4}</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},</t>
-  </si>
-  <si>
-    <t>阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n</t>
-  </si>
-  <si>
-    <t>阵营攻防·奇袭场·开启分线</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},</t>
-  </si>
-  <si>
-    <t>阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n</t>
-  </si>
-  <si>
-    <t>阵营攻防·奇袭场·未开分线</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},</t>
-  </si>
-  <si>
-    <t>逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n</t>
-  </si>
-  <si>
-    <t>据点攻防·阴山大草原·开启分线·5分钟</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},</t>
-  </si>
-  <si>
-    <t>前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n</t>
-  </si>
-  <si>
-    <t>据点攻防·阴山大草原</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},</t>
-  </si>
-  <si>
-    <t>阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n</t>
-  </si>
-  <si>
-    <t>据点攻防·阴山大草原·分线·正式开始</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},</t>
-  </si>
-  <si>
-    <t>据点争夺已结束，所有交通已恢复。\n</t>
-  </si>
-  <si>
-    <t>据点攻防·已经结束</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},</t>
-  </si>
-  <si>
-    <t>正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·拍卖掉落</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·浩气盟·险胜</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·浩气盟·大胜</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·浩气盟·完胜</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·恶人谷·险胜</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·恶人谷·大胜</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·恶人谷·完胜</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n</t>
-  </si>
-  <si>
-    <t>据点攻防·平局</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺</t>
-  </si>
-  <si>
-    <t>{$3}·{$1}大旗被夺</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},</t>
-  </si>
-  <si>
-    <t>([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！</t>
-  </si>
-  <si>
-    <t>{$3}·{$1}占领</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},</t>
-  </si>
-  <si>
-    <t>前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},</t>
-  </si>
-  <si>
-    <t>本场贡献值进入前1200名，额外获得3000威名，可通过邮件领取\n</t>
-  </si>
-  <si>
-    <t>据点攻防·进入前1200名</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},</t>
-  </si>
-  <si>
-    <t>^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫</t>
-  </si>
-  <si>
-    <t>{$1}·{$2}劫粮</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},</t>
-  </si>
-  <si>
-    <t>秘境地图</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},</t>
@@ -9249,7 +9258,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1791637824000,</v>
+        <v>nTimeStamp = 1791739816000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -10992,10 +11001,10 @@
         <v>1775</v>
       </c>
       <c r="B3" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="C3" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11003,10 +11012,10 @@
         <v>1781</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="C4" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11014,10 +11023,10 @@
         <v>1790</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11025,10 +11034,10 @@
         <v>1794</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11036,10 +11045,10 @@
         <v>1800</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11047,10 +11056,10 @@
         <v>1804</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -11058,10 +11067,10 @@
         <v>1815</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2590</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11069,10 +11078,10 @@
         <v>1819</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11080,10 +11089,10 @@
         <v>1825</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11091,10 +11100,10 @@
         <v>1829</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11102,10 +11111,10 @@
         <v>1833</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11113,10 +11122,10 @@
         <v>1837</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11124,10 +11133,10 @@
         <v>1843</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11135,10 +11144,10 @@
         <v>1847</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11146,10 +11155,10 @@
         <v>1851</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11157,10 +11166,10 @@
         <v>1855</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11168,10 +11177,10 @@
         <v>1861</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2600</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11179,10 +11188,10 @@
         <v>1865</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2601</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11190,10 +11199,10 @@
         <v>1871</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2602</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11201,10 +11210,10 @@
         <v>1875</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2603</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11212,10 +11221,10 @@
         <v>1879</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11223,10 +11232,10 @@
         <v>1883</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2605</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11234,10 +11243,10 @@
         <v>1893</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2606</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11245,10 +11254,10 @@
         <v>1897</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2607</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11256,10 +11265,10 @@
         <v>1901</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2608</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11267,10 +11276,10 @@
         <v>1905</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2609</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11278,10 +11287,10 @@
         <v>1917</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2610</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11289,10 +11298,10 @@
         <v>1921</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2611</v>
+        <v>2614</v>
       </c>
     </row>
   </sheetData>
@@ -37789,7 +37798,7 @@
         <v>30</v>
       </c>
       <c r="V131" t="str">
-        <f t="shared" ref="V131:V162" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V131:V177" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
         <v>},[30]={</v>
       </c>
     </row>
@@ -38496,7 +38505,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W163" t="s">
@@ -38517,7 +38526,7 @@
         <v>656</v>
       </c>
       <c r="V164" t="str">
-        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(D164),ISBLANK(N164),ISBLANK(O164),OR(ISBLANK(B163)=FALSE,ISBLANK(D163)=FALSE,ISBLANK(N163)=FALSE,ISBLANK(O163)=FALSE)),"},},}",IF(ISBLANK(D164),"","{szContent="""&amp;D164&amp;""","&amp;IF(C164&lt;&gt;"","szTarget="""&amp;C164&amp;""",","")&amp;IF(E164&lt;&gt;"","szNote="""&amp;E164&amp;""",","")&amp;IF(M164&lt;&gt;"","col={"&amp;M164&amp;"},","")&amp;IF(N164&gt;0,"bSearch=true,","")&amp;IF(O164&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P164&gt;0,"szVoice="""&amp;P164&amp;""",","")&amp;IF(Q164&gt;0,"bTeamChannel=true,","")&amp;IF(R164&gt;0,"bWhisperChannel=true,","")&amp;IF(S164&gt;0,"bCenterAlarm=true,","")&amp;IF(T164&gt;0,"bScreenHead=true,","")&amp;IF(U164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W164:AAH164)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>},[656]={</v>
       </c>
     </row>
@@ -38532,7 +38541,7 @@
         <v>2180</v>
       </c>
       <c r="V165" t="str">
-        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(D165),ISBLANK(N165),ISBLANK(O165),OR(ISBLANK(B164)=FALSE,ISBLANK(D164)=FALSE,ISBLANK(N164)=FALSE,ISBLANK(O164)=FALSE)),"},},}",IF(ISBLANK(D165),"","{szContent="""&amp;D165&amp;""","&amp;IF(C165&lt;&gt;"","szTarget="""&amp;C165&amp;""",","")&amp;IF(E165&lt;&gt;"","szNote="""&amp;E165&amp;""",","")&amp;IF(M165&lt;&gt;"","col={"&amp;M165&amp;"},","")&amp;IF(N165&gt;0,"bSearch=true,","")&amp;IF(O165&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P165&gt;0,"szVoice="""&amp;P165&amp;""",","")&amp;IF(Q165&gt;0,"bTeamChannel=true,","")&amp;IF(R165&gt;0,"bWhisperChannel=true,","")&amp;IF(S165&gt;0,"bCenterAlarm=true,","")&amp;IF(T165&gt;0,"bScreenHead=true,","")&amp;IF(U165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W165:AAH165)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W165" t="s">
@@ -38556,7 +38565,7 @@
         <v>2185</v>
       </c>
       <c r="V166" t="str">
-        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(D166),ISBLANK(N166),ISBLANK(O166),OR(ISBLANK(B165)=FALSE,ISBLANK(D165)=FALSE,ISBLANK(N165)=FALSE,ISBLANK(O165)=FALSE)),"},},}",IF(ISBLANK(D166),"","{szContent="""&amp;D166&amp;""","&amp;IF(C166&lt;&gt;"","szTarget="""&amp;C166&amp;""",","")&amp;IF(E166&lt;&gt;"","szNote="""&amp;E166&amp;""",","")&amp;IF(M166&lt;&gt;"","col={"&amp;M166&amp;"},","")&amp;IF(N166&gt;0,"bSearch=true,","")&amp;IF(O166&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P166&gt;0,"szVoice="""&amp;P166&amp;""",","")&amp;IF(Q166&gt;0,"bTeamChannel=true,","")&amp;IF(R166&gt;0,"bWhisperChannel=true,","")&amp;IF(S166&gt;0,"bCenterAlarm=true,","")&amp;IF(T166&gt;0,"bScreenHead=true,","")&amp;IF(U166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W166:AAH166)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W166" t="s">
@@ -38580,7 +38589,7 @@
         <v>2188</v>
       </c>
       <c r="V167" t="str">
-        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(D167),ISBLANK(N167),ISBLANK(O167),OR(ISBLANK(B166)=FALSE,ISBLANK(D166)=FALSE,ISBLANK(N166)=FALSE,ISBLANK(O166)=FALSE)),"},},}",IF(ISBLANK(D167),"","{szContent="""&amp;D167&amp;""","&amp;IF(C167&lt;&gt;"","szTarget="""&amp;C167&amp;""",","")&amp;IF(E167&lt;&gt;"","szNote="""&amp;E167&amp;""",","")&amp;IF(M167&lt;&gt;"","col={"&amp;M167&amp;"},","")&amp;IF(N167&gt;0,"bSearch=true,","")&amp;IF(O167&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P167&gt;0,"szVoice="""&amp;P167&amp;""",","")&amp;IF(Q167&gt;0,"bTeamChannel=true,","")&amp;IF(R167&gt;0,"bWhisperChannel=true,","")&amp;IF(S167&gt;0,"bCenterAlarm=true,","")&amp;IF(T167&gt;0,"bScreenHead=true,","")&amp;IF(U167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W167:AAH167)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W167" t="s">
@@ -38598,7 +38607,7 @@
         <v>2190</v>
       </c>
       <c r="V168" t="str">
-        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(D168),ISBLANK(N168),ISBLANK(O168),OR(ISBLANK(B167)=FALSE,ISBLANK(D167)=FALSE,ISBLANK(N167)=FALSE,ISBLANK(O167)=FALSE)),"},},}",IF(ISBLANK(D168),"","{szContent="""&amp;D168&amp;""","&amp;IF(C168&lt;&gt;"","szTarget="""&amp;C168&amp;""",","")&amp;IF(E168&lt;&gt;"","szNote="""&amp;E168&amp;""",","")&amp;IF(M168&lt;&gt;"","col={"&amp;M168&amp;"},","")&amp;IF(N168&gt;0,"bSearch=true,","")&amp;IF(O168&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P168&gt;0,"szVoice="""&amp;P168&amp;""",","")&amp;IF(Q168&gt;0,"bTeamChannel=true,","")&amp;IF(R168&gt;0,"bWhisperChannel=true,","")&amp;IF(S168&gt;0,"bCenterAlarm=true,","")&amp;IF(T168&gt;0,"bScreenHead=true,","")&amp;IF(U168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W168:AAH168)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W168" t="s">
@@ -38621,7 +38630,7 @@
         <v>2002</v>
       </c>
       <c r="V169" t="str">
-        <f>IF(ISBLANK(B169)=FALSE,IF(ISBLANK(B168),"},["&amp;B169&amp;"]={","["&amp;B169&amp;"]={"),IF(AND(ISBLANK(B169),ISBLANK(D169),ISBLANK(N169),ISBLANK(O169),OR(ISBLANK(B168)=FALSE,ISBLANK(D168)=FALSE,ISBLANK(N168)=FALSE,ISBLANK(O168)=FALSE)),"},},}",IF(ISBLANK(D169),"","{szContent="""&amp;D169&amp;""","&amp;IF(C169&lt;&gt;"","szTarget="""&amp;C169&amp;""",","")&amp;IF(E169&lt;&gt;"","szNote="""&amp;E169&amp;""",","")&amp;IF(M169&lt;&gt;"","col={"&amp;M169&amp;"},","")&amp;IF(N169&gt;0,"bSearch=true,","")&amp;IF(O169&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P169&gt;0,"szVoice="""&amp;P169&amp;""",","")&amp;IF(Q169&gt;0,"bTeamChannel=true,","")&amp;IF(R169&gt;0,"bWhisperChannel=true,","")&amp;IF(S169&gt;0,"bCenterAlarm=true,","")&amp;IF(T169&gt;0,"bScreenHead=true,","")&amp;IF(U169&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W169&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W169:AAH169)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W169" t="s">
@@ -38655,7 +38664,7 @@
         <v>1</v>
       </c>
       <c r="V170" t="str">
-        <f>IF(ISBLANK(B170)=FALSE,IF(ISBLANK(B169),"},["&amp;B170&amp;"]={","["&amp;B170&amp;"]={"),IF(AND(ISBLANK(B170),ISBLANK(D170),ISBLANK(N170),ISBLANK(O170),OR(ISBLANK(B169)=FALSE,ISBLANK(D169)=FALSE,ISBLANK(N169)=FALSE,ISBLANK(O169)=FALSE)),"},},}",IF(ISBLANK(D170),"","{szContent="""&amp;D170&amp;""","&amp;IF(C170&lt;&gt;"","szTarget="""&amp;C170&amp;""",","")&amp;IF(E170&lt;&gt;"","szNote="""&amp;E170&amp;""",","")&amp;IF(M170&lt;&gt;"","col={"&amp;M170&amp;"},","")&amp;IF(N170&gt;0,"bSearch=true,","")&amp;IF(O170&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P170&gt;0,"szVoice="""&amp;P170&amp;""",","")&amp;IF(Q170&gt;0,"bTeamChannel=true,","")&amp;IF(R170&gt;0,"bWhisperChannel=true,","")&amp;IF(S170&gt;0,"bCenterAlarm=true,","")&amp;IF(T170&gt;0,"bScreenHead=true,","")&amp;IF(U170&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W170&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W170:AAH170)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W170" t="s">
@@ -38685,7 +38694,7 @@
         <v>1</v>
       </c>
       <c r="V171" t="str">
-        <f>IF(ISBLANK(B171)=FALSE,IF(ISBLANK(B170),"},["&amp;B171&amp;"]={","["&amp;B171&amp;"]={"),IF(AND(ISBLANK(B171),ISBLANK(D171),ISBLANK(N171),ISBLANK(O171),OR(ISBLANK(B170)=FALSE,ISBLANK(D170)=FALSE,ISBLANK(N170)=FALSE,ISBLANK(O170)=FALSE)),"},},}",IF(ISBLANK(D171),"","{szContent="""&amp;D171&amp;""","&amp;IF(C171&lt;&gt;"","szTarget="""&amp;C171&amp;""",","")&amp;IF(E171&lt;&gt;"","szNote="""&amp;E171&amp;""",","")&amp;IF(M171&lt;&gt;"","col={"&amp;M171&amp;"},","")&amp;IF(N171&gt;0,"bSearch=true,","")&amp;IF(O171&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P171&gt;0,"szVoice="""&amp;P171&amp;""",","")&amp;IF(Q171&gt;0,"bTeamChannel=true,","")&amp;IF(R171&gt;0,"bWhisperChannel=true,","")&amp;IF(S171&gt;0,"bCenterAlarm=true,","")&amp;IF(T171&gt;0,"bScreenHead=true,","")&amp;IF(U171&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W171&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W171:AAH171)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W171" t="s">
@@ -38715,7 +38724,7 @@
         <v>1</v>
       </c>
       <c r="V172" t="str">
-        <f>IF(ISBLANK(B172)=FALSE,IF(ISBLANK(B171),"},["&amp;B172&amp;"]={","["&amp;B172&amp;"]={"),IF(AND(ISBLANK(B172),ISBLANK(D172),ISBLANK(N172),ISBLANK(O172),OR(ISBLANK(B171)=FALSE,ISBLANK(D171)=FALSE,ISBLANK(N171)=FALSE,ISBLANK(O171)=FALSE)),"},},}",IF(ISBLANK(D172),"","{szContent="""&amp;D172&amp;""","&amp;IF(C172&lt;&gt;"","szTarget="""&amp;C172&amp;""",","")&amp;IF(E172&lt;&gt;"","szNote="""&amp;E172&amp;""",","")&amp;IF(M172&lt;&gt;"","col={"&amp;M172&amp;"},","")&amp;IF(N172&gt;0,"bSearch=true,","")&amp;IF(O172&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P172&gt;0,"szVoice="""&amp;P172&amp;""",","")&amp;IF(Q172&gt;0,"bTeamChannel=true,","")&amp;IF(R172&gt;0,"bWhisperChannel=true,","")&amp;IF(S172&gt;0,"bCenterAlarm=true,","")&amp;IF(T172&gt;0,"bScreenHead=true,","")&amp;IF(U172&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W172&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W172:AAH172)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W172" t="s">
@@ -38739,7 +38748,7 @@
         <v>1</v>
       </c>
       <c r="V173" t="str">
-        <f>IF(ISBLANK(B173)=FALSE,IF(ISBLANK(B172),"},["&amp;B173&amp;"]={","["&amp;B173&amp;"]={"),IF(AND(ISBLANK(B173),ISBLANK(D173),ISBLANK(N173),ISBLANK(O173),OR(ISBLANK(B172)=FALSE,ISBLANK(D172)=FALSE,ISBLANK(N172)=FALSE,ISBLANK(O172)=FALSE)),"},},}",IF(ISBLANK(D173),"","{szContent="""&amp;D173&amp;""","&amp;IF(C173&lt;&gt;"","szTarget="""&amp;C173&amp;""",","")&amp;IF(E173&lt;&gt;"","szNote="""&amp;E173&amp;""",","")&amp;IF(M173&lt;&gt;"","col={"&amp;M173&amp;"},","")&amp;IF(N173&gt;0,"bSearch=true,","")&amp;IF(O173&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P173&gt;0,"szVoice="""&amp;P173&amp;""",","")&amp;IF(Q173&gt;0,"bTeamChannel=true,","")&amp;IF(R173&gt;0,"bWhisperChannel=true,","")&amp;IF(S173&gt;0,"bCenterAlarm=true,","")&amp;IF(T173&gt;0,"bScreenHead=true,","")&amp;IF(U173&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W173&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W173:AAH173)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W173" t="s">
@@ -38773,7 +38782,7 @@
         <v>1</v>
       </c>
       <c r="V174" t="str">
-        <f>IF(ISBLANK(B174)=FALSE,IF(ISBLANK(B173),"},["&amp;B174&amp;"]={","["&amp;B174&amp;"]={"),IF(AND(ISBLANK(B174),ISBLANK(D174),ISBLANK(N174),ISBLANK(O174),OR(ISBLANK(B173)=FALSE,ISBLANK(D173)=FALSE,ISBLANK(N173)=FALSE,ISBLANK(O173)=FALSE)),"},},}",IF(ISBLANK(D174),"","{szContent="""&amp;D174&amp;""","&amp;IF(C174&lt;&gt;"","szTarget="""&amp;C174&amp;""",","")&amp;IF(E174&lt;&gt;"","szNote="""&amp;E174&amp;""",","")&amp;IF(M174&lt;&gt;"","col={"&amp;M174&amp;"},","")&amp;IF(N174&gt;0,"bSearch=true,","")&amp;IF(O174&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P174&gt;0,"szVoice="""&amp;P174&amp;""",","")&amp;IF(Q174&gt;0,"bTeamChannel=true,","")&amp;IF(R174&gt;0,"bWhisperChannel=true,","")&amp;IF(S174&gt;0,"bCenterAlarm=true,","")&amp;IF(T174&gt;0,"bScreenHead=true,","")&amp;IF(U174&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W174&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W174:AAH174)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W174" t="s">
@@ -38798,7 +38807,7 @@
         <v>1</v>
       </c>
       <c r="V175" t="str">
-        <f>IF(ISBLANK(B175)=FALSE,IF(ISBLANK(B174),"},["&amp;B175&amp;"]={","["&amp;B175&amp;"]={"),IF(AND(ISBLANK(B175),ISBLANK(D175),ISBLANK(N175),ISBLANK(O175),OR(ISBLANK(B174)=FALSE,ISBLANK(D174)=FALSE,ISBLANK(N174)=FALSE,ISBLANK(O174)=FALSE)),"},},}",IF(ISBLANK(D175),"","{szContent="""&amp;D175&amp;""","&amp;IF(C175&lt;&gt;"","szTarget="""&amp;C175&amp;""",","")&amp;IF(E175&lt;&gt;"","szNote="""&amp;E175&amp;""",","")&amp;IF(M175&lt;&gt;"","col={"&amp;M175&amp;"},","")&amp;IF(N175&gt;0,"bSearch=true,","")&amp;IF(O175&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P175&gt;0,"szVoice="""&amp;P175&amp;""",","")&amp;IF(Q175&gt;0,"bTeamChannel=true,","")&amp;IF(R175&gt;0,"bWhisperChannel=true,","")&amp;IF(S175&gt;0,"bCenterAlarm=true,","")&amp;IF(T175&gt;0,"bScreenHead=true,","")&amp;IF(U175&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W175&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W175:AAH175)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W175" t="s">
@@ -38828,7 +38837,7 @@
         <v>1</v>
       </c>
       <c r="V176" t="str">
-        <f>IF(ISBLANK(B176)=FALSE,IF(ISBLANK(B175),"},["&amp;B176&amp;"]={","["&amp;B176&amp;"]={"),IF(AND(ISBLANK(B176),ISBLANK(D176),ISBLANK(N176),ISBLANK(O176),OR(ISBLANK(B175)=FALSE,ISBLANK(D175)=FALSE,ISBLANK(N175)=FALSE,ISBLANK(O175)=FALSE)),"},},}",IF(ISBLANK(D176),"","{szContent="""&amp;D176&amp;""","&amp;IF(C176&lt;&gt;"","szTarget="""&amp;C176&amp;""",","")&amp;IF(E176&lt;&gt;"","szNote="""&amp;E176&amp;""",","")&amp;IF(M176&lt;&gt;"","col={"&amp;M176&amp;"},","")&amp;IF(N176&gt;0,"bSearch=true,","")&amp;IF(O176&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P176&gt;0,"szVoice="""&amp;P176&amp;""",","")&amp;IF(Q176&gt;0,"bTeamChannel=true,","")&amp;IF(R176&gt;0,"bWhisperChannel=true,","")&amp;IF(S176&gt;0,"bCenterAlarm=true,","")&amp;IF(T176&gt;0,"bScreenHead=true,","")&amp;IF(U176&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W176&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W176:AAH176)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W176" t="s">
@@ -38843,7 +38852,7 @@
     </row>
     <row r="177" spans="22:22">
       <c r="V177" t="str">
-        <f>IF(ISBLANK(B177)=FALSE,IF(ISBLANK(B176),"},["&amp;B177&amp;"]={","["&amp;B177&amp;"]={"),IF(AND(ISBLANK(B177),ISBLANK(D177),ISBLANK(N177),ISBLANK(O177),OR(ISBLANK(B176)=FALSE,ISBLANK(D176)=FALSE,ISBLANK(N176)=FALSE,ISBLANK(O176)=FALSE)),"},},}",IF(ISBLANK(D177),"","{szContent="""&amp;D177&amp;""","&amp;IF(C177&lt;&gt;"","szTarget="""&amp;C177&amp;""",","")&amp;IF(E177&lt;&gt;"","szNote="""&amp;E177&amp;""",","")&amp;IF(M177&lt;&gt;"","col={"&amp;M177&amp;"},","")&amp;IF(N177&gt;0,"bSearch=true,","")&amp;IF(O177&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P177&gt;0,"szVoice="""&amp;P177&amp;""",","")&amp;IF(Q177&gt;0,"bTeamChannel=true,","")&amp;IF(R177&gt;0,"bWhisperChannel=true,","")&amp;IF(S177&gt;0,"bCenterAlarm=true,","")&amp;IF(T177&gt;0,"bScreenHead=true,","")&amp;IF(U177&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W177&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W177:AAH177)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="20"/>
         <v>},},}</v>
       </c>
     </row>
@@ -39173,7 +39182,7 @@
       </c>
       <c r="T9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
+        <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=0,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=0,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,nRefresh=10,key="大攻防·{$1}",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,nRefresh=0,key="大攻防·奇袭场",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,nRefresh=0,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U9" t="s">
         <v>2326</v>
@@ -39233,13 +39242,13 @@
         <v>2341</v>
       </c>
       <c r="V10" t="s">
-        <v>2331</v>
+        <v>2326</v>
       </c>
       <c r="W10" t="s">
-        <v>2332</v>
+        <v>2327</v>
       </c>
       <c r="X10" t="s">
-        <v>2333</v>
+        <v>2328</v>
       </c>
       <c r="Y10" t="s">
         <v>2334</v>
@@ -39275,13 +39284,13 @@
         <v>2344</v>
       </c>
       <c r="V11" t="s">
-        <v>2331</v>
+        <v>2326</v>
       </c>
       <c r="W11" t="s">
-        <v>2332</v>
+        <v>2327</v>
       </c>
       <c r="X11" t="s">
-        <v>2333</v>
+        <v>2328</v>
       </c>
       <c r="Y11" t="s">
         <v>2334</v>
@@ -41401,27 +41410,27 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U115" t="s">
-        <v>2326</v>
+        <v>2483</v>
       </c>
       <c r="V115" t="s">
-        <v>2327</v>
+        <v>2484</v>
       </c>
       <c r="W115" t="s">
-        <v>2328</v>
+        <v>2485</v>
       </c>
       <c r="X115" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="Y115" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:34">
       <c r="C116" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="D116" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="K116" t="s">
         <v>2002</v>
@@ -41431,15 +41440,15 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U116" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:34">
       <c r="C117" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
       <c r="D117" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="K117" t="s">
         <v>2002</v>
@@ -41449,7 +41458,7 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U117" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:34">
@@ -41472,7 +41481,7 @@
         <v>2447</v>
       </c>
       <c r="G119" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="K119" t="s">
         <v>2002</v>
@@ -41502,13 +41511,13 @@
         <v>2450</v>
       </c>
       <c r="Z119" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AA119" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AB119" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AC119" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G119&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G119&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41521,10 +41530,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:34">
       <c r="C120" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D120" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K120" t="s">
         <v>2002</v>
@@ -41537,16 +41546,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U120" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="V120" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="W120" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="X120" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="121" spans="1:34">
@@ -41569,7 +41578,7 @@
         <v>2447</v>
       </c>
       <c r="G122" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="K122" t="s">
         <v>2002</v>
@@ -41599,13 +41608,13 @@
         <v>2450</v>
       </c>
       <c r="Z122" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AA122" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AB122" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AC122" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G122&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G122&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41618,10 +41627,10 @@
     </row>
     <row r="123" spans="1:34">
       <c r="C123" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D123" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K123" t="s">
         <v>2002</v>
@@ -41634,16 +41643,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U123" t="s">
+        <v>2505</v>
+      </c>
+      <c r="V123" t="s">
+        <v>2501</v>
+      </c>
+      <c r="W123" t="s">
         <v>2502</v>
       </c>
-      <c r="V123" t="s">
-        <v>2498</v>
-      </c>
-      <c r="W123" t="s">
-        <v>2499</v>
-      </c>
       <c r="X123" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -41666,10 +41675,10 @@
         <v>2447</v>
       </c>
       <c r="G125" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="H125" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="K125" t="s">
         <v>2002</v>
@@ -41707,13 +41716,13 @@
         <v>2450</v>
       </c>
       <c r="AB125" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC125" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD125" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE125" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G125&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G125&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41734,10 +41743,10 @@
     </row>
     <row r="126" spans="1:34">
       <c r="C126" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D126" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K126" t="s">
         <v>2002</v>
@@ -41750,22 +41759,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U126" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
       <c r="V126" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="W126" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X126" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y126" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="Z126" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="127" spans="1:34">
@@ -41788,10 +41797,10 @@
         <v>2447</v>
       </c>
       <c r="G128" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="H128" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="K128" t="s">
         <v>2002</v>
@@ -41829,13 +41838,13 @@
         <v>2450</v>
       </c>
       <c r="AB128" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC128" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD128" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE128" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G128&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G128&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41856,10 +41865,10 @@
     </row>
     <row r="129" spans="1:34">
       <c r="C129" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D129" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K129" t="s">
         <v>2002</v>
@@ -41872,22 +41881,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U129" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
       <c r="V129" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="W129" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X129" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y129" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="Z129" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="130" spans="1:34">
@@ -41910,10 +41919,10 @@
         <v>2447</v>
       </c>
       <c r="G131" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="H131" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="K131" t="s">
         <v>2002</v>
@@ -41951,13 +41960,13 @@
         <v>2450</v>
       </c>
       <c r="AB131" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC131" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD131" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE131" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G131&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G131&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41978,10 +41987,10 @@
     </row>
     <row r="132" spans="1:34">
       <c r="C132" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D132" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K132" t="s">
         <v>2002</v>
@@ -41994,22 +42003,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U132" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="V132" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="W132" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X132" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y132" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="Z132" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="133" spans="1:34">
@@ -42032,10 +42041,10 @@
         <v>2447</v>
       </c>
       <c r="G134" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="H134" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="K134" t="s">
         <v>2002</v>
@@ -42073,13 +42082,13 @@
         <v>2450</v>
       </c>
       <c r="AB134" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC134" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD134" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE134" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G134&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G134&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42100,10 +42109,10 @@
     </row>
     <row r="135" spans="1:34">
       <c r="C135" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D135" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K135" t="s">
         <v>2002</v>
@@ -42116,22 +42125,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U135" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="V135" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="W135" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X135" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y135" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="Z135" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -42154,10 +42163,10 @@
         <v>2447</v>
       </c>
       <c r="G137" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="H137" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="K137" t="s">
         <v>2002</v>
@@ -42195,13 +42204,13 @@
         <v>2450</v>
       </c>
       <c r="AB137" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC137" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD137" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE137" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G137&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G137&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42222,10 +42231,10 @@
     </row>
     <row r="138" spans="1:34">
       <c r="C138" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D138" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K138" t="s">
         <v>2002</v>
@@ -42238,22 +42247,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U138" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="V138" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="W138" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X138" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y138" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="Z138" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="139" spans="1:34">
@@ -42276,10 +42285,10 @@
         <v>2447</v>
       </c>
       <c r="G140" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="H140" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="K140" t="s">
         <v>2002</v>
@@ -42317,13 +42326,13 @@
         <v>2450</v>
       </c>
       <c r="AB140" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC140" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD140" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE140" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G140&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G140&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42344,10 +42353,10 @@
     </row>
     <row r="141" spans="1:34">
       <c r="C141" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D141" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K141" t="s">
         <v>2002</v>
@@ -42360,22 +42369,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U141" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="V141" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="W141" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X141" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y141" t="s">
-        <v>2538</v>
+        <v>2541</v>
       </c>
       <c r="Z141" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -42398,10 +42407,10 @@
         <v>2447</v>
       </c>
       <c r="G143" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
       <c r="H143" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="K143" t="s">
         <v>2002</v>
@@ -42439,13 +42448,13 @@
         <v>2450</v>
       </c>
       <c r="AB143" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC143" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD143" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE143" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G143&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G143&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42466,10 +42475,10 @@
     </row>
     <row r="144" spans="1:34">
       <c r="C144" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D144" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K144" t="s">
         <v>2002</v>
@@ -42482,22 +42491,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U144" t="s">
-        <v>2542</v>
+        <v>2545</v>
       </c>
       <c r="V144" t="s">
-        <v>2543</v>
+        <v>2546</v>
       </c>
       <c r="W144" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X144" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y144" t="s">
-        <v>2544</v>
+        <v>2547</v>
       </c>
       <c r="Z144" t="s">
-        <v>2545</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="145" spans="1:34">
@@ -42520,10 +42529,10 @@
         <v>2447</v>
       </c>
       <c r="G146" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="H146" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="K146" t="s">
         <v>2002</v>
@@ -42561,13 +42570,13 @@
         <v>2450</v>
       </c>
       <c r="AB146" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC146" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD146" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE146" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G146&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G146&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42588,10 +42597,10 @@
     </row>
     <row r="147" spans="1:34">
       <c r="C147" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D147" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K147" t="s">
         <v>2002</v>
@@ -42604,22 +42613,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U147" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="V147" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="W147" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X147" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y147" t="s">
-        <v>2550</v>
+        <v>2553</v>
       </c>
       <c r="Z147" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -42642,10 +42651,10 @@
         <v>2447</v>
       </c>
       <c r="G149" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="H149" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="K149" t="s">
         <v>2002</v>
@@ -42683,13 +42692,13 @@
         <v>2450</v>
       </c>
       <c r="AB149" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC149" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD149" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE149" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G149&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G149&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42710,10 +42719,10 @@
     </row>
     <row r="150" spans="1:34">
       <c r="C150" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D150" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K150" t="s">
         <v>2002</v>
@@ -42726,22 +42735,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U150" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="V150" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="W150" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X150" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y150" t="s">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="Z150" t="s">
-        <v>2557</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="151" spans="1:34">
@@ -42764,10 +42773,10 @@
         <v>2447</v>
       </c>
       <c r="G152" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="H152" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="K152" t="s">
         <v>2002</v>
@@ -42805,13 +42814,13 @@
         <v>2450</v>
       </c>
       <c r="AB152" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC152" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD152" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE152" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G152&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G152&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42832,10 +42841,10 @@
     </row>
     <row r="153" spans="1:34">
       <c r="C153" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D153" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K153" t="s">
         <v>2002</v>
@@ -42848,22 +42857,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U153" t="s">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="V153" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="W153" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X153" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y153" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="Z153" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -42886,10 +42895,10 @@
         <v>2447</v>
       </c>
       <c r="G155" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="H155" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="K155" t="s">
         <v>2002</v>
@@ -42927,13 +42936,13 @@
         <v>2450</v>
       </c>
       <c r="AB155" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC155" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD155" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE155" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G155&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G155&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42954,10 +42963,10 @@
     </row>
     <row r="156" spans="1:34">
       <c r="C156" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D156" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K156" t="s">
         <v>2002</v>
@@ -42970,22 +42979,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U156" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="V156" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="W156" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X156" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y156" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="Z156" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="157" spans="1:34">
@@ -43008,10 +43017,10 @@
         <v>2447</v>
       </c>
       <c r="G158" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="H158" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
       <c r="K158" t="s">
         <v>2002</v>
@@ -43049,13 +43058,13 @@
         <v>2450</v>
       </c>
       <c r="AB158" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="AC158" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="AD158" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="AE158" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G158&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G158&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43076,10 +43085,10 @@
     </row>
     <row r="159" spans="1:34">
       <c r="C159" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D159" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K159" t="s">
         <v>2002</v>
@@ -43092,22 +43101,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U159" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="V159" t="s">
-        <v>2573</v>
+        <v>2576</v>
       </c>
       <c r="W159" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X159" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y159" t="s">
-        <v>2574</v>
+        <v>2577</v>
       </c>
       <c r="Z159" t="s">
-        <v>2575</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="160" spans="1:34">
@@ -43124,16 +43133,16 @@
     </row>
     <row r="161" spans="1:26">
       <c r="C161" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="D161" t="s">
         <v>2447</v>
       </c>
       <c r="G161" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
       <c r="H161" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="K161" t="s">
         <v>2002</v>
@@ -43155,7 +43164,7 @@
         <v>2450</v>
       </c>
       <c r="X161" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="Y161" t="s">
         <v>2452</v>
@@ -43166,10 +43175,10 @@
     </row>
     <row r="162" spans="1:26">
       <c r="C162" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D162" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K162" t="s">
         <v>2002</v>
@@ -43182,22 +43191,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U162" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
       <c r="V162" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
       <c r="W162" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X162" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y162" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="Z162" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:26">
@@ -43247,16 +43256,16 @@
     </row>
     <row r="165" spans="1:26">
       <c r="C165" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="D165" t="s">
         <v>2447</v>
       </c>
       <c r="G165" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
       <c r="H165" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="K165" t="s">
         <v>2002</v>
@@ -43278,7 +43287,7 @@
         <v>2450</v>
       </c>
       <c r="X165" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="Y165" t="s">
         <v>2452</v>
@@ -43289,10 +43298,10 @@
     </row>
     <row r="166" spans="1:26">
       <c r="C166" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="D166" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="K166" t="s">
         <v>2002</v>
@@ -43305,22 +43314,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
       <c r="V166" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
       <c r="W166" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="X166" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="Y166" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="Z166" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:26">

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据总控" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5692" uniqueCount="2616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5692" uniqueCount="2617">
   <si>
     <t>__meta = {</t>
   </si>
@@ -6742,220 +6742,223 @@
     <t>[{$1}]·离开据点·大旗重置</t>
   </si>
   <si>
+    <t>{nClass=14,nIcon=592,nFrame=4,szName="【{$1}·离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},</t>
+  </si>
+  <si>
+    <t>^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！</t>
+  </si>
+  <si>
+    <t>[{$1}]·{$2}·城门</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},</t>
+  </si>
+  <si>
+    <t>身负据点大旗，当心被夺！</t>
+  </si>
+  <si>
+    <t>[{$me}]·扛起大旗</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},</t>
+  </si>
+  <si>
+    <t>你已经离开据点，10秒内未进入据点，则据点旗帜重置。</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},</t>
+  </si>
+  <si>
+    <t>系统检测您有挂机行为，如果长期维持该状态将被传送出图！</t>
+  </si>
+  <si>
+    <t>挂机检测·快活跃起来</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},</t>
+  </si>
+  <si>
+    <t>侠士对抗类装分过低，请前往分流场景或黑戈壁参与。</t>
+  </si>
+  <si>
+    <t>据点攻防·装分过低</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·装分过低",key="挂机检测",},</t>
+  </si>
+  <si>
+    <t>因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！</t>
+  </si>
+  <si>
+    <t>据点攻防·禁止参与</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},</t>
+  </si>
+  <si>
+    <t>据点之战在即，为公平起见，侠士将在30秒后被传出本图，据点帮会25名拥有地图优先进入权的玩家将不会被传送出去。</t>
+  </si>
+  <si>
+    <t>据点攻防·场景清图</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=4,szName="攻防清图·出图剩余",nTime="30,攻防清图·出图剩余;32,据点攻防·清图传出",nRefresh=1,key="挂机检测",},</t>
+  </si>
+  <si>
+    <t>万水千山总是情，买满货物行不行？</t>
+  </si>
+  <si>
+    <t>据点贸易·货物不足</t>
+  </si>
+  <si>
+    <t>浩气盟督廷卫</t>
+  </si>
+  <si>
+    <t>增援已至武王城，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·武王城</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},</t>
+  </si>
+  <si>
+    <t>恶人谷督廷卫</t>
+  </si>
+  <si>
+    <t>增援已至凛风堡，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·凛风堡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},</t>
+  </si>
+  <si>
+    <t>增援已至盘龙坞，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·盘龙坞</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},</t>
+  </si>
+  <si>
+    <t>增援已至逐鹿坪，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·逐鹿坪</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},</t>
+  </si>
+  <si>
+    <t>增援已至龙门镇，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·龙门镇</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},</t>
+  </si>
+  <si>
+    <t>增援已至飞沙关，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·飞沙关</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},</t>
+  </si>
+  <si>
+    <t>增援已至红莲岗，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·红莲岗</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},</t>
+  </si>
+  <si>
+    <t>增援已至秋雨堡，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·秋雨堡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},</t>
+  </si>
+  <si>
+    <t>增援已至神池岭，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·神池岭</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},</t>
+  </si>
+  <si>
+    <t>增援已至烈日岗，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·烈日岗</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},</t>
+  </si>
+  <si>
+    <t>增援已至大理山城，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·大理山城</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},</t>
+  </si>
+  <si>
+    <t>增援已至千岩关，速速进攻！</t>
+  </si>
+  <si>
+    <t>浩气·兵符增援·千岩关</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},</t>
+  </si>
+  <si>
+    <t>增援已至扶风郡，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·扶风郡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},</t>
+  </si>
+  <si>
+    <t>增援已至世外坡，速速进攻！</t>
+  </si>
+  <si>
+    <t>恶人·兵符增援·世外坡</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},</t>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},</t>
+  </si>
+  <si>
     <t>{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},</t>
-  </si>
-  <si>
-    <t>^%[逐鹿中原%]%[(.-)%]：正在(.-)城门！</t>
-  </si>
-  <si>
-    <t>[{$1}]·{$2}·城门</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="打开·城门",nRefresh=10,key="打开·城门",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=1465,nFrame=5,nTime=-2,szName="关闭·城门",nRefresh=10,key="关闭·城门",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=5,nTime=-2,szName="{$2}·城门",key="{$2}·城门",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=2310,nFrame=1,nTime=10,szName="城门·打开·[{$1}]",nRefresh=10,key="打开·城门",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=4839,nFrame=1,nTime=10,szName="城门·关闭·[{$1}]",nRefresh=10,key="关闭·城门",},</t>
-  </si>
-  <si>
-    <t>身负据点大旗，当心被夺！</t>
-  </si>
-  <si>
-    <t>[{$me}]·扛起大旗</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=592,nFrame=8,szName="【{$me}】·拾取大旗",nTime=30,key="拾取大旗·{$me}",},</t>
-  </si>
-  <si>
-    <t>你已经离开据点，10秒内未进入据点，则据点旗帜重置。</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},</t>
-  </si>
-  <si>
-    <t>系统检测您有挂机行为，如果长期维持该状态将被传送出图！</t>
-  </si>
-  <si>
-    <t>挂机检测·快活跃起来</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},</t>
-  </si>
-  <si>
-    <t>侠士对抗类装分过低，请前往分流场景或黑戈壁参与。</t>
-  </si>
-  <si>
-    <t>据点攻防·装分过低</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·装分过低",key="挂机检测",},</t>
-  </si>
-  <si>
-    <t>因侠士近来行为异常，逐鹿中原期间，禁止参与，你即将被传送到百溪！</t>
-  </si>
-  <si>
-    <t>据点攻防·禁止参与</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=2,bHold=true,nTime=30,szName="据点攻防·禁止参与本场",key="挂机检测",},</t>
-  </si>
-  <si>
-    <t>据点之战在即，为公平起见，侠士将在30秒后被传出本图，据点帮会25名拥有地图优先进入权的玩家将不会被传送出去。</t>
-  </si>
-  <si>
-    <t>据点攻防·场景清图</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=13,nFrame=4,szName="攻防清图·出图剩余",nTime="30,攻防清图·出图剩余;32,据点攻防·清图传出",nRefresh=1,key="挂机检测",},</t>
-  </si>
-  <si>
-    <t>万水千山总是情，买满货物行不行？</t>
-  </si>
-  <si>
-    <t>据点贸易·货物不足</t>
-  </si>
-  <si>
-    <t>浩气盟督廷卫</t>
-  </si>
-  <si>
-    <t>增援已至武王城，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·武王城</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·武王城",nTime="10,浩气·兵符增援·武王城;300,浩气·武王城·兵符冷却;305,浩气·武王城·可用兵符",nRefresh=1,key="兵符·武王城",},</t>
-  </si>
-  <si>
-    <t>恶人谷督廷卫</t>
-  </si>
-  <si>
-    <t>增援已至凛风堡，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·凛风堡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·凛风堡",nTime="10,恶人·兵符增援·凛风堡;300,恶人·凛风堡·兵符冷却;305,恶人·凛风堡·可用兵符",nRefresh=1,key="兵符·凛风堡",},</t>
-  </si>
-  <si>
-    <t>增援已至盘龙坞，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·盘龙坞</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·盘龙坞",nTime="10,浩气·兵符增援·盘龙坞;300,浩气·盘龙坞·兵符冷却;305,浩气·盘龙坞·可用兵符",nRefresh=1,key="兵符·盘龙坞",},</t>
-  </si>
-  <si>
-    <t>增援已至逐鹿坪，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·逐鹿坪</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·逐鹿坪",nTime="10,浩气·兵符增援·逐鹿坪;300,浩气·逐鹿坪·兵符冷却;305,浩气·逐鹿坪·可用兵符",nRefresh=1,key="兵符·逐鹿坪",},</t>
-  </si>
-  <si>
-    <t>增援已至龙门镇，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·龙门镇</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·龙门镇",nTime="10,恶人·兵符增援·龙门镇;300,恶人·龙门镇·兵符冷却;305,恶人·龙门镇·可用兵符",nRefresh=1,key="兵符·龙门镇",},</t>
-  </si>
-  <si>
-    <t>增援已至飞沙关，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·飞沙关</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·飞沙关",nTime="10,恶人·兵符增援·飞沙关;300,恶人·飞沙关·兵符冷却;305,恶人·飞沙关·可用兵符",nRefresh=1,key="兵符·飞沙关",},</t>
-  </si>
-  <si>
-    <t>增援已至红莲岗，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·红莲岗</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·红莲岗",nTime="10,浩气·兵符增援·红莲岗;300,浩气·红莲岗·兵符冷却;305,浩气·红莲岗·可用兵符",nRefresh=1,key="兵符·红莲岗",},</t>
-  </si>
-  <si>
-    <t>增援已至秋雨堡，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·秋雨堡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},</t>
-  </si>
-  <si>
-    <t>增援已至神池岭，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·神池岭</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·神池岭",nTime="10,恶人·兵符增援·神池岭;300,恶人·神池岭·兵符冷却;305,恶人·神池岭·可用兵符",nRefresh=1,key="兵符·神池岭",},</t>
-  </si>
-  <si>
-    <t>增援已至烈日岗，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·烈日岗</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·烈日岗",nTime="10,恶人·兵符增援·烈日岗;300,恶人·烈日岗·兵符冷却;305,恶人·烈日岗·可用兵符",nRefresh=1,key="兵符·烈日岗",},</t>
-  </si>
-  <si>
-    <t>增援已至大理山城，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·大理山城</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·大理山城",nTime="10,浩气·兵符增援·大理山城;300,浩气·大理山城·兵符冷却;305,浩气·大理山城·可用兵符",nRefresh=1,key="兵符·大理山城",},</t>
-  </si>
-  <si>
-    <t>增援已至千岩关，速速进攻！</t>
-  </si>
-  <si>
-    <t>浩气·兵符增援·千岩关</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·千岩关",nTime="10,浩气·兵符增援·千岩关;300,浩气·千岩关·兵符冷却;305,浩气·千岩关·可用兵符",nRefresh=1,key="兵符·千岩关",},</t>
-  </si>
-  <si>
-    <t>增援已至扶风郡，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·扶风郡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·扶风郡",nTime="10,恶人·兵符增援·扶风郡;300,恶人·扶风郡·兵符冷却;305,恶人·扶风郡·可用兵符",nRefresh=1,key="兵符·扶风郡",},</t>
-  </si>
-  <si>
-    <t>增援已至世外坡，速速进攻！</t>
-  </si>
-  <si>
-    <t>恶人·兵符增援·世外坡</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=8478,nFrame=8,szName="恶人·兵符增援·世外坡",nTime="10,恶人·兵符增援·世外坡;300,恶人·世外坡·兵符冷却;305,恶人·世外坡·可用兵符",nRefresh=1,key="兵符·世外坡",},</t>
-  </si>
-  <si>
-    <t>{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},</t>
   </si>
   <si>
     <t>(.-)侠士([打开关闭]+)了【(.-)据点】城门！</t>
@@ -9261,7 +9264,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1791818579000,</v>
+        <v>nTimeStamp = 1792134736000,</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>11</v>
@@ -11004,10 +11007,10 @@
         <v>1776</v>
       </c>
       <c r="B3" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="C3" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -11015,10 +11018,10 @@
         <v>1782</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="C4" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -11026,10 +11029,10 @@
         <v>1791</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11037,10 +11040,10 @@
         <v>1795</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11048,10 +11051,10 @@
         <v>1801</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11059,10 +11062,10 @@
         <v>1805</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -11070,10 +11073,10 @@
         <v>1816</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -11081,10 +11084,10 @@
         <v>1820</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11092,10 +11095,10 @@
         <v>1826</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -11103,10 +11106,10 @@
         <v>1830</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -11114,10 +11117,10 @@
         <v>1834</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -11125,10 +11128,10 @@
         <v>1838</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -11136,10 +11139,10 @@
         <v>1844</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -11147,10 +11150,10 @@
         <v>1848</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11158,10 +11161,10 @@
         <v>1852</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -11169,10 +11172,10 @@
         <v>1856</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -11180,10 +11183,10 @@
         <v>1862</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -11191,10 +11194,10 @@
         <v>1866</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -11202,10 +11205,10 @@
         <v>1872</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -11213,10 +11216,10 @@
         <v>1876</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -11224,10 +11227,10 @@
         <v>1880</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -11235,10 +11238,10 @@
         <v>1884</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -11246,10 +11249,10 @@
         <v>1894</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -11257,10 +11260,10 @@
         <v>1898</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -11268,10 +11271,10 @@
         <v>1902</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -11279,10 +11282,10 @@
         <v>1906</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -11290,10 +11293,10 @@
         <v>1918</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -11301,10 +11304,10 @@
         <v>1922</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
     </row>
   </sheetData>
@@ -37584,7 +37587,7 @@
       </c>
       <c r="V120" t="str">
         <f t="shared" si="19"/>
-        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
+        <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【{$1}·离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W120" t="s">
         <v>2227</v>
@@ -37834,7 +37837,7 @@
         <v>30</v>
       </c>
       <c r="V131" t="str">
-        <f t="shared" ref="V131:V177" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V131:V162" si="20">IF(ISBLANK(B131)=FALSE,IF(ISBLANK(B130),"},["&amp;B131&amp;"]={","["&amp;B131&amp;"]={"),IF(AND(ISBLANK(B131),ISBLANK(D131),ISBLANK(N131),ISBLANK(O131),OR(ISBLANK(B130)=FALSE,ISBLANK(D130)=FALSE,ISBLANK(N130)=FALSE,ISBLANK(O130)=FALSE)),"},},}",IF(ISBLANK(D131),"","{szContent="""&amp;D131&amp;""","&amp;IF(C131&lt;&gt;"","szTarget="""&amp;C131&amp;""",","")&amp;IF(E131&lt;&gt;"","szNote="""&amp;E131&amp;""",","")&amp;IF(M131&lt;&gt;"","col={"&amp;M131&amp;"},","")&amp;IF(N131&gt;0,"bSearch=true,","")&amp;IF(O131&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P131&gt;0,"szVoice="""&amp;P131&amp;""",","")&amp;IF(Q131&gt;0,"bTeamChannel=true,","")&amp;IF(R131&gt;0,"bWhisperChannel=true,","")&amp;IF(S131&gt;0,"bCenterAlarm=true,","")&amp;IF(T131&gt;0,"bScreenHead=true,","")&amp;IF(U131&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W131&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W131:AAH131)&amp;"},","")&amp;"},")))</f>
         <v>},[30]={</v>
       </c>
     </row>
@@ -38432,7 +38435,7 @@
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W159" t="s">
-        <v>2227</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:27">
@@ -38526,10 +38529,10 @@
         <v>1992</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="E163" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="M163" t="s">
         <v>2003</v>
@@ -38541,17 +38544,17 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W163" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="X163" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="Y163" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="164" spans="1:27">
@@ -38562,7 +38565,7 @@
         <v>656</v>
       </c>
       <c r="V164" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B164)=FALSE,IF(ISBLANK(B163),"},["&amp;B164&amp;"]={","["&amp;B164&amp;"]={"),IF(AND(ISBLANK(B164),ISBLANK(D164),ISBLANK(N164),ISBLANK(O164),OR(ISBLANK(B163)=FALSE,ISBLANK(D163)=FALSE,ISBLANK(N163)=FALSE,ISBLANK(O163)=FALSE)),"},},}",IF(ISBLANK(D164),"","{szContent="""&amp;D164&amp;""","&amp;IF(C164&lt;&gt;"","szTarget="""&amp;C164&amp;""",","")&amp;IF(E164&lt;&gt;"","szNote="""&amp;E164&amp;""",","")&amp;IF(M164&lt;&gt;"","col={"&amp;M164&amp;"},","")&amp;IF(N164&gt;0,"bSearch=true,","")&amp;IF(O164&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P164&gt;0,"szVoice="""&amp;P164&amp;""",","")&amp;IF(Q164&gt;0,"bTeamChannel=true,","")&amp;IF(R164&gt;0,"bWhisperChannel=true,","")&amp;IF(S164&gt;0,"bCenterAlarm=true,","")&amp;IF(T164&gt;0,"bScreenHead=true,","")&amp;IF(U164&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W164&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W164:AAH164)&amp;"},","")&amp;"},")))</f>
         <v>},[656]={</v>
       </c>
     </row>
@@ -38577,7 +38580,7 @@
         <v>2181</v>
       </c>
       <c r="V165" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B165)=FALSE,IF(ISBLANK(B164),"},["&amp;B165&amp;"]={","["&amp;B165&amp;"]={"),IF(AND(ISBLANK(B165),ISBLANK(D165),ISBLANK(N165),ISBLANK(O165),OR(ISBLANK(B164)=FALSE,ISBLANK(D164)=FALSE,ISBLANK(N164)=FALSE,ISBLANK(O164)=FALSE)),"},},}",IF(ISBLANK(D165),"","{szContent="""&amp;D165&amp;""","&amp;IF(C165&lt;&gt;"","szTarget="""&amp;C165&amp;""",","")&amp;IF(E165&lt;&gt;"","szNote="""&amp;E165&amp;""",","")&amp;IF(M165&lt;&gt;"","col={"&amp;M165&amp;"},","")&amp;IF(N165&gt;0,"bSearch=true,","")&amp;IF(O165&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P165&gt;0,"szVoice="""&amp;P165&amp;""",","")&amp;IF(Q165&gt;0,"bTeamChannel=true,","")&amp;IF(R165&gt;0,"bWhisperChannel=true,","")&amp;IF(S165&gt;0,"bCenterAlarm=true,","")&amp;IF(T165&gt;0,"bScreenHead=true,","")&amp;IF(U165&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W165&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W165:AAH165)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="我竟然败给你们这群小辈！",szTarget="狼牙先锋首领",szNote="防冲突禁用·击退·狼牙先锋首领",[14]={},tCountdown={{nClass=-1,nIcon=3556,nFrame=1,szName="狼牙先锋首领·拾取掉落",nTime="10,狼牙先锋首领·已击退;300,狼牙先锋首领·拾取剩余;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;627,狼牙先锋首领·延迟刷新",nRefresh=2,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W165" t="s">
@@ -38601,7 +38604,7 @@
         <v>2186</v>
       </c>
       <c r="V166" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B166)=FALSE,IF(ISBLANK(B165),"},["&amp;B166&amp;"]={","["&amp;B166&amp;"]={"),IF(AND(ISBLANK(B166),ISBLANK(D166),ISBLANK(N166),ISBLANK(O166),OR(ISBLANK(B165)=FALSE,ISBLANK(D165)=FALSE,ISBLANK(N165)=FALSE,ISBLANK(O165)=FALSE)),"},},}",IF(ISBLANK(D166),"","{szContent="""&amp;D166&amp;""","&amp;IF(C166&lt;&gt;"","szTarget="""&amp;C166&amp;""",","")&amp;IF(E166&lt;&gt;"","szNote="""&amp;E166&amp;""",","")&amp;IF(M166&lt;&gt;"","col={"&amp;M166&amp;"},","")&amp;IF(N166&gt;0,"bSearch=true,","")&amp;IF(O166&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P166&gt;0,"szVoice="""&amp;P166&amp;""",","")&amp;IF(Q166&gt;0,"bTeamChannel=true,","")&amp;IF(R166&gt;0,"bWhisperChannel=true,","")&amp;IF(S166&gt;0,"bCenterAlarm=true,","")&amp;IF(T166&gt;0,"bScreenHead=true,","")&amp;IF(U166&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W166&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W166:AAH166)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="你爷爷我年轻些时候，也是翻云覆雨的江湖响当当一号人物！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话2",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=14,nIcon=13,nTime=-1,szName="金水镇",nRefresh=7200,key="金水镇",},{nClass=14,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=7200,key="巴陵县",},{nClass=14,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=7200,key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-1,szName="南屏山",nRefresh=7200,key="南屏山",},{nClass=14,nIcon=13,nTime=-1,szName="昆仑",nRefresh=7200,key="昆仑",},{nClass=14,nIcon=13,nTime=-1,szName="白龙口",nRefresh=7200,key="白龙口",},{nClass=14,nIcon=13,nTime=-1,szName="无量山",nRefresh=7200,key="无量山",},{nClass=14,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=7200,key="黑龙沼",},{nClass=14,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=7200,key="阴山大草原",},{nClass=14,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=7200,key="黑戈壁",},{nClass=14,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=7200,key="鲲鹏岛",},},},</v>
       </c>
       <c r="W166" t="s">
@@ -38625,7 +38628,7 @@
         <v>2189</v>
       </c>
       <c r="V167" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B167)=FALSE,IF(ISBLANK(B166),"},["&amp;B167&amp;"]={","["&amp;B167&amp;"]={"),IF(AND(ISBLANK(B167),ISBLANK(D167),ISBLANK(N167),ISBLANK(O167),OR(ISBLANK(B166)=FALSE,ISBLANK(D166)=FALSE,ISBLANK(N166)=FALSE,ISBLANK(O166)=FALSE)),"},},}",IF(ISBLANK(D167),"","{szContent="""&amp;D167&amp;""","&amp;IF(C167&lt;&gt;"","szTarget="""&amp;C167&amp;""",","")&amp;IF(E167&lt;&gt;"","szNote="""&amp;E167&amp;""",","")&amp;IF(M167&lt;&gt;"","col={"&amp;M167&amp;"},","")&amp;IF(N167&gt;0,"bSearch=true,","")&amp;IF(O167&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P167&gt;0,"szVoice="""&amp;P167&amp;""",","")&amp;IF(Q167&gt;0,"bTeamChannel=true,","")&amp;IF(R167&gt;0,"bWhisperChannel=true,","")&amp;IF(S167&gt;0,"bCenterAlarm=true,","")&amp;IF(T167&gt;0,"bScreenHead=true,","")&amp;IF(U167&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W167&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W167:AAH167)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="哼，打扰本大爷休息！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·刷新喊话1",[14]={},tCountdown={{nClass=14,nIcon=3556,nFrame=1,szName="狼牙先锋首领·已经刷新",nTime=10,nRefresh=120,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W167" t="s">
@@ -38643,7 +38646,7 @@
         <v>2191</v>
       </c>
       <c r="V168" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B168)=FALSE,IF(ISBLANK(B167),"},["&amp;B168&amp;"]={","["&amp;B168&amp;"]={"),IF(AND(ISBLANK(B168),ISBLANK(D168),ISBLANK(N168),ISBLANK(O168),OR(ISBLANK(B167)=FALSE,ISBLANK(D167)=FALSE,ISBLANK(N167)=FALSE,ISBLANK(O167)=FALSE)),"},},}",IF(ISBLANK(D168),"","{szContent="""&amp;D168&amp;""","&amp;IF(C168&lt;&gt;"","szTarget="""&amp;C168&amp;""",","")&amp;IF(E168&lt;&gt;"","szNote="""&amp;E168&amp;""",","")&amp;IF(M168&lt;&gt;"","col={"&amp;M168&amp;"},","")&amp;IF(N168&gt;0,"bSearch=true,","")&amp;IF(O168&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P168&gt;0,"szVoice="""&amp;P168&amp;""",","")&amp;IF(Q168&gt;0,"bTeamChannel=true,","")&amp;IF(R168&gt;0,"bWhisperChannel=true,","")&amp;IF(S168&gt;0,"bCenterAlarm=true,","")&amp;IF(T168&gt;0,"bScreenHead=true,","")&amp;IF(U168&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W168&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W168:AAH168)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="哼，还有要事要办，今日收获甚多，来日定多来领略你们的武功！",szTarget="狼牙先锋首领",szNote="狼牙先锋首领·攻防结束",[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领·离开",nTime=0,key="狼牙先锋首领",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="W168" t="s">
@@ -38666,7 +38669,7 @@
         <v>2003</v>
       </c>
       <c r="V169" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B169)=FALSE,IF(ISBLANK(B168),"},["&amp;B169&amp;"]={","["&amp;B169&amp;"]={"),IF(AND(ISBLANK(B169),ISBLANK(D169),ISBLANK(N169),ISBLANK(O169),OR(ISBLANK(B168)=FALSE,ISBLANK(D168)=FALSE,ISBLANK(N168)=FALSE,ISBLANK(O168)=FALSE)),"},},}",IF(ISBLANK(D169),"","{szContent="""&amp;D169&amp;""","&amp;IF(C169&lt;&gt;"","szTarget="""&amp;C169&amp;""",","")&amp;IF(E169&lt;&gt;"","szNote="""&amp;E169&amp;""",","")&amp;IF(M169&lt;&gt;"","col={"&amp;M169&amp;"},","")&amp;IF(N169&gt;0,"bSearch=true,","")&amp;IF(O169&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P169&gt;0,"szVoice="""&amp;P169&amp;""",","")&amp;IF(Q169&gt;0,"bTeamChannel=true,","")&amp;IF(R169&gt;0,"bWhisperChannel=true,","")&amp;IF(S169&gt;0,"bCenterAlarm=true,","")&amp;IF(T169&gt;0,"bScreenHead=true,","")&amp;IF(U169&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W169&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W169:AAH169)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="你已经离开据点，10秒内未进入据点，则据点旗帜重置。",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=592,nFrame=2,szName="据点大旗·重置剩余",nTime=10,key="据点大旗·旗手提示",},},},</v>
       </c>
       <c r="W169" t="s">
@@ -38700,7 +38703,7 @@
         <v>1</v>
       </c>
       <c r="V170" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B170)=FALSE,IF(ISBLANK(B169),"},["&amp;B170&amp;"]={","["&amp;B170&amp;"]={"),IF(AND(ISBLANK(B170),ISBLANK(D170),ISBLANK(N170),ISBLANK(O170),OR(ISBLANK(B169)=FALSE,ISBLANK(D169)=FALSE,ISBLANK(N169)=FALSE,ISBLANK(O169)=FALSE)),"},},}",IF(ISBLANK(D170),"","{szContent="""&amp;D170&amp;""","&amp;IF(C170&lt;&gt;"","szTarget="""&amp;C170&amp;""",","")&amp;IF(E170&lt;&gt;"","szNote="""&amp;E170&amp;""",","")&amp;IF(M170&lt;&gt;"","col={"&amp;M170&amp;"},","")&amp;IF(N170&gt;0,"bSearch=true,","")&amp;IF(O170&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P170&gt;0,"szVoice="""&amp;P170&amp;""",","")&amp;IF(Q170&gt;0,"bTeamChannel=true,","")&amp;IF(R170&gt;0,"bWhisperChannel=true,","")&amp;IF(S170&gt;0,"bCenterAlarm=true,","")&amp;IF(T170&gt;0,"bScreenHead=true,","")&amp;IF(U170&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W170&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W170:AAH170)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="系统检测您有挂机行为，如果长期维持该状态将被传送出图！",szNote="挂机检测·快活跃起来",col={255,50,255,},[14]={szVoice="DianMing_P",bTeamChannel=true,bWhisperChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=2,szName="挂机检测·动一动",nTime=30,key="挂机检测",},},},</v>
       </c>
       <c r="W170" t="s">
@@ -38730,7 +38733,7 @@
         <v>1</v>
       </c>
       <c r="V171" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B171)=FALSE,IF(ISBLANK(B170),"},["&amp;B171&amp;"]={","["&amp;B171&amp;"]={"),IF(AND(ISBLANK(B171),ISBLANK(D171),ISBLANK(N171),ISBLANK(O171),OR(ISBLANK(B170)=FALSE,ISBLANK(D170)=FALSE,ISBLANK(N170)=FALSE,ISBLANK(O170)=FALSE)),"},},}",IF(ISBLANK(D171),"","{szContent="""&amp;D171&amp;""","&amp;IF(C171&lt;&gt;"","szTarget="""&amp;C171&amp;""",","")&amp;IF(E171&lt;&gt;"","szNote="""&amp;E171&amp;""",","")&amp;IF(M171&lt;&gt;"","col={"&amp;M171&amp;"},","")&amp;IF(N171&gt;0,"bSearch=true,","")&amp;IF(O171&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P171&gt;0,"szVoice="""&amp;P171&amp;""",","")&amp;IF(Q171&gt;0,"bTeamChannel=true,","")&amp;IF(R171&gt;0,"bWhisperChannel=true,","")&amp;IF(S171&gt;0,"bCenterAlarm=true,","")&amp;IF(T171&gt;0,"bScreenHead=true,","")&amp;IF(U171&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W171&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W171:AAH171)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="^【(.-)】据点大旗受损，获得(%d-)层易伤，当前总计【(%d-)层易伤】！",szTarget="%",szNote="【{$1}】大旗·易伤{$3}层",col={255,50,255,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=16834,nFrame=1,szName="大旗易伤",nTime=-1,nRefresh=2,key="大旗易伤",},{nClass=14,nIcon=16834,nFrame=1,szName="【{$1}】大旗·易伤{$3}层",nTime="60,【{$1}】大旗·易伤{$3}层;62,【{$1}】大旗·易伤冷却结束",nRefresh=0,key="{$1}·大旗易伤",},},},</v>
       </c>
       <c r="W171" t="s">
@@ -38760,11 +38763,11 @@
         <v>1</v>
       </c>
       <c r="V172" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B172)=FALSE,IF(ISBLANK(B171),"},["&amp;B172&amp;"]={","["&amp;B172&amp;"]={"),IF(AND(ISBLANK(B172),ISBLANK(D172),ISBLANK(N172),ISBLANK(O172),OR(ISBLANK(B171)=FALSE,ISBLANK(D171)=FALSE,ISBLANK(N171)=FALSE,ISBLANK(O171)=FALSE)),"},},}",IF(ISBLANK(D172),"","{szContent="""&amp;D172&amp;""","&amp;IF(C172&lt;&gt;"","szTarget="""&amp;C172&amp;""",","")&amp;IF(E172&lt;&gt;"","szNote="""&amp;E172&amp;""",","")&amp;IF(M172&lt;&gt;"","col={"&amp;M172&amp;"},","")&amp;IF(N172&gt;0,"bSearch=true,","")&amp;IF(O172&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P172&gt;0,"szVoice="""&amp;P172&amp;""",","")&amp;IF(Q172&gt;0,"bTeamChannel=true,","")&amp;IF(R172&gt;0,"bWhisperChannel=true,","")&amp;IF(S172&gt;0,"bCenterAlarm=true,","")&amp;IF(T172&gt;0,"bScreenHead=true,","")&amp;IF(U172&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W172&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W172:AAH172)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="(.-)离开据点过久，或在原地五尺范围内盘踞超过五分钟，旗帜重置！",szTarget="%",szNote="[{$1}]·离开据点·大旗重置",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=592,nFrame=4,szName="【离开据点】大旗重置",nTime=180,key="离开据点·大旗重置",},},},</v>
       </c>
       <c r="W172" t="s">
-        <v>2227</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:27">
@@ -38784,7 +38787,7 @@
         <v>1</v>
       </c>
       <c r="V173" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B173)=FALSE,IF(ISBLANK(B172),"},["&amp;B173&amp;"]={","["&amp;B173&amp;"]={"),IF(AND(ISBLANK(B173),ISBLANK(D173),ISBLANK(N173),ISBLANK(O173),OR(ISBLANK(B172)=FALSE,ISBLANK(D172)=FALSE,ISBLANK(N172)=FALSE,ISBLANK(O172)=FALSE)),"},},}",IF(ISBLANK(D173),"","{szContent="""&amp;D173&amp;""","&amp;IF(C173&lt;&gt;"","szTarget="""&amp;C173&amp;""",","")&amp;IF(E173&lt;&gt;"","szNote="""&amp;E173&amp;""",","")&amp;IF(M173&lt;&gt;"","col={"&amp;M173&amp;"},","")&amp;IF(N173&gt;0,"bSearch=true,","")&amp;IF(O173&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P173&gt;0,"szVoice="""&amp;P173&amp;""",","")&amp;IF(Q173&gt;0,"bTeamChannel=true,","")&amp;IF(R173&gt;0,"bWhisperChannel=true,","")&amp;IF(S173&gt;0,"bCenterAlarm=true,","")&amp;IF(T173&gt;0,"bScreenHead=true,","")&amp;IF(U173&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W173&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W173:AAH173)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="恶人谷大将",},},},</v>
       </c>
       <c r="W173" t="s">
@@ -38818,7 +38821,7 @@
         <v>1</v>
       </c>
       <c r="V174" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B174)=FALSE,IF(ISBLANK(B173),"},["&amp;B174&amp;"]={","["&amp;B174&amp;"]={"),IF(AND(ISBLANK(B174),ISBLANK(D174),ISBLANK(N174),ISBLANK(O174),OR(ISBLANK(B173)=FALSE,ISBLANK(D173)=FALSE,ISBLANK(N173)=FALSE,ISBLANK(O173)=FALSE)),"},},}",IF(ISBLANK(D174),"","{szContent="""&amp;D174&amp;""","&amp;IF(C174&lt;&gt;"","szTarget="""&amp;C174&amp;""",","")&amp;IF(E174&lt;&gt;"","szNote="""&amp;E174&amp;""",","")&amp;IF(M174&lt;&gt;"","col={"&amp;M174&amp;"},","")&amp;IF(N174&gt;0,"bSearch=true,","")&amp;IF(O174&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P174&gt;0,"szVoice="""&amp;P174&amp;""",","")&amp;IF(Q174&gt;0,"bTeamChannel=true,","")&amp;IF(R174&gt;0,"bWhisperChannel=true,","")&amp;IF(S174&gt;0,"bCenterAlarm=true,","")&amp;IF(T174&gt;0,"bScreenHead=true,","")&amp;IF(U174&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W174&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W174:AAH174)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W174" t="s">
@@ -38843,7 +38846,7 @@
         <v>1</v>
       </c>
       <c r="V175" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B175)=FALSE,IF(ISBLANK(B174),"},["&amp;B175&amp;"]={","["&amp;B175&amp;"]={"),IF(AND(ISBLANK(B175),ISBLANK(D175),ISBLANK(N175),ISBLANK(O175),OR(ISBLANK(B174)=FALSE,ISBLANK(D174)=FALSE,ISBLANK(N174)=FALSE,ISBLANK(O174)=FALSE)),"},},}",IF(ISBLANK(D175),"","{szContent="""&amp;D175&amp;""","&amp;IF(C175&lt;&gt;"","szTarget="""&amp;C175&amp;""",","")&amp;IF(E175&lt;&gt;"","szNote="""&amp;E175&amp;""",","")&amp;IF(M175&lt;&gt;"","col={"&amp;M175&amp;"},","")&amp;IF(N175&gt;0,"bSearch=true,","")&amp;IF(O175&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P175&gt;0,"szVoice="""&amp;P175&amp;""",","")&amp;IF(Q175&gt;0,"bTeamChannel=true,","")&amp;IF(R175&gt;0,"bWhisperChannel=true,","")&amp;IF(S175&gt;0,"bCenterAlarm=true,","")&amp;IF(T175&gt;0,"bScreenHead=true,","")&amp;IF(U175&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W175&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W175:AAH175)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W175" t="s">
@@ -38858,10 +38861,10 @@
         <v>1992</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="E176" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="M176" t="s">
         <v>2003</v>
@@ -38873,22 +38876,22 @@
         <v>1</v>
       </c>
       <c r="V176" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B176)=FALSE,IF(ISBLANK(B175),"},["&amp;B176&amp;"]={","["&amp;B176&amp;"]={"),IF(AND(ISBLANK(B176),ISBLANK(D176),ISBLANK(N176),ISBLANK(O176),OR(ISBLANK(B175)=FALSE,ISBLANK(D175)=FALSE,ISBLANK(N175)=FALSE,ISBLANK(O175)=FALSE)),"},},}",IF(ISBLANK(D176),"","{szContent="""&amp;D176&amp;""","&amp;IF(C176&lt;&gt;"","szTarget="""&amp;C176&amp;""",","")&amp;IF(E176&lt;&gt;"","szNote="""&amp;E176&amp;""",","")&amp;IF(M176&lt;&gt;"","col={"&amp;M176&amp;"},","")&amp;IF(N176&gt;0,"bSearch=true,","")&amp;IF(O176&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P176&gt;0,"szVoice="""&amp;P176&amp;""",","")&amp;IF(Q176&gt;0,"bTeamChannel=true,","")&amp;IF(R176&gt;0,"bWhisperChannel=true,","")&amp;IF(S176&gt;0,"bCenterAlarm=true,","")&amp;IF(T176&gt;0,"bScreenHead=true,","")&amp;IF(U176&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W176&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W176:AAH176)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W176" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="X176" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="Y176" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="177" spans="22:22">
       <c r="V177" t="str">
-        <f t="shared" si="20"/>
+        <f>IF(ISBLANK(B177)=FALSE,IF(ISBLANK(B176),"},["&amp;B177&amp;"]={","["&amp;B177&amp;"]={"),IF(AND(ISBLANK(B177),ISBLANK(D177),ISBLANK(N177),ISBLANK(O177),OR(ISBLANK(B176)=FALSE,ISBLANK(D176)=FALSE,ISBLANK(N176)=FALSE,ISBLANK(O176)=FALSE)),"},},}",IF(ISBLANK(D177),"","{szContent="""&amp;D177&amp;""","&amp;IF(C177&lt;&gt;"","szTarget="""&amp;C177&amp;""",","")&amp;IF(E177&lt;&gt;"","szNote="""&amp;E177&amp;""",","")&amp;IF(M177&lt;&gt;"","col={"&amp;M177&amp;"},","")&amp;IF(N177&gt;0,"bSearch=true,","")&amp;IF(O177&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P177&gt;0,"szVoice="""&amp;P177&amp;""",","")&amp;IF(Q177&gt;0,"bTeamChannel=true,","")&amp;IF(R177&gt;0,"bWhisperChannel=true,","")&amp;IF(S177&gt;0,"bCenterAlarm=true,","")&amp;IF(T177&gt;0,"bScreenHead=true,","")&amp;IF(U177&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W177&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W177:AAH177)&amp;"},","")&amp;"},")))</f>
         <v>},},}</v>
       </c>
     </row>
@@ -38950,10 +38953,10 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="F1" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="G1" t="s">
         <v>1970</v>
@@ -38995,7 +38998,7 @@
         <v>1981</v>
       </c>
       <c r="T1" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="2" customFormat="1" spans="1:33">
@@ -39012,16 +39015,16 @@
     </row>
     <row r="3" customFormat="1" spans="1:33">
       <c r="C3" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="D3" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="E3" t="s">
         <v>2013</v>
       </c>
       <c r="F3" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="G3" t="s">
         <v>2019</v>
@@ -39059,16 +39062,16 @@
     </row>
     <row r="4" customFormat="1" spans="1:33">
       <c r="C4" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="D4" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="E4" t="s">
         <v>2016</v>
       </c>
       <c r="F4" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="G4" t="s">
         <v>2017</v>
@@ -39106,10 +39109,10 @@
     </row>
     <row r="5" customFormat="1" spans="1:33">
       <c r="C5" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="D5" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="K5" t="s">
         <v>2003</v>
@@ -39125,15 +39128,15 @@
         <v>{szContent="侠士 [{$me}] 在拾取复活点物资时意外获得了[便携装置·神机车]。",szNote="获得·便携装置·神机车",col={255,255,100,},bSearch=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=134,nFrame=0,szName="获得·[便携装置·神机车]",nTime=10,nRefresh=1,key="交互事件",},},},</v>
       </c>
       <c r="U5" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:33">
       <c r="C6" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="D6" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="K6" t="s">
         <v>2003</v>
@@ -39146,18 +39149,18 @@
         <v>{szContent="本场浩气盟攻防即将结束，南屏山物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U6" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="C7" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="D7" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="K7" t="s">
         <v>2003</v>
@@ -39170,18 +39173,18 @@
         <v>{szContent="本场恶人谷攻防即将结束，昆仑物资运送暂且休整，等待下一场攻防开启！\n",szNote="本场攻防·即将结束",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="本场攻防·结束剩余",nTime=60,nRefresh=5,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·肖药儿",nTime=-1,key="浩气·召请CD·肖药儿",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·司徒一一",nTime=-1,key="浩气·召请CD·司徒一一",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·陶寒亭",nTime=-1,key="浩气·召请CD·陶寒亭",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·白某",nTime=-1,key="浩气·召请CD·白某",},{nClass=20,nIcon=13,nFrame=-1,szName="浩气·召请CD·米丽古丽",nTime=-1,key="浩气·召请CD·米丽古丽",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·小七",nTime=-1,key="恶人·召请CD·小七",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·游驹",nTime=-1,key="恶人·召请CD·游驹",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·张桎辕",nTime=-1,key="恶人·召请CD·张桎辕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·月弄痕",nTime=-1,key="恶人·召请CD·月弄痕",},{nClass=20,nIcon=13,nFrame=-1,szName="恶人·召请CD·司空仲平",nTime=-1,key="恶人·召请CD·司空仲平",},},},</v>
       </c>
       <c r="U7" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="8" spans="1:33">
       <c r="C8" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D8" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="K8" t="s">
         <v>2003</v>
@@ -39191,21 +39194,21 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U8" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="9" spans="1:33">
       <c r="C9" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="D9" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="K9" t="s">
         <v>2003</v>
@@ -39221,51 +39224,51 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=0,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=0,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,nRefresh=10,key="大攻防·{$1}",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,nRefresh=0,key="大攻防·奇袭场",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=0.001,nRefresh=0,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U9" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="V9" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="W9" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="X9" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="Y9" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="Z9" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="AA9" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="AB9" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="AC9" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="AD9" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="AE9" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="AF9" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:33">
       <c r="C10" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="D10" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="K10" t="s">
         <v>2003</v>
@@ -39275,39 +39278,39 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="主战场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,bHold=true,szName="主战场·平局",nTime=57,nRefresh=5,key="大攻防·主战场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U10" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="V10" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="W10" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="X10" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="Y10" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="Z10" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="AA10" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="AB10" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="C11" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="D11" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="K11" t="s">
         <v>2003</v>
@@ -39317,39 +39320,39 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手。战利品稍后开始拍卖，请留意！\n",szNote="奇袭场·平局",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,bHold=true,szName="奇袭场·平局",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="阵营活动",key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·一",key="破阵点将·一",},{nClass=20,nIcon=13,nFrame=-1,nTime=0,szName="破阵点将·二",key="破阵点将·二",},{nClass=20,nIcon=7674,szName="破阵点将·一·常驻",nTime=-1,key="破阵点将·一·常驻",},{nClass=20,nIcon=7676,szName="破阵点将·二·常驻",nTime=-1,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="牛车拾取间隔",nTime=-1,key="牛车拾取间隔",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,key="首领拾取间隔",},{nClass=20,nIcon=13,nFrame=4,szName="浩气·物资车·运达",nTime=-1,key="浩气·物资车·运达",},{nClass=20,nIcon=13,nFrame=4,szName="恶人·物资车·运达",nTime=-1,key="恶人·物资车·运达",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·月弄痕·减伤",nTime=-1,key="谢渊·月弄痕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·游驹·减伤",nTime=-1,key="谢渊·游驹·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·小七·减伤",nTime=-1,key="谢渊·小七·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·张桎辕·减伤",nTime=-1,key="谢渊·张桎辕·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·司空仲平·减伤",nTime=-1,key="谢渊·司空仲平·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·韩非池·减伤",nTime=-1,key="谢渊·韩非池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·赵紫儿·减伤",nTime=-1,key="谢渊·赵紫儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·叶镜池·减伤",nTime=-1,key="谢渊·叶镜池·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郭珠·减伤",nTime=-1,key="谢渊·郭珠·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·穆玄英·减伤",nTime=-1,key="谢渊·穆玄英·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·影·减伤",nTime=-1,key="谢渊·影·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·司徒一一·减伤",nTime=-1,key="王遗风·司徒一一·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·白某·减伤",nTime=-1,key="王遗风·白某·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·米丽古丽·减伤",nTime=-1,key="王遗风·米丽古丽·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶寒亭·减伤",nTime=-1,key="王遗风·陶寒亭·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·肖药儿·减伤",nTime=-1,key="王遗风·肖药儿·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·伊夜·减伤",nTime=-1,key="王遗风·伊夜·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·丁丁·减伤",nTime=-1,key="王遗风·丁丁·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·岳琅·减伤",nTime=-1,key="王遗风·岳琅·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·毕罗巴·减伤",nTime=-1,key="王遗风·毕罗巴·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·烟·减伤",nTime=-1,key="王遗风·烟·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·独孤修·减伤",nTime=-1,key="王遗风·独孤修·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·周峰·减伤",nTime=-1,key="谢渊·周峰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·郑鸥·减伤",nTime=-1,key="谢渊·郑鸥·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·陶杰·减伤",nTime=-1,key="谢渊·陶杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢烟客·减伤",nTime=-1,key="谢渊·谢烟客·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·张一洋·减伤",nTime=-1,key="王遗风·张一洋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·陶国栋·减伤",nTime=-1,key="王遗风·陶国栋·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·吕沛杰·减伤",nTime=-1,key="王遗风·吕沛杰·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·顾延恶·减伤",nTime=-1,key="王遗风·顾延恶·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·莫雨·减伤",nTime=-1,key="王遗风·莫雨·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="王遗风·万兽王·减伤",nTime=-1,key="王遗风·万兽王·减伤",},{nClass=20,nIcon=13,nFrame=-1,szName="谢渊·谢铃儿·减伤",nTime=-1,key="谢渊·谢铃儿·减伤",},},},</v>
       </c>
       <c r="U11" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="V11" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="W11" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="X11" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="Y11" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="Z11" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="AA11" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="AB11" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="C12" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D12" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="K12" t="s">
         <v>1999</v>
@@ -39359,15 +39362,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U12" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="C13" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D13" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K13" t="s">
         <v>1995</v>
@@ -39377,15 +39380,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U13" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="C14" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="D14" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="K14" t="s">
         <v>2003</v>
@@ -39395,15 +39398,15 @@
         <v>{szContent="驿马快报！本周浩气盟和恶人谷最终战为平手，未分胜负！\n",szNote="阵营事件·本周战平",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13354,nFrame=4,szName="阵营事件·本周战平",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U14" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="15" spans="1:33">
       <c r="C15" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="D15" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -39413,16 +39416,16 @@
         <v>{szContent="[团队监控]数据加载成功",szNote="关闭刷马等计时条",bSearch=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},{nClass=20,nIcon=2402,szName="大攻防·奇袭场",nTime=-1,nRefresh=999999,key="大攻防·奇袭场",},{nClass=-1,key="订阅提示1",nTime=15,szName="订阅提示1",nRefresh=2,nIcon=13,nFrame=5,},{nClass=-1,key="订阅提示2",nTime=15,szName="订阅提示2",nRefresh=2,nIcon=13,nFrame=6,},{nClass=-1,key="订阅提示3",nTime=15,szName="订阅提示3",nRefresh=2,nIcon=13,nFrame=7,},},},</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="V15" s="5" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="W15" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="X15" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -39439,40 +39442,40 @@
     </row>
     <row r="17" spans="1:26">
       <c r="C17" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="D17" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="T17" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【浩气盟】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U17" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="V17" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="W17" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="X17" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="Y17" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="Z17" s="5" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:26">
       <c r="C18" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="D18" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="K18" t="s">
         <v>2003</v>
@@ -39485,24 +39488,24 @@
         <v>{szContent="伊夜使用了一招围魏救赵的妙计，率众客将奇袭了浩气盟大本营，浩气盟侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U18" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="V18" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="W18" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="X18" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="19" spans="1:26">
       <c r="C19" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="D19" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="K19" t="s">
         <v>2003</v>
@@ -39515,19 +39518,19 @@
         <v>{szContent="王遗风已率恶人谷众首领抵达浩气盟，请各位恶人谷侠士速到浩气盟支援。浩气盟侠士也请速回浩气盟防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U19" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="V19" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="W19" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="Y19" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -39544,40 +39547,40 @@
     </row>
     <row r="21" spans="1:26">
       <c r="C21" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="D21" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="T21" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="你已进入地图【恶人谷】。",szNote="关闭刷马等计时条",[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·一·常驻",},{nClass=20,nIcon=1465,nFrame=-1,nTime=0.001,szName=" ",nRefresh=99999,key="破阵点将·二·常驻",},{nClass=20,nIcon=13,szName="天气事件1",nTime=-2,key="天气事件1",},{nClass=20,nIcon=13,szName="天气事件2",nTime=-2,key="天气事件2",},{nClass=20,nIcon=13,nFrame=-1,szName="阵营活动",nTime=-2,key="阵营活动",},{nClass=20,nIcon=13,nFrame=-1,szName="创意食品",nTime=-1,nRefresh=5,key="创意食品",},{nClass=20,nIcon=13,szName="速战速决",nTime=-1,nRefresh=99999,key="速战速决",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=99999,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=99999,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=99999,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=99999,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=99999,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=99999,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=99999,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=99999,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=99999,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=99999,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=99999,key="鲲鹏岛",},},},</v>
       </c>
       <c r="U21" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="V21" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="W21" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="X21" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="Y21" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="Z21" s="5" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:26">
       <c r="C22" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="D22" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="K22" t="s">
         <v>2003</v>
@@ -39590,24 +39593,24 @@
         <v>{szContent="韩非池使用了一招围魏救赵的妙计，率众客将奇袭了恶人谷大本营，恶人谷侠士也请速回救援！\n",szNote="奇袭攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=0,szName="奇袭攻防·正式开始",nTime="30,奇袭攻防·正式开始;60,建议关闭·江湖身份",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=7200,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U22" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="V22" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="W22" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="X22" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="23" spans="1:26">
       <c r="C23" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D23" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="K23" t="s">
         <v>2003</v>
@@ -39620,24 +39623,24 @@
         <v>{szContent="谢渊已率浩气盟众首领抵达恶人谷，请各位浩气盟侠士速到恶人谷支援。恶人谷侠士也请速回恶人谷防御！\n",szNote="主场攻防·正式开启",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,szName="主场攻防·正式开始",nTime="2,主场攻防·正式开始;10,建议关闭·江湖身份;900,阶段·速战速决·15分钟;905,阶段·速战速决·已经结束;910,阶段·首领出战·正在召请;1800,阶段·物资车1·出发剩余;1810,阶段·物资车1·正在出发;2700,阶段·破阵点将1·结算剩余;2710,阶段·破阵点将1·正在结算;3540,阶段·物资车2·出发剩余;3550,阶段·物资车2·正在出发;3600,阶段·首领出战·助战剩余;3605,阶段·首领出战·助战结束;5400,阶段·破阵点将2·结算剩余;5405,阶段·破阵点将2·正在结算;5410,阶段·物资车3·正在出发;7200,阶段·本场攻防·结束剩余;7205,阶段·本场攻防·正在结算;7210,阶段·本场攻防·已经结束",nRefresh=10,key="阵营活动",},{nClass=20,nIcon=13,szName="首领拾取间隔",nTime=-1,nRefresh=30,key="首领拾取间隔",},{nClass=20,nIcon=13,szName="速战速决",nTime=-2,key="速战速决",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=7200,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=7200,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="屹立不倒",key="屹立不倒",},},},</v>
       </c>
       <c r="U23" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="V23" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="W23" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="Y23" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:26">
       <c r="A24" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="B24">
         <v>-1</v>
@@ -39649,7 +39652,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:26">
       <c r="C25" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="D25"/>
       <c r="K25" t="s">
@@ -39660,18 +39663,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14890,nFrame=7,szName="主战场·浩气盟",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14889,nFrame=3,szName="奇袭场·恶人谷",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U25" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="V25" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="W25" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="26" spans="1:26">
       <c r="C26" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="K26" t="s">
         <v>1995</v>
@@ -39681,18 +39684,18 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营攻防·开始排队",nTime="1,阵营攻防·开始排队;10,阵营攻防·开始排队",nRefresh=1,key="阵营活动",},{nClass=20,nIcon=14889,nFrame=3,szName="主战场·恶人谷",nTime=60,key="大攻防·主战场",},{nClass=20,nIcon=14890,nFrame=7,szName="奇袭场·浩气盟",nTime=60,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U26" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="V26" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="W26" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="27" spans="1:26">
       <c r="C27" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="K27" t="s">
         <v>1999</v>
@@ -39702,12 +39705,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U27" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="28" spans="1:26">
       <c r="C28" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="K28" t="s">
         <v>1999</v>
@@ -39717,12 +39720,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“浩气盟”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·浩气盟·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U28" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="29" spans="1:26">
       <c r="C29" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="K29" t="s">
         <v>1995</v>
@@ -39732,12 +39735,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“中午十二点三十分”开始攻防排队，请勿在中午十二点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·12:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U29" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="30" spans="1:26">
       <c r="C30" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="K30" t="s">
         <v>1995</v>
@@ -39747,12 +39750,12 @@
         <v>{szContent="阵营攻防战即将开始，为防弄虚作假者，即将对“恶人谷”地图进行清场操作，并在“下午六点三十分”开始攻防排队，请勿在下午六点三十分前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="阵营攻防·恶人谷·18:30",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="U30" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="31" spans="1:26">
       <c r="C31" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="K31" t="s">
         <v>2003</v>
@@ -39762,12 +39765,12 @@
         <v>{szContent="据点争夺战即将开始，为防弄虚作假者，即将对据点活动地图进行清场操作，同时清空此前所有排队队列，请各阵营侠士做好准备。拥有据点地图优先进入权的帮众可提前进入地图以作防守准备，不会被清出地图。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="阵营活动",nTime="1,据点攻防·开始排队;10,据点攻防·开始排队;60,据点攻防·等待排队",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="U31" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="32" spans="1:26">
       <c r="C32" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="K32" t="s">
         <v>2003</v>
@@ -39777,15 +39780,15 @@
         <v>{szContent="为保障各位侠士的安全，浩气盟和恶人谷重新派出了守卫，在野外地图侠士重伤后复活可回到阵营复活点！\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="据点攻防·消失模式",nTime=1799.795,key="阵营活动",},},},</v>
       </c>
       <c r="U32" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="33" spans="1:22">
       <c r="C33" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="D33" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="K33" t="s">
         <v>2003</v>
@@ -39798,7 +39801,7 @@
         <v>{szContent="(.-)【(.-)】帮会的(.-)大侠成功护送祭祀物资到达(.-)据点，该据点将士备受鼓舞，战意高昂，战时必将固若金汤！",szNote="祭天·{$1}·[{$2}]·{$4}",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=8838,nFrame=1,szName="{$1}祭天·[{$2}]·{$4}",nTime=30,key="通用事件",},},},</v>
       </c>
       <c r="U33" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -39815,10 +39818,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:22">
       <c r="C35" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D35" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="K35" t="s">
         <v>2003</v>
@@ -39828,15 +39831,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U35" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:22">
       <c r="C36" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="D36" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="K36" t="s">
         <v>2003</v>
@@ -39846,15 +39849,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U36" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:22">
       <c r="C37" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D37" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="K37" t="s">
         <v>2003</v>
@@ -39864,18 +39867,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U37" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="V37" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:22">
       <c r="C38" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="D38" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="K38" t="s">
         <v>2003</v>
@@ -39885,15 +39888,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U38" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:22">
       <c r="C39" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="D39" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="K39" t="s">
         <v>2003</v>
@@ -39903,18 +39906,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U39" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="V39" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:22">
       <c r="C40" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D40" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="K40" t="s">
         <v>2003</v>
@@ -39924,18 +39927,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U40" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:22">
       <c r="C41" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D41" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="K41" t="s">
         <v>2003</v>
@@ -39945,16 +39948,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U41" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="V41" s="7"/>
     </row>
     <row r="42" customFormat="1" spans="1:22">
       <c r="C42" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D42" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="K42" t="s">
         <v>2003</v>
@@ -39964,16 +39967,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U42" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="V42" s="7"/>
     </row>
     <row r="43" customFormat="1" spans="1:22">
       <c r="C43" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D43" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="K43" t="s">
         <v>1999</v>
@@ -39983,15 +39986,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U43" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:22">
       <c r="C44" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="D44" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="K44" t="s">
         <v>1999</v>
@@ -40001,15 +40004,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U44" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:22">
       <c r="C45" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D45" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K45" t="s">
         <v>1999</v>
@@ -40019,15 +40022,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U45" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:22">
       <c r="C46" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D46" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="K46" t="s">
         <v>1995</v>
@@ -40037,15 +40040,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U46" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:22">
       <c r="C47" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D47" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="K47" t="s">
         <v>1995</v>
@@ -40055,15 +40058,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U47" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:22">
       <c r="C48" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D48" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="K48" t="s">
         <v>1995</v>
@@ -40073,15 +40076,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U48" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="49" spans="1:26">
       <c r="C49" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D49" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="K49" t="s">
         <v>2003</v>
@@ -40094,15 +40097,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U49" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="50" spans="1:26">
       <c r="C50" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D50" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="K50" t="s">
         <v>1999</v>
@@ -40112,15 +40115,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U50" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="51" spans="1:26">
       <c r="C51" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D51" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K51" t="s">
         <v>1995</v>
@@ -40130,15 +40133,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U51" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="52" spans="1:26">
       <c r="C52" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D52" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="K52" t="s">
         <v>2003</v>
@@ -40151,30 +40154,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U52" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V52" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="W52" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="X52" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="Y52" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="Z52" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="53" spans="1:26">
       <c r="C53" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D53" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="K53" t="s">
         <v>2003</v>
@@ -40187,19 +40190,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U53" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="V53" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="W53" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="X53" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="Y53" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="54" s="2" customFormat="1" spans="1:26">
@@ -40216,10 +40219,10 @@
     </row>
     <row r="55" spans="1:26">
       <c r="C55" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D55" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="K55" t="s">
         <v>2003</v>
@@ -40229,15 +40232,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U55" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:26">
       <c r="C56" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="D56" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="K56" t="s">
         <v>2003</v>
@@ -40247,12 +40250,12 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U56" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:26">
       <c r="C57" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="D57" t="s">
         <v>2196</v>
@@ -40265,15 +40268,15 @@
         <v>{szContent="前线据点之争已经打响，争夺正式开始，沙盘地图（CTRL + M）绘有详细战略意图，谁将称霸中原，我们拭目以待！\n",szNote="据点攻防·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·正式开始",nTime=10,key="阵营活动",},},},</v>
       </c>
       <c r="U57" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:26">
       <c r="C58" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D58" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="K58" t="s">
         <v>2003</v>
@@ -40283,18 +40286,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U58" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="V58" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="59" spans="1:26">
       <c r="C59" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="D59" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="K59" t="s">
         <v>2003</v>
@@ -40304,18 +40307,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U59" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="V59" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:26">
       <c r="C60" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D60" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="K60" t="s">
         <v>2003</v>
@@ -40325,24 +40328,24 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=0,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=13,szName="狼牙先锋首领",nTime=0,key="狼牙先锋首领",},{nClass=20,nIcon=13,szName="离开据点·大旗重置",nTime=0,key="离开据点·大旗重置",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U60" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="V60" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="W60" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:26">
       <c r="C61" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D61" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="K61" t="s">
         <v>1999</v>
@@ -40352,15 +40355,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U61" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:26">
       <c r="C62" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="D62" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="K62" t="s">
         <v>1999</v>
@@ -40370,15 +40373,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U62" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:26">
       <c r="C63" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D63" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K63" t="s">
         <v>1999</v>
@@ -40388,15 +40391,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U63" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:26">
       <c r="C64" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D64" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="K64" t="s">
         <v>1995</v>
@@ -40406,15 +40409,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U64" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:26">
       <c r="C65" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D65" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="K65" t="s">
         <v>1995</v>
@@ -40424,15 +40427,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U65" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:26">
       <c r="C66" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D66" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="K66" t="s">
         <v>1995</v>
@@ -40442,15 +40445,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U66" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:26">
       <c r="C67" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D67" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="K67" t="s">
         <v>2003</v>
@@ -40463,15 +40466,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U67" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:26">
       <c r="C68" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D68" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="K68" t="s">
         <v>2003</v>
@@ -40481,16 +40484,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U68" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="V68" s="7"/>
     </row>
     <row r="69" spans="1:26">
       <c r="C69" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D69" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="K69" t="s">
         <v>2003</v>
@@ -40500,21 +40503,21 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=20,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=20,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=20,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=20,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=20,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=20,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=20,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=20,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=20,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=20,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="U69" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="V69" s="4" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="W69" s="4" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="70" spans="1:26">
       <c r="C70" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D70" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="K70" t="s">
         <v>2003</v>
@@ -40529,10 +40532,10 @@
     </row>
     <row r="71" spans="1:26">
       <c r="C71" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D71" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="K71" t="s">
         <v>1999</v>
@@ -40542,15 +40545,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U71" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="72" spans="1:26">
       <c r="C72" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D72" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K72" t="s">
         <v>1995</v>
@@ -40560,15 +40563,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U72" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:26">
       <c r="C73" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D73" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="K73" t="s">
         <v>2003</v>
@@ -40581,30 +40584,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U73" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V73" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="W73" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="X73" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="Y73" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="Z73" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:26">
       <c r="C74" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D74" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="K74" t="s">
         <v>2003</v>
@@ -40617,19 +40620,19 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,key="{$3}·恶人大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气占领",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人占领",},{nClass=20,nIcon=13,szName="{$3}·{$1}占领",nTime=-1,key="{$3}·{$1}占领",},},},</v>
       </c>
       <c r="U74" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="V74" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="W74" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="X74" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="Y74" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:26">
@@ -40646,10 +40649,10 @@
     </row>
     <row r="76" customFormat="1" spans="1:26">
       <c r="C76" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="D76" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="K76" t="s">
         <v>2003</v>
@@ -40662,19 +40665,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U76" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="V76" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="W76" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="X76" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="Y76" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:26">
@@ -40691,10 +40694,10 @@
     </row>
     <row r="78" customFormat="1" spans="1:26">
       <c r="C78" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D78" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="K78" t="s">
         <v>2003</v>
@@ -40704,15 +40707,15 @@
         <v>{szContent="阵营攻防首领战奇袭场分线已经开启，现可前往本日奇袭场分线参与争夺，也可通过主城战场区分线接引人前往各个奇袭场分线参与。\n",szNote="阵营攻防·奇袭场·开启分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·开启分线",nTime=30,nRefresh=10,key="分流活动",},},},</v>
       </c>
       <c r="U78" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:26">
       <c r="C79" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="D79" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="K79" t="s">
         <v>2003</v>
@@ -40722,15 +40725,15 @@
         <v>{szContent="阵营攻防首领战紧张火热，本服今日无奇袭场分线模式，请侠士速速前往主战场及奇袭场参与活动。\n",szNote="阵营攻防·奇袭场·未开分线",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="攻防·奇袭场·未开分线",nTime=30,key="分流活动",},},},</v>
       </c>
       <c r="U79" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:26">
       <c r="C80" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D80" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="K80" t="s">
         <v>2003</v>
@@ -40740,18 +40743,18 @@
         <v>{szContent="逐鹿中原前线战况空前激烈，位于阴山大草原的分线据点争夺将于5分钟后开启！未能进入前线据点争夺场景的侠士可从沙盘地图（Ctrl + M）动态分线入口，或主城战场区小曾和小珍处进入分线场景。\n",szNote="据点攻防·阴山大草原·开启分线·5分钟",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分线开启",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U80" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="V80" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="3:26">
       <c r="C81" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="D81" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="K81" t="s">
         <v>2003</v>
@@ -40761,15 +40764,15 @@
         <v>{szContent="前线战况空前激烈！未能进入前线据点争夺场景参与战斗的侠士，可前往阴山大草原助本阵营后方物资运送一臂之力！只需完成增援任务，也可以参与本日逐鹿中原结算奖励发放。\n",szNote="据点攻防·阴山大草原",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·分流",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U81" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="3:26">
       <c r="C82" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="D82" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="K82" t="s">
         <v>2003</v>
@@ -40779,18 +40782,18 @@
         <v>{szContent="阴山大草原·分线据点争夺正式开始，场景内交通已中断。\n",szNote="据点攻防·阴山大草原·分线·正式开始",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,szName="分流活动",nTime=-2,key="分流活动",},{nClass=20,nIcon=3536,nFrame=4,szName="小攻防·阴山大草原·正式开始",nTime=10,nRefresh=3600,key="分流活动",},},},</v>
       </c>
       <c r="U82" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="V82" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="3:26">
       <c r="C83" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D83" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="K83" t="s">
         <v>2003</v>
@@ -40800,18 +40803,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U83" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="V83" s="3" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="3:26">
       <c r="C84" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D84" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="K84" t="s">
         <v>1999</v>
@@ -40821,15 +40824,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U84" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="3:26">
       <c r="C85" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="D85" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="K85" t="s">
         <v>1999</v>
@@ -40839,15 +40842,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U85" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="3:26">
       <c r="C86" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D86" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K86" t="s">
         <v>1999</v>
@@ -40857,15 +40860,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U86" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="3:26">
       <c r="C87" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D87" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="K87" t="s">
         <v>1995</v>
@@ -40875,15 +40878,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U87" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="3:26">
       <c r="C88" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D88" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="K88" t="s">
         <v>1995</v>
@@ -40893,15 +40896,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U88" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="3:26">
       <c r="C89" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D89" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="K89" t="s">
         <v>1995</v>
@@ -40911,15 +40914,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U89" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="3:26">
       <c r="C90" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D90" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="K90" t="s">
         <v>2003</v>
@@ -40932,15 +40935,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U90" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="3:26">
       <c r="C91" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D91" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="K91" t="s">
         <v>2003</v>
@@ -40950,16 +40953,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U91" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="V91" s="7"/>
     </row>
     <row r="92" customFormat="1" spans="3:26">
       <c r="C92" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D92" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="K92" t="s">
         <v>2003</v>
@@ -40969,16 +40972,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U92" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="V92" s="7"/>
     </row>
     <row r="93" customFormat="1" spans="3:26">
       <c r="C93" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D93" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="K93" t="s">
         <v>1999</v>
@@ -40988,15 +40991,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U93" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="3:26">
       <c r="C94" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D94" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K94" t="s">
         <v>1995</v>
@@ -41006,15 +41009,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U94" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="3:26">
       <c r="C95" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D95" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="K95" t="s">
         <v>2003</v>
@@ -41027,30 +41030,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U95" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V95" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="W95" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="X95" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="Y95" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="Z95" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="3:26">
       <c r="C96" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D96" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="K96" t="s">
         <v>2003</v>
@@ -41063,24 +41066,24 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U96" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="V96" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="W96" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="X96" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="Y96" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:22">
       <c r="A97" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="B97">
         <v>-3</v>
@@ -41092,7 +41095,7 @@
     </row>
     <row r="98" customFormat="1" spans="1:22">
       <c r="C98" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="K98" t="s">
         <v>1995</v>
@@ -41102,12 +41105,12 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往恶人谷地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=3,szName="主战场·恶人谷",nTime="1,阵营攻防·开始排队·恶人谷;10,阵营攻防·开始排队·恶人谷",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U98" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:22">
       <c r="C99" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="K99" t="s">
         <v>1999</v>
@@ -41117,7 +41120,7 @@
         <v>{szContent="阵营攻防排队正式开始，同时清空此前所有排队队列，尚未排队的侠士们速速前往浩气盟地图参与排队，亦可与主城战场的冷倪之、冷允之对话进行排队。\n",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=7,szName="主战场·浩气盟",nTime="1,阵营攻防·开始排队·浩气盟;10,阵营攻防·开始排队·浩气盟",nRefresh=1,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U99" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:22">
@@ -41134,10 +41137,10 @@
     </row>
     <row r="101" customFormat="1" spans="1:22">
       <c r="C101" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="D101" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="K101" t="s">
         <v>2003</v>
@@ -41147,16 +41150,16 @@
         <v>{szContent="正在拍卖攻防掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="阵营攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="阵营攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U101" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="V101" s="7"/>
     </row>
     <row r="102" customFormat="1" spans="1:22">
       <c r="C102" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D102" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="K102" t="s">
         <v>2003</v>
@@ -41166,16 +41169,16 @@
         <v>{szContent="正在拍卖逐鹿中原掉落的稀有物品，其中通常有当前最高品质附魔、绝世稀有坐骑、玄晶等，阵营侠士们切勿错过！\n",szNote="据点攻防·拍卖掉落",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=0,szName="据点攻防·拍卖掉落",nTime=30,key="拍卖分红",},},},</v>
       </c>
       <c r="U102" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="V102" s="7"/>
     </row>
     <row r="103" customFormat="1" spans="1:22">
       <c r="C103" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D103" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="K103" t="s">
         <v>2003</v>
@@ -41185,18 +41188,18 @@
         <v>{szContent="据点争夺已结束，所有交通已恢复。\n",szNote="据点攻防·已经结束",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=3536,nFrame=3,szName="据点攻防·活动结束",nTime=5,key="阵营活动",},{nClass=20,nIcon=4837,szName="武王城·浩气大旗",nTime=-1,key="武王城·浩气大旗",},{nClass=20,nIcon=4837,szName="凛风堡·浩气大旗",nTime=-1,key="凛风堡·浩气大旗",},{nClass=20,nIcon=4837,szName="盘龙坞·浩气大旗",nTime=-1,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=4837,szName="逐鹿坪·浩气大旗",nTime=-1,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=4837,szName="龙门镇·浩气大旗",nTime=-1,key="龙门镇·浩气大旗",},{nClass=20,nIcon=4837,szName="飞沙关·浩气大旗",nTime=-1,key="飞沙关·浩气大旗",},{nClass=20,nIcon=4837,szName="红莲岗·浩气大旗",nTime=-1,key="红莲岗·浩气大旗",},{nClass=20,nIcon=4837,szName="秋雨堡·浩气大旗",nTime=-1,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=4837,szName="金门关·浩气大旗",nTime=-1,key="金门关·浩气大旗",},{nClass=20,nIcon=4837,szName="青云坞·浩气大旗",nTime=-1,key="青云坞·浩气大旗",},{nClass=20,nIcon=4837,szName="激流坞·浩气大旗",nTime=-1,key="激流坞·浩气大旗",},{nClass=20,nIcon=4837,szName="不空关·浩气大旗",nTime=-1,key="不空关·浩气大旗",},{nClass=20,nIcon=4837,szName="日月崖·浩气大旗",nTime=-1,key="日月崖·浩气大旗",},{nClass=20,nIcon=4837,szName="卧龙坡·浩气大旗",nTime=-1,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=4837,szName="霜戈堡·浩气大旗",nTime=-1,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=4837,szName="澜沧城·浩气大旗",nTime=-1,key="澜沧城·浩气大旗",},{nClass=20,nIcon=4837,szName="神池岭·浩气大旗",nTime=-1,key="神池岭·浩气大旗",},{nClass=20,nIcon=4837,szName="烈日岗·浩气大旗",nTime=-1,key="烈日岗·浩气大旗",},{nClass=20,nIcon=4837,szName="凤鸣堡·浩气大旗",nTime=-1,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=4837,szName="惊虬谷·浩气大旗",nTime=-1,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=4837,szName="大理山城·浩气大旗",nTime=-1,key="大理山城·浩气大旗",},{nClass=20,nIcon=4837,szName="千岩关·浩气大旗",nTime=-1,key="千岩关·浩气大旗",},{nClass=20,nIcon=4837,szName="枫湖寨·浩气大旗",nTime=-1,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=4837,szName="啖杏林·浩气大旗",nTime=-1,key="啖杏林·浩气大旗",},{nClass=20,nIcon=4837,szName="扶风郡·浩气大旗",nTime=-1,key="扶风郡·浩气大旗",},{nClass=20,nIcon=4837,szName="世外坡·浩气大旗",nTime=-1,key="世外坡·浩气大旗",},{nClass=20,nIcon=4838,szName="武王城·恶人大旗",nTime=-1,key="武王城·恶人大旗",},{nClass=20,nIcon=4838,szName="凛风堡·恶人大旗",nTime=-1,key="凛风堡·恶人大旗",},{nClass=20,nIcon=4838,szName="盘龙坞·恶人大旗",nTime=-1,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=4838,szName="逐鹿坪·恶人大旗",nTime=-1,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=4838,szName="龙门镇·恶人大旗",nTime=-1,key="龙门镇·恶人大旗",},{nClass=20,nIcon=4838,szName="飞沙关·恶人大旗",nTime=-1,key="飞沙关·恶人大旗",},{nClass=20,nIcon=4838,szName="红莲岗·恶人大旗",nTime=-1,key="红莲岗·恶人大旗",},{nClass=20,nIcon=4838,szName="秋雨堡·恶人大旗",nTime=-1,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=4838,szName="金门关·恶人大旗",nTime=-1,key="金门关·恶人大旗",},{nClass=20,nIcon=4838,szName="青云坞·恶人大旗",nTime=-1,key="青云坞·恶人大旗",},{nClass=20,nIcon=4838,szName="激流坞·恶人大旗",nTime=-1,key="激流坞·恶人大旗",},{nClass=20,nIcon=4838,szName="不空关·恶人大旗",nTime=-1,key="不空关·恶人大旗",},{nClass=20,nIcon=4838,szName="日月崖·恶人大旗",nTime=-1,key="日月崖·恶人大旗",},{nClass=20,nIcon=4838,szName="卧龙坡·恶人大旗",nTime=-1,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=4838,szName="霜戈堡·恶人大旗",nTime=-1,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=4838,szName="澜沧城·恶人大旗",nTime=-1,key="澜沧城·恶人大旗",},{nClass=20,nIcon=4838,szName="神池岭·恶人大旗",nTime=-1,key="神池岭·恶人大旗",},{nClass=20,nIcon=4838,szName="烈日岗·恶人大旗",nTime=-1,key="烈日岗·恶人大旗",},{nClass=20,nIcon=4838,szName="凤鸣堡·恶人大旗",nTime=-1,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=4838,szName="惊虬谷·恶人大旗",nTime=-1,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=4838,szName="大理山城·恶人大旗",nTime=-1,key="大理山城·恶人大旗",},{nClass=20,nIcon=4838,szName="千岩关·恶人大旗",nTime=-1,key="千岩关·恶人大旗",},{nClass=20,nIcon=4838,szName="枫湖寨·恶人大旗",nTime=-1,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=4838,szName="啖杏林·恶人大旗",nTime=-1,key="啖杏林·恶人大旗",},{nClass=20,nIcon=4838,szName="扶风郡·恶人大旗",nTime=-1,key="扶风郡·恶人大旗",},{nClass=20,nIcon=4838,szName="世外坡·恶人大旗",nTime=-1,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U103" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="V103" s="3" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:22">
       <c r="C104" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D104" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="K104" t="s">
         <v>1999</v>
@@ -41206,15 +41209,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，险胜！浩气盟士气大涨500分！\n",szNote="据点攻防·浩气盟·险胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U104" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:22">
       <c r="C105" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="D105" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="K105" t="s">
         <v>1999</v>
@@ -41224,15 +41227,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，大胜！浩气盟士气大涨600分！\n",szNote="据点攻防·浩气盟·大胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U105" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:22">
       <c r="C106" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="D106" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="K106" t="s">
         <v>1999</v>
@@ -41242,15 +41245,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是浩气盟略胜一筹，完胜！浩气盟士气大涨700分！\n",szNote="据点攻防·浩气盟·完胜",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·浩气盟·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U106" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:22">
       <c r="C107" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D107" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="K107" t="s">
         <v>1995</v>
@@ -41260,15 +41263,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，险胜！恶人谷士气大涨500分！\n",szNote="据点攻防·恶人谷·险胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·险胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U107" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:22">
       <c r="C108" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="D108" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="K108" t="s">
         <v>1995</v>
@@ -41278,15 +41281,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，大胜！恶人谷士气大涨600分！\n",szNote="据点攻防·恶人谷·大胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·大胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U108" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:22">
       <c r="C109" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D109" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="K109" t="s">
         <v>1995</v>
@@ -41296,15 +41299,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，但终是恶人谷略胜一筹，完胜！恶人谷士气大涨700分！\n",szNote="据点攻防·恶人谷·完胜",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·恶人谷·完胜",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U109" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:22">
       <c r="C110" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="D110" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="K110" t="s">
         <v>2003</v>
@@ -41317,15 +41320,15 @@
         <v>{szContent="本场战役已结束，双方战事惨烈，未分胜负！双方士气各涨500分！\n",szNote="据点攻防·平局",col={255,255,100,},[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="据点攻防·平局",nTime=30,nRefresh=2,key="阵营活动",},},},</v>
       </c>
       <c r="U110" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:22">
       <c r="C111" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="D111" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="K111" t="s">
         <v>1999</v>
@@ -41335,15 +41338,15 @@
         <v>{szContent="本周浩气盟略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的浩气盟侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，浩气盟首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="浩气盟·本周胜利",col={100,100,255,},[20]={},tCountdown={{nClass=20,nIcon=3444,nFrame=7,szName="浩气盟·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U111" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:22">
       <c r="C112" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D112" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K112" t="s">
         <v>1995</v>
@@ -41353,15 +41356,15 @@
         <v>{szContent="本周恶人谷略胜一筹，赢得了阵营胜利！所有参与击退敌对首领十次以上的恶人谷侠士下周一七时以后均可获得【血踪万里】称号！另外为了庆祝本周的胜利，恶人谷首领特请来舞狮队在长安、洛阳、扬州庆祝，感兴趣的侠士可以前往一观。\n",szNote="恶人谷·本周胜利",col={255,100,100,},[20]={},tCountdown={{nClass=20,nIcon=3445,nFrame=3,szName="恶人谷·本周胜利",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="U112" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:34">
       <c r="C113" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D113" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="K113" t="s">
         <v>2003</v>
@@ -41374,30 +41377,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=7,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U113" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V113" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="W113" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="X113" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="Y113" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="Z113" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:34">
       <c r="C114" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D114" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="K114" t="s">
         <v>2003</v>
@@ -41410,27 +41413,27 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-的【(.-)】帮会成功占领【(.-)】据点！",szNote="{$3}·{$1}占领",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=13,szName="{$3}·浩气大旗",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=13,szName="{$3}·恶人大旗",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=13,szName="{$3}·{$1}大旗",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=14888,nFrame=7,szName="【{$3}】·浩气[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=14887,nFrame=3,szName="【{$3}】·恶人[{$2}]占领",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U114" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="V114" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="W114" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="X114" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="Y114" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:34">
       <c r="C115" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="D115" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="K115" t="s">
         <v>2003</v>
@@ -41446,27 +41449,27 @@
         <v>{szContent="^本场攻防“([主战奇袭场]+)”已结束，([浩气盟恶人谷]+)[侠士们众志成城和，]-([大完险胜]+)([浩气盟恶人谷]+)[！，]+",szNote="{$1}·{$2}·{$3}",col={255,255,100,},bReg=true,[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,szName="大攻防·奇袭场",nTime=-2,nRefresh=10,key="大攻防·奇袭场",},{nClass=20,nIcon=13,szName="大攻防·主战场",nTime=-2,nRefresh=10,key="大攻防·主战场",},{nClass=20,nIcon=13,szName="大攻防·{$1}",nTime=-2,key="大攻防·{$1}",},{nClass=20,nIcon=2402,nFrame=4,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·奇袭场",},{nClass=20,nIcon=2400,nFrame=0,szName="{$1}·{$2}·{$3}",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U115" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="V115" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="W115" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="X115" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="Y115" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:34">
       <c r="C116" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="D116" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="K116" t="s">
         <v>2003</v>
@@ -41476,15 +41479,15 @@
         <v>{szContent="本场攻防“主战场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="主战场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2400,nFrame=0,szName="主战场·平手",nTime=57,nRefresh=5,key="大攻防·主战场",},},},</v>
       </c>
       <c r="U116" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:34">
       <c r="C117" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="D117" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="K117" t="s">
         <v>2003</v>
@@ -41494,7 +41497,7 @@
         <v>{szContent="本场攻防“奇袭场”已结束，浩气盟侠士和恶人谷侠士经过一场恶战，势均力敌，最终打为平手，暂时休战！\n",szNote="奇袭场·平手",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=2402,nFrame=4,szName="奇袭场·平手",nTime=57,nRefresh=5,key="大攻防·奇袭场",},},},</v>
       </c>
       <c r="U117" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:34">
@@ -41511,13 +41514,13 @@
     </row>
     <row r="119" customFormat="1" spans="1:34">
       <c r="C119" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D119" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G119" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K119" t="s">
         <v>2003</v>
@@ -41530,7 +41533,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【武王城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="武王城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【武王城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="武王城·恶人大旗",},},},</v>
       </c>
       <c r="U119" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V119" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G119&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41541,19 +41544,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="武王城·恶人大旗",},</v>
       </c>
       <c r="X119" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="Y119" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z119" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AA119" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AB119" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AC119" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G119&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G119&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41566,10 +41569,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:34">
       <c r="C120" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D120" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K120" t="s">
         <v>2003</v>
@@ -41582,16 +41585,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="武王城·大旗重置",nTime=-2,nRefresh=7200,key="武王城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【武王城】大旗重置",nTime="180,【武王城】大旗重置;185,【武王城】大旗重置·结束",nRefresh=7200,key="武王城·大旗重置",},},},</v>
       </c>
       <c r="U120" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="V120" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="W120" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="X120" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="121" spans="1:34">
@@ -41608,13 +41611,13 @@
     </row>
     <row r="122" customFormat="1" spans="1:34">
       <c r="C122" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D122" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G122" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="K122" t="s">
         <v>2003</v>
@@ -41627,7 +41630,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凛风堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凛风堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凛风堡·恶人大旗",},},},</v>
       </c>
       <c r="U122" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V122" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G122&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41638,19 +41641,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凛风堡·恶人大旗",},</v>
       </c>
       <c r="X122" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="Y122" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="Z122" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AA122" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AB122" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AC122" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G122&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G122&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41663,10 +41666,10 @@
     </row>
     <row r="123" spans="1:34">
       <c r="C123" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D123" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K123" t="s">
         <v>2003</v>
@@ -41679,16 +41682,16 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凛风堡·大旗重置",nTime=-2,nRefresh=7200,key="凛风堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凛风堡】大旗重置",nTime="180,【凛风堡】大旗重置;185,【凛风堡】大旗重置·结束",nRefresh=7200,key="凛风堡·大旗重置",},},},</v>
       </c>
       <c r="U123" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="V123" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="W123" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="X123" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -41705,16 +41708,16 @@
     </row>
     <row r="125" customFormat="1" spans="1:34">
       <c r="C125" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D125" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G125" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="H125" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="K125" t="s">
         <v>2003</v>
@@ -41727,7 +41730,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【盘龙坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【逐鹿坪】恶人·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【盘龙坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="盘龙坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【逐鹿坪】浩气·占领剩余",nTime=600.1,nRefresh=720,key="逐鹿坪·恶人大旗",},},},</v>
       </c>
       <c r="U125" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V125" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G125&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41746,19 +41749,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="逐鹿坪·恶人大旗",},</v>
       </c>
       <c r="Z125" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA125" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB125" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC125" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD125" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE125" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G125&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G125&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41779,10 +41782,10 @@
     </row>
     <row r="126" spans="1:34">
       <c r="C126" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D126" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K126" t="s">
         <v>2003</v>
@@ -41795,22 +41798,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="盘龙坞·大旗重置",nTime=-2,nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=1465,szName="逐鹿坪·大旗重置",nTime=-2,nRefresh=7200,key="逐鹿坪·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【盘龙坞】大旗重置",nTime="180,【盘龙坞】大旗重置;185,【盘龙坞】大旗重置·结束",nRefresh=7200,key="盘龙坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【逐鹿坪】大旗重置",nTime="180,【逐鹿坪】大旗重置;185,【逐鹿坪】大旗重置·结束",nRefresh=7200,key="逐鹿坪·大旗重置",},},},</v>
       </c>
       <c r="U126" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="V126" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="W126" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X126" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y126" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="Z126" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="127" spans="1:34">
@@ -41827,16 +41830,16 @@
     </row>
     <row r="128" customFormat="1" spans="1:34">
       <c r="C128" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D128" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G128" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="H128" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="K128" t="s">
         <v>2003</v>
@@ -41849,7 +41852,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="龙门镇·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【龙门镇】恶人·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【飞沙关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【龙门镇】浩气·占领剩余",nTime=600.1,nRefresh=720,key="龙门镇·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【飞沙关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="飞沙关·恶人大旗",},},},</v>
       </c>
       <c r="U128" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V128" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G128&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41868,19 +41871,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="飞沙关·恶人大旗",},</v>
       </c>
       <c r="Z128" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA128" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB128" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC128" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD128" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE128" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G128&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G128&amp;"·浩气大旗"""&amp;",},"</f>
@@ -41901,10 +41904,10 @@
     </row>
     <row r="129" spans="1:34">
       <c r="C129" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D129" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K129" t="s">
         <v>2003</v>
@@ -41917,22 +41920,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="龙门镇·大旗重置",nTime=-2,nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=1465,szName="飞沙关·大旗重置",nTime=-2,nRefresh=7200,key="飞沙关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【龙门镇】大旗重置",nTime="180,【龙门镇】大旗重置;185,【龙门镇】大旗重置·结束",nRefresh=7200,key="龙门镇·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【飞沙关】大旗重置",nTime="180,【飞沙关】大旗重置;185,【飞沙关】大旗重置·结束",nRefresh=7200,key="飞沙关·大旗重置",},},},</v>
       </c>
       <c r="U129" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="V129" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="W129" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X129" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y129" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="Z129" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="130" spans="1:34">
@@ -41949,16 +41952,16 @@
     </row>
     <row r="131" customFormat="1" spans="1:34">
       <c r="C131" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D131" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G131" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="H131" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="K131" t="s">
         <v>2003</v>
@@ -41971,7 +41974,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="红莲岗·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【红莲岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【秋雨堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【红莲岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="红莲岗·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【秋雨堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="秋雨堡·恶人大旗",},},},</v>
       </c>
       <c r="U131" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V131" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G131&amp;"·浩气大旗"&amp;""",},"</f>
@@ -41990,19 +41993,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="秋雨堡·恶人大旗",},</v>
       </c>
       <c r="Z131" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA131" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB131" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC131" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD131" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE131" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G131&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G131&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42023,10 +42026,10 @@
     </row>
     <row r="132" spans="1:34">
       <c r="C132" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D132" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K132" t="s">
         <v>2003</v>
@@ -42039,22 +42042,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="红莲岗·大旗重置",nTime=-2,nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=1465,szName="秋雨堡·大旗重置",nTime=-2,nRefresh=7200,key="秋雨堡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【红莲岗】大旗重置",nTime="180,【红莲岗】大旗重置;185,【红莲岗】大旗重置·结束",nRefresh=7200,key="红莲岗·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【秋雨堡】大旗重置",nTime="180,【秋雨堡】大旗重置;185,【秋雨堡】大旗重置·结束",nRefresh=7200,key="秋雨堡·大旗重置",},},},</v>
       </c>
       <c r="U132" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="V132" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="W132" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X132" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y132" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="Z132" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="133" spans="1:34">
@@ -42071,16 +42074,16 @@
     </row>
     <row r="134" customFormat="1" spans="1:34">
       <c r="C134" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D134" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G134" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="H134" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="K134" t="s">
         <v>2003</v>
@@ -42093,7 +42096,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="金门关·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【金门关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="金门关·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【青云坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【金门关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="金门关·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【青云坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="青云坞·恶人大旗",},},},</v>
       </c>
       <c r="U134" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V134" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G134&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42112,19 +42115,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="青云坞·恶人大旗",},</v>
       </c>
       <c r="Z134" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA134" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB134" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC134" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD134" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE134" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G134&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G134&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42145,10 +42148,10 @@
     </row>
     <row r="135" spans="1:34">
       <c r="C135" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D135" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K135" t="s">
         <v>2003</v>
@@ -42161,22 +42164,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="金门关·大旗重置",nTime=-2,nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=1465,szName="青云坞·大旗重置",nTime=-2,nRefresh=7200,key="青云坞·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【金门关】大旗重置",nTime="180,【金门关】大旗重置;185,【金门关】大旗重置·结束",nRefresh=7200,key="金门关·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【青云坞】大旗重置",nTime="180,【青云坞】大旗重置;185,【青云坞】大旗重置·结束",nRefresh=7200,key="青云坞·大旗重置",},},},</v>
       </c>
       <c r="U135" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="V135" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="W135" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X135" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y135" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="Z135" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -42193,16 +42196,16 @@
     </row>
     <row r="137" customFormat="1" spans="1:34">
       <c r="C137" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D137" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G137" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="H137" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="K137" t="s">
         <v>2003</v>
@@ -42215,7 +42218,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="激流坞·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【激流坞】恶人·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【不空关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="不空关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【激流坞】浩气·占领剩余",nTime=600.1,nRefresh=720,key="激流坞·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【不空关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="不空关·恶人大旗",},},},</v>
       </c>
       <c r="U137" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V137" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G137&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42234,19 +42237,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="不空关·恶人大旗",},</v>
       </c>
       <c r="Z137" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA137" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB137" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC137" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD137" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE137" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G137&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G137&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42267,10 +42270,10 @@
     </row>
     <row r="138" spans="1:34">
       <c r="C138" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D138" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K138" t="s">
         <v>2003</v>
@@ -42283,22 +42286,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="激流坞·大旗重置",nTime=-2,nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=1465,szName="不空关·大旗重置",nTime=-2,nRefresh=7200,key="不空关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【激流坞】大旗重置",nTime="180,【激流坞】大旗重置;185,【激流坞】大旗重置·结束",nRefresh=7200,key="激流坞·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【不空关】大旗重置",nTime="180,【不空关】大旗重置;185,【不空关】大旗重置·结束",nRefresh=7200,key="不空关·大旗重置",},},},</v>
       </c>
       <c r="U138" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="V138" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="W138" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X138" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y138" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="Z138" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="139" spans="1:34">
@@ -42315,16 +42318,16 @@
     </row>
     <row r="140" customFormat="1" spans="1:34">
       <c r="C140" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D140" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G140" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="H140" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="K140" t="s">
         <v>2003</v>
@@ -42337,7 +42340,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="日月崖·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【日月崖】恶人·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【卧龙坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【日月崖】浩气·占领剩余",nTime=600.1,nRefresh=720,key="日月崖·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【卧龙坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="卧龙坡·恶人大旗",},},},</v>
       </c>
       <c r="U140" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V140" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G140&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42356,19 +42359,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="卧龙坡·恶人大旗",},</v>
       </c>
       <c r="Z140" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA140" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB140" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC140" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD140" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE140" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G140&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G140&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42389,10 +42392,10 @@
     </row>
     <row r="141" spans="1:34">
       <c r="C141" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D141" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K141" t="s">
         <v>2003</v>
@@ -42405,22 +42408,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="日月崖·大旗重置",nTime=-2,nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=1465,szName="卧龙坡·大旗重置",nTime=-2,nRefresh=7200,key="卧龙坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【日月崖】大旗重置",nTime="180,【日月崖】大旗重置;185,【日月崖】大旗重置·结束",nRefresh=7200,key="日月崖·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【卧龙坡】大旗重置",nTime="180,【卧龙坡】大旗重置;185,【卧龙坡】大旗重置·结束",nRefresh=7200,key="卧龙坡·大旗重置",},},},</v>
       </c>
       <c r="U141" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="V141" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="W141" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X141" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y141" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="Z141" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -42437,16 +42440,16 @@
     </row>
     <row r="143" customFormat="1" spans="1:34">
       <c r="C143" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D143" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G143" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="H143" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="K143" t="s">
         <v>2003</v>
@@ -42459,7 +42462,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【霜戈堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【澜沧城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【霜戈堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="霜戈堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【澜沧城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="澜沧城·恶人大旗",},},},</v>
       </c>
       <c r="U143" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V143" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G143&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42478,19 +42481,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="澜沧城·恶人大旗",},</v>
       </c>
       <c r="Z143" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA143" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB143" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC143" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD143" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE143" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G143&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G143&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42511,10 +42514,10 @@
     </row>
     <row r="144" spans="1:34">
       <c r="C144" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D144" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K144" t="s">
         <v>2003</v>
@@ -42527,22 +42530,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="霜戈堡·大旗重置",nTime=-2,nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=1465,szName="澜沧城·大旗重置",nTime=-2,nRefresh=7200,key="澜沧城·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【霜戈堡】大旗重置",nTime="180,【霜戈堡】大旗重置;185,【霜戈堡】大旗重置·结束",nRefresh=7200,key="霜戈堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【澜沧城】大旗重置",nTime="180,【澜沧城】大旗重置;185,【澜沧城】大旗重置·结束",nRefresh=7200,key="澜沧城·大旗重置",},},},</v>
       </c>
       <c r="U144" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="V144" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="W144" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X144" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y144" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="Z144" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="145" spans="1:34">
@@ -42559,16 +42562,16 @@
     </row>
     <row r="146" customFormat="1" spans="1:34">
       <c r="C146" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D146" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G146" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="H146" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="K146" t="s">
         <v>2003</v>
@@ -42581,7 +42584,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="神池岭·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【神池岭】恶人·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【烈日岗】恶人·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【神池岭】浩气·占领剩余",nTime=600.1,nRefresh=720,key="神池岭·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【烈日岗】浩气·占领剩余",nTime=600.1,nRefresh=720,key="烈日岗·恶人大旗",},},},</v>
       </c>
       <c r="U146" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V146" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G146&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42600,19 +42603,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="烈日岗·恶人大旗",},</v>
       </c>
       <c r="Z146" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA146" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB146" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC146" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD146" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE146" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G146&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G146&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42633,10 +42636,10 @@
     </row>
     <row r="147" spans="1:34">
       <c r="C147" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D147" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K147" t="s">
         <v>2003</v>
@@ -42649,22 +42652,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="神池岭·大旗重置",nTime=-2,nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=1465,szName="烈日岗·大旗重置",nTime=-2,nRefresh=7200,key="烈日岗·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【神池岭】大旗重置",nTime="180,【神池岭】大旗重置;185,【神池岭】大旗重置·结束",nRefresh=7200,key="神池岭·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【烈日岗】大旗重置",nTime="180,【烈日岗】大旗重置;185,【烈日岗】大旗重置·结束",nRefresh=7200,key="烈日岗·大旗重置",},},},</v>
       </c>
       <c r="U147" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="V147" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="W147" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X147" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y147" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="Z147" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -42681,16 +42684,16 @@
     </row>
     <row r="149" customFormat="1" spans="1:34">
       <c r="C149" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D149" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G149" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="H149" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="K149" t="s">
         <v>2003</v>
@@ -42703,7 +42706,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【凤鸣堡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【惊虬谷】恶人·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【凤鸣堡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="凤鸣堡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【惊虬谷】浩气·占领剩余",nTime=600.1,nRefresh=720,key="惊虬谷·恶人大旗",},},},</v>
       </c>
       <c r="U149" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V149" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G149&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42722,19 +42725,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="惊虬谷·恶人大旗",},</v>
       </c>
       <c r="Z149" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA149" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB149" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC149" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD149" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE149" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G149&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G149&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42755,10 +42758,10 @@
     </row>
     <row r="150" spans="1:34">
       <c r="C150" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D150" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K150" t="s">
         <v>2003</v>
@@ -42771,22 +42774,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="凤鸣堡·大旗重置",nTime=-2,nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=1465,szName="惊虬谷·大旗重置",nTime=-2,nRefresh=7200,key="惊虬谷·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【凤鸣堡】大旗重置",nTime="180,【凤鸣堡】大旗重置;185,【凤鸣堡】大旗重置·结束",nRefresh=7200,key="凤鸣堡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【惊虬谷】大旗重置",nTime="180,【惊虬谷】大旗重置;185,【惊虬谷】大旗重置·结束",nRefresh=7200,key="惊虬谷·大旗重置",},},},</v>
       </c>
       <c r="U150" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="V150" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="W150" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X150" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y150" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="Z150" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="151" spans="1:34">
@@ -42803,16 +42806,16 @@
     </row>
     <row r="152" customFormat="1" spans="1:34">
       <c r="C152" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D152" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G152" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="H152" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="K152" t="s">
         <v>2003</v>
@@ -42825,7 +42828,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="大理山城·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【大理山城】恶人·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【千岩关】恶人·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【大理山城】浩气·占领剩余",nTime=600.1,nRefresh=720,key="大理山城·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【千岩关】浩气·占领剩余",nTime=600.1,nRefresh=720,key="千岩关·恶人大旗",},},},</v>
       </c>
       <c r="U152" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V152" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G152&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42844,19 +42847,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="千岩关·恶人大旗",},</v>
       </c>
       <c r="Z152" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA152" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB152" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC152" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD152" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE152" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G152&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G152&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42877,10 +42880,10 @@
     </row>
     <row r="153" spans="1:34">
       <c r="C153" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D153" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K153" t="s">
         <v>2003</v>
@@ -42893,22 +42896,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="大理山城·大旗重置",nTime=-2,nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=1465,szName="千岩关·大旗重置",nTime=-2,nRefresh=7200,key="千岩关·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【大理山城】大旗重置",nTime="180,【大理山城】大旗重置;185,【大理山城】大旗重置·结束",nRefresh=7200,key="大理山城·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【千岩关】大旗重置",nTime="180,【千岩关】大旗重置;185,【千岩关】大旗重置·结束",nRefresh=7200,key="千岩关·大旗重置",},},},</v>
       </c>
       <c r="U153" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="V153" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="W153" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X153" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y153" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="Z153" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -42925,16 +42928,16 @@
     </row>
     <row r="155" customFormat="1" spans="1:34">
       <c r="C155" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D155" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G155" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="H155" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="K155" t="s">
         <v>2003</v>
@@ -42947,7 +42950,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【枫湖寨】恶人·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【啖杏林】恶人·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【枫湖寨】浩气·占领剩余",nTime=600.1,nRefresh=720,key="枫湖寨·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【啖杏林】浩气·占领剩余",nTime=600.1,nRefresh=720,key="啖杏林·恶人大旗",},},},</v>
       </c>
       <c r="U155" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V155" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G155&amp;"·浩气大旗"&amp;""",},"</f>
@@ -42966,19 +42969,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="啖杏林·恶人大旗",},</v>
       </c>
       <c r="Z155" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA155" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB155" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC155" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD155" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE155" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G155&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G155&amp;"·浩气大旗"""&amp;",},"</f>
@@ -42999,10 +43002,10 @@
     </row>
     <row r="156" spans="1:34">
       <c r="C156" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D156" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K156" t="s">
         <v>2003</v>
@@ -43015,22 +43018,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="枫湖寨·大旗重置",nTime=-2,nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=1465,szName="啖杏林·大旗重置",nTime=-2,nRefresh=7200,key="啖杏林·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【枫湖寨】大旗重置",nTime="180,【枫湖寨】大旗重置;185,【枫湖寨】大旗重置·结束",nRefresh=7200,key="枫湖寨·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【啖杏林】大旗重置",nTime="180,【啖杏林】大旗重置;185,【啖杏林】大旗重置·结束",nRefresh=7200,key="啖杏林·大旗重置",},},},</v>
       </c>
       <c r="U156" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="V156" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="W156" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X156" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y156" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="Z156" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="157" spans="1:34">
@@ -43047,16 +43050,16 @@
     </row>
     <row r="158" customFormat="1" spans="1:34">
       <c r="C158" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D158" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G158" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="H158" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="K158" t="s">
         <v>2003</v>
@@ -43069,7 +43072,7 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于([^%d]-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·浩气大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="扶风郡·恶人大旗",},{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,nFrame=-1,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,key="{$3}·恶人大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【扶风郡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·浩气大旗",},{nClass=20,nIcon=3445,nFrame=3,szName="【世外坡】恶人·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·浩气大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【扶风郡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="扶风郡·恶人大旗",},{nClass=20,nIcon=3444,nFrame=7,szName="【世外坡】浩气·占领剩余",nTime=600.1,nRefresh=720,key="世外坡·恶人大旗",},},},</v>
       </c>
       <c r="U158" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V158" t="str">
         <f>"{nClass=20,nIcon=1465,nFrame=-1,szName="&amp;""" """&amp;",nTime=-2,nRefresh=7200,key="""&amp;G158&amp;"·浩气大旗"&amp;""",},"</f>
@@ -43088,19 +43091,19 @@
         <v>{nClass=20,nIcon=1465,nFrame=-1,szName=" ",nTime=-2,nRefresh=7200,key="世外坡·恶人大旗",},</v>
       </c>
       <c r="Z158" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="AA158" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="AB158" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="AC158" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="AD158" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="AE158" t="str">
         <f>"{nClass=20,nIcon=3445,nFrame=3,szName="&amp;"""【"&amp;G158&amp;"】恶人·占领剩余"""&amp;",nTime=600.1,nRefresh=720,key="&amp;""""&amp;G158&amp;"·浩气大旗"""&amp;",},"</f>
@@ -43121,10 +43124,10 @@
     </row>
     <row r="159" spans="1:34">
       <c r="C159" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D159" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K159" t="s">
         <v>2003</v>
@@ -43137,22 +43140,22 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="扶风郡·大旗重置",nTime=-2,nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=1465,szName="世外坡·大旗重置",nTime=-2,nRefresh=7200,key="世外坡·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【扶风郡】大旗重置",nTime="180,【扶风郡】大旗重置;185,【扶风郡】大旗重置·结束",nRefresh=7200,key="扶风郡·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【世外坡】大旗重置",nTime="180,【世外坡】大旗重置;185,【世外坡】大旗重置·结束",nRefresh=7200,key="世外坡·大旗重置",},},},</v>
       </c>
       <c r="U159" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="V159" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="W159" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X159" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y159" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="Z159" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="160" spans="1:34">
@@ -43169,16 +43172,16 @@
     </row>
     <row r="161" spans="1:26">
       <c r="C161" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="D161" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G161" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="H161" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="K161" t="s">
         <v>2003</v>
@@ -43191,30 +43194,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U161" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V161" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="W161" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="X161" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="Y161" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="Z161" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="162" spans="1:26">
       <c r="C162" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D162" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K162" t="s">
         <v>2003</v>
@@ -43227,30 +43230,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U162" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="V162" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="W162" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X162" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y162" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="Z162" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:26">
       <c r="C163" s="5" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="D163" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="K163" t="s">
         <v>2003</v>
@@ -43263,19 +43266,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U163" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="V163" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="W163" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="X163" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="Y163" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="164" spans="1:26">
@@ -43292,16 +43295,16 @@
     </row>
     <row r="165" spans="1:26">
       <c r="C165" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="D165" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="G165" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="H165" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="K165" t="s">
         <v>2003</v>
@@ -43314,30 +43317,30 @@
         <v>{szContent="([浩气恶人]+)[盟谷]-位于(.-)的【(.-)据点】大旗被夺",szNote="{$3}·{$1}大旗被夺",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=4,szName="{$3}·大旗重置",nTime=-1,key="{$3}·大旗重置",},{nClass=20,nIcon=2397,nFrame=-1,szName="{$3}·浩气大旗被夺",nTime=-1,nRefresh=2,key="{$3}·浩气大旗",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$3}·恶人大旗被夺",nTime=-1,nRefresh=2,key="{$3}·恶人大旗",},{nClass=20,nIcon=2400,szName="{$3}·{$1}大旗被夺",nTime=-2,key="{$3}·{$1}大旗",},{nClass=20,nIcon=4837,nFrame=7,szName="{$2}【{$3}】浩气大旗被夺",nTime=30,nRefresh=1,key="{$3}·浩气大旗",},{nClass=20,nIcon=4838,nFrame=3,szName="{$2}【{$3}】恶人大旗被夺",nTime=30,nRefresh=1,key="{$3}·恶人大旗",},},},</v>
       </c>
       <c r="U165" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="V165" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="W165" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="X165" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="Y165" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="Z165" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="166" spans="1:26">
       <c r="C166" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D166" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K166" t="s">
         <v>2003</v>
@@ -43350,30 +43353,30 @@
         <v>{szContent="^【(.*)】据点大旗(.*)重置回初始位置！\n",szNote="{$1}·大旗重置",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=1465,szName="云台营·大旗重置",nTime=-2,nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=1465,szName="高阳营·大旗重置",nTime=-2,nRefresh=7200,key="高阳营·大旗重置",},{nClass=20,nIcon=13,szName="【{$1}】大旗重置",nTime=-2,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【{$1}】大旗重置",nTime=30,key="{$1}·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【云台营】大旗重置",nTime="180,【云台营】大旗重置;185,【云台营】大旗重置·结束",nRefresh=7200,key="云台营·大旗重置",},{nClass=20,nIcon=592,nFrame=4,szName="【高阳营】大旗重置",nTime="180,【高阳营】大旗重置;185,【高阳营】大旗重置·结束",nRefresh=7200,key="高阳营·大旗重置",},},},</v>
       </c>
       <c r="U166" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="V166" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="W166" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="X166" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="Y166" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="Z166" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:26">
       <c r="C167" s="5" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="D167" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="K167" t="s">
         <v>2003</v>
@@ -43386,19 +43389,19 @@
         <v>{szContent="^江湖快报！(.-)据点粮仓被一群([浩气恶人]+)[盟谷]-人士洗劫",szNote="{$1}·{$2}劫粮",col={255,255,100,},bReg=true,[20]={},tCountdown={{nClass=20,nIcon=2397,nFrame=-1,szName="{$1}·浩气劫粮",nTime=-1,nRefresh=2,key="{$1}·浩气劫粮",},{nClass=20,nIcon=2398,nFrame=-1,szName="{$1}·恶人劫粮",nTime=-1,nRefresh=2,key="{$1}·恶人劫粮",},{nClass=20,nIcon=2400,nFrame=7,szName="{$1}·{$2}劫粮",nTime=-2,key="{$1}·{$2}劫粮",},{nClass=20,nIcon=10449,nFrame=7,szName="【{$1}】浩气劫粮",nTime=30,nRefresh=1,key="{$1}·浩气劫粮",},{nClass=20,nIcon=10450,nFrame=3,szName="【{$1}】恶人劫粮",nTime=30,nRefresh=1,key="{$1}·恶人劫粮",},},},</v>
       </c>
       <c r="U167" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="V167" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="W167" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="X167" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="Y167" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="168" spans="1:26">

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -4828,7 +4828,7 @@
     <t>爆炸·烈日剑·升凤</t>
   </si>
   <si>
-    <t>爆</t>
+    <t>雷</t>
   </si>
   <si>
     <t>DOT·毒王杖·爆</t>
@@ -5065,31 +5065,31 @@
     <t>月弄痕·霸气</t>
   </si>
   <si>
-    <t>{nClass=9,nIcon=2037,nFrame=5,nTime="10,月弄痕·霸气·正在反弹;68,月弄痕·霸气·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},</t>
+    <t>{nClass=9,nIcon=2037,nFrame=0,nTime="10,月弄痕·霸气·正在反弹;68,月弄痕·霸气·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},</t>
   </si>
   <si>
     <t>小七·珠袖落日</t>
   </si>
   <si>
-    <t>{nClass=8,nIcon=21,nFrame=5,nTime="6,小七·珠袖落日·正在反弹;44,小七·珠袖落日·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},</t>
+    <t>{nClass=8,nIcon=21,nFrame=0,nTime="6,小七·珠袖落日·正在反弹;44,小七·珠袖落日·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},</t>
   </si>
   <si>
     <t>伊夜·斩无常</t>
   </si>
   <si>
-    <t>{nClass=8,nIcon=12101,nFrame=5,nTime="2.5,伊夜·斩无常·正在反弹;27,伊夜·斩无常·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},</t>
+    <t>{nClass=8,nIcon=12101,nFrame=0,nTime="2.5,伊夜·斩无常·正在反弹;27,伊夜·斩无常·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},</t>
   </si>
   <si>
     <t>王遗风·红尘曲·倾城</t>
   </si>
   <si>
-    <t>{nClass=8,nIcon=2033,nFrame=5,nTime="1,红尘曲倾城·抬血",szName="招式提示1",nRefresh=1,key="招式提示1",},</t>
+    <t>{nClass=8,nIcon=2033,nFrame=0,nTime="1,红尘曲倾城·抬血",szName="招式提示1",nRefresh=1,key="招式提示1",},</t>
   </si>
   <si>
     <t>王遗风·红尘曲·御伤</t>
   </si>
   <si>
-    <t>{nClass=9,nIcon=2024,nFrame=5,nTime="10,红尘曲御伤·80减伤",szName="王遗风",nRefresh=2,key="王遗风",},</t>
+    <t>{nClass=9,nIcon=2024,nFrame=0,nTime="10,红尘曲御伤·80减伤",szName="王遗风",nRefresh=2,key="王遗风",},</t>
   </si>
   <si>
     <t>{nClass=9,nFrame=5,nIcon=13,key="招式提示1",nTime="2,御城·抛掷;4.5,抛掷·眩晕;15,御城·抛掷·下一个",szName="御城·抛掷·下一个",nRefresh=2,},</t>
@@ -9387,7 +9387,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="38" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1792528069000,</v>
+        <v>nTimeStamp = 1792576162000,</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>11</v>
@@ -21478,7 +21478,7 @@
       </c>
       <c r="AN26" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=1452,nLevel=1,nScrutinyType=2,szNote="爆炸·烈日剑·升凤",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="爆",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bCaution=true,bScreenHead=true,},},},</v>
+        <v>{dwID=1452,nLevel=1,nScrutinyType=2,szNote="爆炸·烈日剑·升凤",col={255,50,255,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="雷",nPriority=4,col="#FF32FFFF",colScreenHead="#FF32FF",nColAlpha=255,bCaution=true,bScreenHead=true,},},},</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="3:46">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="X4" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=1361,nLevel=1,szNote="月弄痕·霸气",[9]={},[8]={},tCountdown={{nClass=9,nIcon=2037,nFrame=5,nTime="10,月弄痕·霸气·正在反弹;68,月弄痕·霸气·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},},},</v>
+        <v>{dwID=1361,nLevel=1,szNote="月弄痕·霸气",[9]={},[8]={},tCountdown={{nClass=9,nIcon=2037,nFrame=0,nTime="10,月弄痕·霸气·正在反弹;68,月弄痕·霸气·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},},},</v>
       </c>
       <c r="Y4" s="11" t="s">
         <v>1668</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="X5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=27379,nLevel=1,szNote="小七·珠袖落日",[9]={},[8]={},tCountdown={{nClass=8,nIcon=21,nFrame=5,nTime="6,小七·珠袖落日·正在反弹;44,小七·珠袖落日·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},},},</v>
+        <v>{dwID=27379,nLevel=1,szNote="小七·珠袖落日",[9]={},[8]={},tCountdown={{nClass=8,nIcon=21,nFrame=0,nTime="6,小七·珠袖落日·正在反弹;44,小七·珠袖落日·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},},},</v>
       </c>
       <c r="Y5" s="11" t="s">
         <v>1670</v>
@@ -24421,7 +24421,7 @@
       </c>
       <c r="X6" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=27917,nLevel=1,szNote="伊夜·斩无常",[9]={},[8]={},tCountdown={{nClass=8,nIcon=12101,nFrame=5,nTime="2.5,伊夜·斩无常·正在反弹;27,伊夜·斩无常·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},},},</v>
+        <v>{dwID=27917,nLevel=1,szNote="伊夜·斩无常",[9]={},[8]={},tCountdown={{nClass=8,nIcon=12101,nFrame=0,nTime="2.5,伊夜·斩无常·正在反弹;27,伊夜·斩无常·释放剩余",szName="反弹提示",nRefresh=2,key="反弹提示",},},},</v>
       </c>
       <c r="Y6" s="11" t="s">
         <v>1672</v>
@@ -24439,7 +24439,7 @@
       </c>
       <c r="X7" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7230,nLevel=1,szNote="王遗风·红尘曲·倾城",[9]={},[8]={},tCountdown={{nClass=8,nIcon=2033,nFrame=5,nTime="1,红尘曲倾城·抬血",szName="招式提示1",nRefresh=1,key="招式提示1",},},},</v>
+        <v>{dwID=7230,nLevel=1,szNote="王遗风·红尘曲·倾城",[9]={},[8]={},tCountdown={{nClass=8,nIcon=2033,nFrame=0,nTime="1,红尘曲倾城·抬血",szName="招式提示1",nRefresh=1,key="招式提示1",},},},</v>
       </c>
       <c r="Y7" s="11" t="s">
         <v>1674</v>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="X8" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=7330,nLevel=1,szNote="王遗风·红尘曲·御伤",[9]={},[8]={},tCountdown={{nClass=9,nIcon=2024,nFrame=5,nTime="10,红尘曲御伤·80减伤",szName="王遗风",nRefresh=2,key="王遗风",},},},</v>
+        <v>{dwID=7330,nLevel=1,szNote="王遗风·红尘曲·御伤",[9]={},[8]={},tCountdown={{nClass=9,nIcon=2024,nFrame=0,nTime="10,红尘曲御伤·80减伤",szName="王遗风",nRefresh=2,key="王遗风",},},},</v>
       </c>
       <c r="Y8" s="11" t="s">
         <v>1676</v>

--- a/阵营/攻防监控.xlsx
+++ b/阵营/攻防监控.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5991" uniqueCount="2663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6084" uniqueCount="2663">
   <si>
     <t>__meta = {</t>
   </si>
@@ -9055,16 +9055,6 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF92D050"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -9405,7 +9395,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="38" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1792679477000,</v>
+        <v>nTimeStamp = 1792681762000,</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>11</v>
@@ -24529,7 +24519,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:X370"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -24985,12 +24975,18 @@
       <c r="I22" t="s">
         <v>1700</v>
       </c>
+      <c r="J22" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
       <c r="U22" t="s">
         <v>1701</v>
       </c>
       <c r="V22" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29001,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29001,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="23" spans="3:22">
@@ -25003,12 +24999,18 @@
       <c r="I23" t="s">
         <v>1700</v>
       </c>
+      <c r="J23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
       <c r="U23" t="s">
         <v>1701</v>
       </c>
       <c r="V23" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29002,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29002,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="24" spans="3:22">
@@ -25021,12 +25023,18 @@
       <c r="I24" t="s">
         <v>1700</v>
       </c>
+      <c r="J24" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
       <c r="U24" t="s">
         <v>1701</v>
       </c>
       <c r="V24" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29003,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29003,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="25" spans="3:22">
@@ -25039,12 +25047,18 @@
       <c r="I25" t="s">
         <v>1700</v>
       </c>
+      <c r="J25" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
       <c r="U25" t="s">
         <v>1701</v>
       </c>
       <c r="V25" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29004,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29004,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="26" spans="3:22">
@@ -25057,12 +25071,18 @@
       <c r="I26" t="s">
         <v>1700</v>
       </c>
+      <c r="J26" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
       <c r="U26" t="s">
         <v>1701</v>
       </c>
       <c r="V26" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29005,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29005,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="27" spans="3:22">
@@ -25075,12 +25095,18 @@
       <c r="I27" t="s">
         <v>1700</v>
       </c>
+      <c r="J27" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
       <c r="U27" t="s">
         <v>1701</v>
       </c>
       <c r="V27" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29006,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29006,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="28" spans="3:22">
@@ -25093,12 +25119,18 @@
       <c r="I28" t="s">
         <v>1700</v>
       </c>
+      <c r="J28" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
       <c r="U28" t="s">
         <v>1701</v>
       </c>
       <c r="V28" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29007,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29007,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="29" spans="3:22">
@@ -25111,12 +25143,18 @@
       <c r="I29" t="s">
         <v>1700</v>
       </c>
+      <c r="J29" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
       <c r="U29" t="s">
         <v>1701</v>
       </c>
       <c r="V29" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29008,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29008,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="30" spans="3:22">
@@ -25129,12 +25167,18 @@
       <c r="I30" t="s">
         <v>1700</v>
       </c>
+      <c r="J30" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P30">
+        <v>1</v>
+      </c>
       <c r="U30" t="s">
         <v>1701</v>
       </c>
       <c r="V30" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29009,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29009,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="31" spans="3:22">
@@ -25147,12 +25191,18 @@
       <c r="I31" t="s">
         <v>1700</v>
       </c>
+      <c r="J31" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
+      </c>
       <c r="U31" t="s">
         <v>1701</v>
       </c>
       <c r="V31" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29010,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29010,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="32" spans="3:22">
@@ -25165,12 +25215,18 @@
       <c r="I32" t="s">
         <v>1700</v>
       </c>
+      <c r="J32" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
+      </c>
       <c r="U32" t="s">
         <v>1701</v>
       </c>
       <c r="V32" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29011,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29011,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="33" spans="3:23">
@@ -25183,12 +25239,18 @@
       <c r="I33" t="s">
         <v>1700</v>
       </c>
+      <c r="J33" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
+      </c>
       <c r="U33" t="s">
         <v>1701</v>
       </c>
       <c r="V33" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29012,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29012,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="34" spans="3:23">
@@ -25201,12 +25263,18 @@
       <c r="I34" t="s">
         <v>1700</v>
       </c>
+      <c r="J34" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
       <c r="U34" t="s">
         <v>1701</v>
       </c>
       <c r="V34" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29013,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29013,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="35" spans="3:23">
@@ -25219,12 +25287,18 @@
       <c r="I35" t="s">
         <v>1700</v>
       </c>
+      <c r="J35" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
       <c r="U35" t="s">
         <v>1701</v>
       </c>
       <c r="V35" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29101,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29101,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="36" spans="3:23">
@@ -25237,12 +25311,18 @@
       <c r="I36" t="s">
         <v>1700</v>
       </c>
+      <c r="J36" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
       <c r="U36" t="s">
         <v>1701</v>
       </c>
       <c r="V36" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29102,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29102,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="37" spans="3:23">
@@ -25255,12 +25335,18 @@
       <c r="I37" t="s">
         <v>1700</v>
       </c>
+      <c r="J37" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
       <c r="U37" t="s">
         <v>1701</v>
       </c>
       <c r="V37" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29103,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29103,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="38" spans="3:23">
@@ -25273,12 +25359,18 @@
       <c r="I38" t="s">
         <v>1700</v>
       </c>
+      <c r="J38" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
+      </c>
       <c r="U38" t="s">
         <v>1701</v>
       </c>
       <c r="V38" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29201,nFrame=52,szNote="通用箭塔",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29201,nFrame=52,szNote="通用箭塔",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="3:23">
@@ -28399,12 +28491,18 @@
       <c r="I162" t="s">
         <v>1817</v>
       </c>
+      <c r="J162" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P162">
+        <v>1</v>
+      </c>
       <c r="U162" t="s">
         <v>1701</v>
       </c>
       <c r="V162" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29801,nFrame=52,szNote="箭塔·昆仑",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29801,nFrame=52,szNote="箭塔·昆仑",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="163" customFormat="1" spans="1:24">
@@ -28417,12 +28515,18 @@
       <c r="I163" t="s">
         <v>1817</v>
       </c>
+      <c r="J163" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P163">
+        <v>1</v>
+      </c>
       <c r="U163" t="s">
         <v>1701</v>
       </c>
       <c r="V163" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29802,nFrame=52,szNote="箭塔·昆仑",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29802,nFrame=52,szNote="箭塔·昆仑",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="164" customFormat="1" spans="1:24">
@@ -28435,12 +28539,18 @@
       <c r="I164" t="s">
         <v>1817</v>
       </c>
+      <c r="J164" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
+      </c>
       <c r="U164" t="s">
         <v>1701</v>
       </c>
       <c r="V164" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29803,nFrame=52,szNote="箭塔·昆仑",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29803,nFrame=52,szNote="箭塔·昆仑",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="165" customFormat="1" spans="1:24">
@@ -28453,12 +28563,18 @@
       <c r="I165" t="s">
         <v>1817</v>
       </c>
+      <c r="J165" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P165">
+        <v>1</v>
+      </c>
       <c r="U165" t="s">
         <v>1701</v>
       </c>
       <c r="V165" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29804,nFrame=52,szNote="箭塔·昆仑",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29804,nFrame=52,szNote="箭塔·昆仑",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="166" customFormat="1" spans="1:24">
@@ -28471,12 +28587,18 @@
       <c r="I166" t="s">
         <v>1818</v>
       </c>
+      <c r="J166" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P166">
+        <v>1</v>
+      </c>
       <c r="U166" t="s">
         <v>1701</v>
       </c>
       <c r="V166" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29601,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29601,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:24">
@@ -28489,12 +28611,18 @@
       <c r="I167" t="s">
         <v>1818</v>
       </c>
+      <c r="J167" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P167">
+        <v>1</v>
+      </c>
       <c r="U167" t="s">
         <v>1701</v>
       </c>
       <c r="V167" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29602,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29602,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:24">
@@ -28507,12 +28635,18 @@
       <c r="I168" t="s">
         <v>1818</v>
       </c>
+      <c r="J168" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P168">
+        <v>1</v>
+      </c>
       <c r="U168" t="s">
         <v>1701</v>
       </c>
       <c r="V168" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29603,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29603,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:24">
@@ -28525,12 +28659,18 @@
       <c r="I169" t="s">
         <v>1818</v>
       </c>
+      <c r="J169" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P169">
+        <v>1</v>
+      </c>
       <c r="U169" t="s">
         <v>1701</v>
       </c>
       <c r="V169" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29604,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29604,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:24">
@@ -28543,12 +28683,18 @@
       <c r="I170" t="s">
         <v>1818</v>
       </c>
+      <c r="J170" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P170">
+        <v>1</v>
+      </c>
       <c r="U170" t="s">
         <v>1701</v>
       </c>
       <c r="V170" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29605,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29605,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:24">
@@ -28561,12 +28707,18 @@
       <c r="I171" t="s">
         <v>1818</v>
       </c>
+      <c r="J171" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P171">
+        <v>1</v>
+      </c>
       <c r="U171" t="s">
         <v>1701</v>
       </c>
       <c r="V171" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29701,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29701,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:24">
@@ -29017,12 +29169,18 @@
       <c r="I193" t="s">
         <v>1842</v>
       </c>
+      <c r="J193" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P193">
+        <v>1</v>
+      </c>
       <c r="U193" t="s">
         <v>1701</v>
       </c>
       <c r="V193" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29301,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29301,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="194" customFormat="1" spans="1:24">
@@ -29035,12 +29193,18 @@
       <c r="I194" t="s">
         <v>1842</v>
       </c>
+      <c r="J194" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P194">
+        <v>1</v>
+      </c>
       <c r="U194" t="s">
         <v>1701</v>
       </c>
       <c r="V194" t="str">
         <f t="shared" si="2"/>
-        <v>{dwID=29302,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29302,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="195" customFormat="1" spans="1:24">
@@ -29053,12 +29217,18 @@
       <c r="I195" t="s">
         <v>1842</v>
       </c>
+      <c r="J195" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P195">
+        <v>1</v>
+      </c>
       <c r="U195" t="s">
         <v>1701</v>
       </c>
       <c r="V195" t="str">
         <f t="shared" ref="V195:V258" si="3">IF(ISBLANK(B195)=FALSE,IF(ISBLANK(B194),"},["&amp;B195&amp;"]={","["&amp;B195&amp;"]={"),IF(AND(ISBLANK(B195),ISBLANK(D195),ISBLANK(C195),OR(ISBLANK(B194)=FALSE,ISBLANK(D194)=FALSE,ISBLANK(C194)=FALSE)),"},},}",IF(ISBLANK(C195),"","{dwID="&amp;C195&amp;","&amp;"nFrame="&amp;D195&amp;","&amp;IF(E195&gt;0,"nCount="&amp;E195&amp;",","")&amp;IF(F195&gt;0,"bAllLeave=true,","")&amp;IF(G195&lt;&gt;"","szName="""&amp;G195&amp;""",","")&amp;IF(H195&lt;&gt;"","tKungFu={"&amp;H195&amp;"},","")&amp;IF(I195&lt;&gt;"","szNote="""&amp;I195&amp;""",","")&amp;IF(J195&lt;&gt;"","col={"&amp;J195&amp;"},","")&amp;"[3]={"&amp;IF(K195&lt;&gt;"","tMark={"&amp;K195&amp;"},","")&amp;IF(L195&lt;&gt;"","szVoice="""&amp;L195&amp;""",","")&amp;IF(M195&gt;0,"bTeamChannel=true,","")&amp;IF(N195&gt;0,"bWhisperChannel=true,","")&amp;IF(O195&gt;0,"bCenterAlarm=true,","")&amp;IF(P195&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q195&lt;&gt;"","szVoice="""&amp;Q195&amp;""",","")&amp;IF(R195&gt;0,"bTeamChannel=true,","")&amp;IF(S195&gt;0,"bWhisperChannel=true,","")&amp;IF(T195&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U195&lt;&gt;"","aFocus={"&amp;U195&amp;"},","")&amp;IF(W195&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W195:ZZ195)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=29303,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29303,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="196" customFormat="1" spans="1:24">
@@ -29071,12 +29241,18 @@
       <c r="I196" t="s">
         <v>1842</v>
       </c>
+      <c r="J196" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P196">
+        <v>1</v>
+      </c>
       <c r="U196" t="s">
         <v>1701</v>
       </c>
       <c r="V196" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29304,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29304,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="197" customFormat="1" spans="1:24">
@@ -29089,12 +29265,18 @@
       <c r="I197" t="s">
         <v>1842</v>
       </c>
+      <c r="J197" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P197">
+        <v>1</v>
+      </c>
       <c r="U197" t="s">
         <v>1701</v>
       </c>
       <c r="V197" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29305,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29305,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="198" customFormat="1" spans="1:24">
@@ -29107,12 +29289,18 @@
       <c r="I198" t="s">
         <v>1842</v>
       </c>
+      <c r="J198" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P198">
+        <v>1</v>
+      </c>
       <c r="U198" t="s">
         <v>1701</v>
       </c>
       <c r="V198" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29306,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29306,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="199" customFormat="1" spans="1:24">
@@ -29125,12 +29313,18 @@
       <c r="I199" t="s">
         <v>1842</v>
       </c>
+      <c r="J199" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P199">
+        <v>1</v>
+      </c>
       <c r="U199" t="s">
         <v>1701</v>
       </c>
       <c r="V199" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29307,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29307,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="200" customFormat="1" spans="1:24">
@@ -29143,12 +29337,18 @@
       <c r="I200" t="s">
         <v>1842</v>
       </c>
+      <c r="J200" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P200">
+        <v>1</v>
+      </c>
       <c r="U200" t="s">
         <v>1701</v>
       </c>
       <c r="V200" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29308,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29308,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="201" customFormat="1" spans="1:24">
@@ -29161,12 +29361,18 @@
       <c r="I201" t="s">
         <v>1842</v>
       </c>
+      <c r="J201" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P201">
+        <v>1</v>
+      </c>
       <c r="U201" t="s">
         <v>1701</v>
       </c>
       <c r="V201" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29309,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29309,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="202" customFormat="1" spans="1:24">
@@ -29179,12 +29385,18 @@
       <c r="I202" t="s">
         <v>1842</v>
       </c>
+      <c r="J202" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P202">
+        <v>1</v>
+      </c>
       <c r="U202" t="s">
         <v>1701</v>
       </c>
       <c r="V202" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29401,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29401,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="203" customFormat="1" spans="1:24">
@@ -29197,12 +29409,18 @@
       <c r="I203" t="s">
         <v>1843</v>
       </c>
+      <c r="J203" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P203">
+        <v>1</v>
+      </c>
       <c r="U203" t="s">
         <v>1701</v>
       </c>
       <c r="V203" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29501,nFrame=52,szNote="箭塔·马嵬驿·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29501,nFrame=52,szNote="箭塔·马嵬驿·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="204" customFormat="1" spans="1:24">
@@ -29215,12 +29433,18 @@
       <c r="I204" t="s">
         <v>1842</v>
       </c>
+      <c r="J204" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P204">
+        <v>1</v>
+      </c>
       <c r="U204" t="s">
         <v>1701</v>
       </c>
       <c r="V204" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29502,nFrame=52,szNote="箭塔·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29502,nFrame=52,szNote="箭塔·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="205" customFormat="1" spans="1:24">
@@ -29527,12 +29751,18 @@
       <c r="I218" t="s">
         <v>1872</v>
       </c>
+      <c r="J218" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P218">
+        <v>1</v>
+      </c>
       <c r="U218" t="s">
         <v>1701</v>
       </c>
       <c r="V218" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29202,nFrame=52,szNote="通用箭塔·瞿塘峡·枫华谷",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29202,nFrame=52,szNote="通用箭塔·瞿塘峡·枫华谷",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="219" customFormat="1" spans="1:24">
@@ -29545,12 +29775,18 @@
       <c r="I219" t="s">
         <v>1873</v>
       </c>
+      <c r="J219" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P219">
+        <v>1</v>
+      </c>
       <c r="U219" t="s">
         <v>1701</v>
       </c>
       <c r="V219" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29203,nFrame=52,szNote="箭塔·瞿塘峡",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29203,nFrame=52,szNote="箭塔·瞿塘峡",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="220" customFormat="1" spans="1:24">
@@ -29563,12 +29799,18 @@
       <c r="I220" t="s">
         <v>1873</v>
       </c>
+      <c r="J220" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P220">
+        <v>1</v>
+      </c>
       <c r="U220" t="s">
         <v>1701</v>
       </c>
       <c r="V220" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29204,nFrame=52,szNote="箭塔·瞿塘峡",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29204,nFrame=52,szNote="箭塔·瞿塘峡",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="221" customFormat="1" spans="1:24">
@@ -29581,12 +29823,18 @@
       <c r="I221" t="s">
         <v>1873</v>
       </c>
+      <c r="J221" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P221">
+        <v>1</v>
+      </c>
       <c r="U221" t="s">
         <v>1701</v>
       </c>
       <c r="V221" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29205,nFrame=52,szNote="箭塔·瞿塘峡",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29205,nFrame=52,szNote="箭塔·瞿塘峡",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="222" customFormat="1" spans="1:24">
@@ -29599,12 +29847,18 @@
       <c r="I222" t="s">
         <v>1873</v>
       </c>
+      <c r="J222" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P222">
+        <v>1</v>
+      </c>
       <c r="U222" t="s">
         <v>1701</v>
       </c>
       <c r="V222" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29206,nFrame=52,szNote="箭塔·瞿塘峡",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29206,nFrame=52,szNote="箭塔·瞿塘峡",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="223" spans="1:24">
@@ -29812,12 +30066,18 @@
       <c r="I232" t="s">
         <v>1891</v>
       </c>
+      <c r="J232" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P232">
+        <v>1</v>
+      </c>
       <c r="U232" t="s">
         <v>1701</v>
       </c>
       <c r="V232" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29014,nFrame=52,szNote="箭塔·无量山",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29014,nFrame=52,szNote="箭塔·无量山",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="233" spans="1:24">
@@ -30253,12 +30513,18 @@
       <c r="I253" t="s">
         <v>1818</v>
       </c>
+      <c r="J253" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P253">
+        <v>1</v>
+      </c>
       <c r="U253" t="s">
         <v>1701</v>
       </c>
       <c r="V253" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29601,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29601,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:24">
@@ -30271,12 +30537,18 @@
       <c r="I254" t="s">
         <v>1818</v>
       </c>
+      <c r="J254" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P254">
+        <v>1</v>
+      </c>
       <c r="U254" t="s">
         <v>1701</v>
       </c>
       <c r="V254" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29602,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29602,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:24">
@@ -30289,12 +30561,18 @@
       <c r="I255" t="s">
         <v>1818</v>
       </c>
+      <c r="J255" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P255">
+        <v>1</v>
+      </c>
       <c r="U255" t="s">
         <v>1701</v>
       </c>
       <c r="V255" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29603,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29603,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:24">
@@ -30307,12 +30585,18 @@
       <c r="I256" t="s">
         <v>1818</v>
       </c>
+      <c r="J256" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P256">
+        <v>1</v>
+      </c>
       <c r="U256" t="s">
         <v>1701</v>
       </c>
       <c r="V256" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29604,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29604,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="257" customFormat="1" spans="1:24">
@@ -30325,12 +30609,18 @@
       <c r="I257" t="s">
         <v>1818</v>
       </c>
+      <c r="J257" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P257">
+        <v>1</v>
+      </c>
       <c r="U257" t="s">
         <v>1701</v>
       </c>
       <c r="V257" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29605,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29605,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="258" customFormat="1" spans="1:24">
@@ -30343,12 +30633,18 @@
       <c r="I258" t="s">
         <v>1818</v>
       </c>
+      <c r="J258" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P258">
+        <v>1</v>
+      </c>
       <c r="U258" t="s">
         <v>1701</v>
       </c>
       <c r="V258" t="str">
         <f t="shared" si="3"/>
-        <v>{dwID=29701,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29701,nFrame=52,szNote="通用箭塔·昆仑·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="259" customFormat="1" spans="1:24">
@@ -30361,12 +30657,18 @@
       <c r="I259" t="s">
         <v>1921</v>
       </c>
+      <c r="J259" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P259">
+        <v>1</v>
+      </c>
       <c r="U259" t="s">
         <v>1701</v>
       </c>
       <c r="V259" t="str">
         <f t="shared" ref="V259:V322" si="4">IF(ISBLANK(B259)=FALSE,IF(ISBLANK(B258),"},["&amp;B259&amp;"]={","["&amp;B259&amp;"]={"),IF(AND(ISBLANK(B259),ISBLANK(D259),ISBLANK(C259),OR(ISBLANK(B258)=FALSE,ISBLANK(D258)=FALSE,ISBLANK(C258)=FALSE)),"},},}",IF(ISBLANK(C259),"","{dwID="&amp;C259&amp;","&amp;"nFrame="&amp;D259&amp;","&amp;IF(E259&gt;0,"nCount="&amp;E259&amp;",","")&amp;IF(F259&gt;0,"bAllLeave=true,","")&amp;IF(G259&lt;&gt;"","szName="""&amp;G259&amp;""",","")&amp;IF(H259&lt;&gt;"","tKungFu={"&amp;H259&amp;"},","")&amp;IF(I259&lt;&gt;"","szNote="""&amp;I259&amp;""",","")&amp;IF(J259&lt;&gt;"","col={"&amp;J259&amp;"},","")&amp;"[3]={"&amp;IF(K259&lt;&gt;"","tMark={"&amp;K259&amp;"},","")&amp;IF(L259&lt;&gt;"","szVoice="""&amp;L259&amp;""",","")&amp;IF(M259&gt;0,"bTeamChannel=true,","")&amp;IF(N259&gt;0,"bWhisperChannel=true,","")&amp;IF(O259&gt;0,"bCenterAlarm=true,","")&amp;IF(P259&gt;0,"bScreenHead=true,","")&amp;"},"&amp;"[4]={"&amp;IF(Q259&lt;&gt;"","szVoice="""&amp;Q259&amp;""",","")&amp;IF(R259&gt;0,"bTeamChannel=true,","")&amp;IF(S259&gt;0,"bWhisperChannel=true,","")&amp;IF(T259&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(U259&lt;&gt;"","aFocus={"&amp;U259&amp;"},","")&amp;IF(W259&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W259:ZZ259)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=29606,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29606,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:24">
@@ -30379,12 +30681,18 @@
       <c r="I260" t="s">
         <v>1921</v>
       </c>
+      <c r="J260" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P260">
+        <v>1</v>
+      </c>
       <c r="U260" t="s">
         <v>1701</v>
       </c>
       <c r="V260" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29607,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29607,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:24">
@@ -30397,12 +30705,18 @@
       <c r="I261" t="s">
         <v>1921</v>
       </c>
+      <c r="J261" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P261">
+        <v>1</v>
+      </c>
       <c r="U261" t="s">
         <v>1701</v>
       </c>
       <c r="V261" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29702,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29702,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="262" customFormat="1" spans="1:24">
@@ -30415,12 +30729,18 @@
       <c r="I262" t="s">
         <v>1921</v>
       </c>
+      <c r="J262" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P262">
+        <v>1</v>
+      </c>
       <c r="U262" t="s">
         <v>1701</v>
       </c>
       <c r="V262" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29703,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29703,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="263" customFormat="1" spans="1:24">
@@ -30433,12 +30753,18 @@
       <c r="I263" t="s">
         <v>1921</v>
       </c>
+      <c r="J263" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P263">
+        <v>1</v>
+      </c>
       <c r="U263" t="s">
         <v>1701</v>
       </c>
       <c r="V263" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29704,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29704,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="264" customFormat="1" spans="1:24">
@@ -30451,12 +30777,18 @@
       <c r="I264" t="s">
         <v>1921</v>
       </c>
+      <c r="J264" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P264">
+        <v>1</v>
+      </c>
       <c r="U264" t="s">
         <v>1701</v>
       </c>
       <c r="V264" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29705,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29705,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="265" customFormat="1" spans="1:24">
@@ -30469,12 +30801,18 @@
       <c r="I265" t="s">
         <v>1921</v>
       </c>
+      <c r="J265" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P265">
+        <v>1</v>
+      </c>
       <c r="U265" t="s">
         <v>1701</v>
       </c>
       <c r="V265" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29706,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29706,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:24">
@@ -30487,12 +30825,18 @@
       <c r="I266" t="s">
         <v>1921</v>
       </c>
+      <c r="J266" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P266">
+        <v>1</v>
+      </c>
       <c r="U266" t="s">
         <v>1701</v>
       </c>
       <c r="V266" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29707,nFrame=52,szNote="箭塔·苍山洱海",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29707,nFrame=52,szNote="箭塔·苍山洱海",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="267" customFormat="1" spans="1:24">
@@ -30619,12 +30963,18 @@
       <c r="I272" t="s">
         <v>1872</v>
       </c>
+      <c r="J272" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P272">
+        <v>1</v>
+      </c>
       <c r="U272" t="s">
         <v>1701</v>
       </c>
       <c r="V272" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29202,nFrame=52,szNote="通用箭塔·瞿塘峡·枫华谷",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29202,nFrame=52,szNote="通用箭塔·瞿塘峡·枫华谷",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="273" spans="1:24">
@@ -30784,12 +31134,18 @@
       <c r="I280" t="s">
         <v>1843</v>
       </c>
+      <c r="J280" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P280">
+        <v>1</v>
+      </c>
       <c r="U280" t="s">
         <v>1701</v>
       </c>
       <c r="V280" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=29501,nFrame=52,szNote="箭塔·马嵬驿·龙门荒漠",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=29501,nFrame=52,szNote="箭塔·马嵬驿·龙门荒漠",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="281" customFormat="1" spans="1:24">
@@ -31354,12 +31710,18 @@
       <c r="I307" t="s">
         <v>1965</v>
       </c>
+      <c r="J307" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P307">
+        <v>1</v>
+      </c>
       <c r="U307" t="s">
         <v>1701</v>
       </c>
       <c r="V307" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="308" spans="3:22">
@@ -31372,12 +31734,18 @@
       <c r="I308" t="s">
         <v>1965</v>
       </c>
+      <c r="J308" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P308">
+        <v>1</v>
+      </c>
       <c r="U308" t="s">
         <v>1701</v>
       </c>
       <c r="V308" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="309" spans="3:22">
@@ -31390,12 +31758,18 @@
       <c r="I309" t="s">
         <v>1965</v>
       </c>
+      <c r="J309" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P309">
+        <v>1</v>
+      </c>
       <c r="U309" t="s">
         <v>1701</v>
       </c>
       <c r="V309" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="310" spans="3:22">
@@ -31408,12 +31782,18 @@
       <c r="I310" t="s">
         <v>1965</v>
       </c>
+      <c r="J310" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P310">
+        <v>1</v>
+      </c>
       <c r="U310" t="s">
         <v>1701</v>
       </c>
       <c r="V310" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="311" spans="3:22">
@@ -31426,12 +31806,18 @@
       <c r="I311" t="s">
         <v>1965</v>
       </c>
+      <c r="J311" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P311">
+        <v>1</v>
+      </c>
       <c r="U311" t="s">
         <v>1701</v>
       </c>
       <c r="V311" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="312" spans="3:22">
@@ -31444,12 +31830,18 @@
       <c r="I312" t="s">
         <v>1965</v>
       </c>
+      <c r="J312" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P312">
+        <v>1</v>
+      </c>
       <c r="U312" t="s">
         <v>1701</v>
       </c>
       <c r="V312" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="313" spans="3:22">
@@ -31462,12 +31854,18 @@
       <c r="I313" t="s">
         <v>1965</v>
       </c>
+      <c r="J313" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P313">
+        <v>1</v>
+      </c>
       <c r="U313" t="s">
         <v>1701</v>
       </c>
       <c r="V313" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="314" spans="3:22">
@@ -31480,12 +31878,18 @@
       <c r="I314" t="s">
         <v>1965</v>
       </c>
+      <c r="J314" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P314">
+        <v>1</v>
+      </c>
       <c r="U314" t="s">
         <v>1701</v>
       </c>
       <c r="V314" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="315" spans="3:22">
@@ -31498,12 +31902,18 @@
       <c r="I315" t="s">
         <v>1965</v>
       </c>
+      <c r="J315" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P315">
+        <v>1</v>
+      </c>
       <c r="U315" t="s">
         <v>1701</v>
       </c>
       <c r="V315" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="316" spans="3:22">
@@ -31516,12 +31926,18 @@
       <c r="I316" t="s">
         <v>1965</v>
       </c>
+      <c r="J316" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P316">
+        <v>1</v>
+      </c>
       <c r="U316" t="s">
         <v>1701</v>
       </c>
       <c r="V316" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="317" spans="3:22">
@@ -31534,12 +31950,18 @@
       <c r="I317" t="s">
         <v>1965</v>
       </c>
+      <c r="J317" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P317">
+        <v>1</v>
+      </c>
       <c r="U317" t="s">
         <v>1701</v>
       </c>
       <c r="V317" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="318" spans="3:22">
@@ -31552,12 +31974,18 @@
       <c r="I318" t="s">
         <v>1965</v>
       </c>
+      <c r="J318" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P318">
+        <v>1</v>
+      </c>
       <c r="U318" t="s">
         <v>1701</v>
       </c>
       <c r="V318" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="319" spans="3:22">
@@ -31570,12 +31998,18 @@
       <c r="I319" t="s">
         <v>1965</v>
       </c>
+      <c r="J319" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P319">
+        <v>1</v>
+      </c>
       <c r="U319" t="s">
         <v>1701</v>
       </c>
       <c r="V319" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="320" spans="3:22">
@@ -31588,12 +32022,18 @@
       <c r="I320" t="s">
         <v>1965</v>
       </c>
+      <c r="J320" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P320">
+        <v>1</v>
+      </c>
       <c r="U320" t="s">
         <v>1701</v>
       </c>
       <c r="V320" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="321" spans="1:23">
@@ -31606,12 +32046,18 @@
       <c r="I321" t="s">
         <v>1965</v>
       </c>
+      <c r="J321" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P321">
+        <v>1</v>
+      </c>
       <c r="U321" t="s">
         <v>1701</v>
       </c>
       <c r="V321" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="322" spans="1:23">
@@ -31624,12 +32070,18 @@
       <c r="I322" t="s">
         <v>1965</v>
       </c>
+      <c r="J322" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P322">
+        <v>1</v>
+      </c>
       <c r="U322" t="s">
         <v>1701</v>
       </c>
       <c r="V322" t="str">
         <f t="shared" si="4"/>
-        <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="323" spans="1:23">
@@ -32140,12 +32592,18 @@
       <c r="I347" t="s">
         <v>1970</v>
       </c>
+      <c r="J347" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P347">
+        <v>1</v>
+      </c>
       <c r="U347" t="s">
         <v>1701</v>
       </c>
       <c r="V347" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124109,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="348" spans="3:23">
@@ -32158,12 +32616,18 @@
       <c r="I348" t="s">
         <v>1970</v>
       </c>
+      <c r="J348" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P348">
+        <v>1</v>
+      </c>
       <c r="U348" t="s">
         <v>1701</v>
       </c>
       <c r="V348" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124110,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="349" spans="3:23">
@@ -32176,12 +32640,18 @@
       <c r="I349" t="s">
         <v>1970</v>
       </c>
+      <c r="J349" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P349">
+        <v>1</v>
+      </c>
       <c r="U349" t="s">
         <v>1701</v>
       </c>
       <c r="V349" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124111,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="350" spans="3:23">
@@ -32194,12 +32664,18 @@
       <c r="I350" t="s">
         <v>1970</v>
       </c>
+      <c r="J350" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P350">
+        <v>1</v>
+      </c>
       <c r="U350" t="s">
         <v>1701</v>
       </c>
       <c r="V350" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124112,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="351" spans="3:23">
@@ -32212,12 +32688,18 @@
       <c r="I351" t="s">
         <v>1970</v>
       </c>
+      <c r="J351" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P351">
+        <v>1</v>
+      </c>
       <c r="U351" t="s">
         <v>1701</v>
       </c>
       <c r="V351" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124113,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="352" spans="3:23">
@@ -32230,12 +32712,18 @@
       <c r="I352" t="s">
         <v>1970</v>
       </c>
+      <c r="J352" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P352">
+        <v>1</v>
+      </c>
       <c r="U352" t="s">
         <v>1701</v>
       </c>
       <c r="V352" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124114,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="353" spans="3:23">
@@ -32248,12 +32736,18 @@
       <c r="I353" t="s">
         <v>1970</v>
       </c>
+      <c r="J353" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P353">
+        <v>1</v>
+      </c>
       <c r="U353" t="s">
         <v>1701</v>
       </c>
       <c r="V353" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124115,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="354" spans="3:23">
@@ -32266,12 +32760,18 @@
       <c r="I354" t="s">
         <v>1970</v>
       </c>
+      <c r="J354" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P354">
+        <v>1</v>
+      </c>
       <c r="U354" t="s">
         <v>1701</v>
       </c>
       <c r="V354" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124116,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="355" spans="3:23">
@@ -32284,12 +32784,18 @@
       <c r="I355" t="s">
         <v>1970</v>
       </c>
+      <c r="J355" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P355">
+        <v>1</v>
+      </c>
       <c r="U355" t="s">
         <v>1701</v>
       </c>
       <c r="V355" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124117,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="356" spans="3:23">
@@ -32302,12 +32808,18 @@
       <c r="I356" t="s">
         <v>1970</v>
       </c>
+      <c r="J356" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P356">
+        <v>1</v>
+      </c>
       <c r="U356" t="s">
         <v>1701</v>
       </c>
       <c r="V356" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124118,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="357" spans="3:23">
@@ -32320,12 +32832,18 @@
       <c r="I357" t="s">
         <v>1970</v>
       </c>
+      <c r="J357" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P357">
+        <v>1</v>
+      </c>
       <c r="U357" t="s">
         <v>1701</v>
       </c>
       <c r="V357" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124119,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="358" spans="3:23">
@@ -32338,12 +32856,18 @@
       <c r="I358" t="s">
         <v>1970</v>
       </c>
+      <c r="J358" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P358">
+        <v>1</v>
+      </c>
       <c r="U358" t="s">
         <v>1701</v>
       </c>
       <c r="V358" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124120,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="359" spans="3:23">
@@ -32356,12 +32880,18 @@
       <c r="I359" t="s">
         <v>1970</v>
       </c>
+      <c r="J359" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P359">
+        <v>1</v>
+      </c>
       <c r="U359" t="s">
         <v>1701</v>
       </c>
       <c r="V359" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124121,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="360" spans="3:23">
@@ -32374,12 +32904,18 @@
       <c r="I360" t="s">
         <v>1970</v>
       </c>
+      <c r="J360" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P360">
+        <v>1</v>
+      </c>
       <c r="U360" t="s">
         <v>1701</v>
       </c>
       <c r="V360" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124122,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="361" spans="3:23">
@@ -32392,12 +32928,18 @@
       <c r="I361" t="s">
         <v>1970</v>
       </c>
+      <c r="J361" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P361">
+        <v>1</v>
+      </c>
       <c r="U361" t="s">
         <v>1701</v>
       </c>
       <c r="V361" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124123,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="362" spans="3:23">
@@ -32410,12 +32952,18 @@
       <c r="I362" t="s">
         <v>1970</v>
       </c>
+      <c r="J362" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P362">
+        <v>1</v>
+      </c>
       <c r="U362" t="s">
         <v>1701</v>
       </c>
       <c r="V362" t="str">
         <f t="shared" si="5"/>
-        <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原·分线",[3]={},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
+        <v>{dwID=124124,nFrame=52,szNote="箭塔·阴山大草原·分线",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,nMaxDistance=-1,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=10,},},{dwMapID=-1,nMaxDistance=90,tRelation={bAll=true,bEnemy=true,bAlly=true,},tLife={bEnable=true,szOperator="&lt;",nValue=100,},},{dwMapID=-1,nMaxDistance=30,tRelation={bAll=false,bEnemy=true,bAlly=false,},tLife={bEnable=true,szOperator="==",nValue=100,},},{dwMapID=-1,nMaxDistance=6,tRelation={bAll=false,bEnemy=false,bAlly=true,},tLife={bEnable=true,szOperator="&gt;",nValue=10,},},},},</v>
       </c>
     </row>
     <row r="363" spans="3:23">
@@ -32582,28 +33130,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:X370" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="8">
-      <colorFilter dxfId="0"/>
-      <extLst>
-        <colorFilter dxfId="0"/>
-        <colorFilter dxfId="1"/>
-        <dxfs count="2">
-          <dxf>
-            <fill>
-              <patternFill patternType="none"/>
-            </fill>
-          </dxf>
-          <dxf>
-            <fill>
-              <patternFill patternType="solid">
-                <fgColor rgb="FF92D050"/>
-                <bgColor rgb="FF92D050"/>
-              </patternFill>
-            </fill>
-          </dxf>
-        </dxfs>
-      </extLst>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <sortState ref="A151:X158">
@@ -40056,7 +40582,7 @@
         <v>1</v>
       </c>
       <c r="V163" t="str">
-        <f t="shared" ref="V163:V194" si="31">IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="V163:V199" si="31">IF(ISBLANK(B163)=FALSE,IF(ISBLANK(B162),"},["&amp;B163&amp;"]={","["&amp;B163&amp;"]={"),IF(AND(ISBLANK(B163),ISBLANK(D163),ISBLANK(N163),ISBLANK(O163),OR(ISBLANK(B162)=FALSE,ISBLANK(D162)=FALSE,ISBLANK(N162)=FALSE,ISBLANK(O162)=FALSE)),"},},}",IF(ISBLANK(D163),"","{szContent="""&amp;D163&amp;""","&amp;IF(C163&lt;&gt;"","szTarget="""&amp;C163&amp;""",","")&amp;IF(E163&lt;&gt;"","szNote="""&amp;E163&amp;""",","")&amp;IF(M163&lt;&gt;"","col={"&amp;M163&amp;"},","")&amp;IF(N163&gt;0,"bSearch=true,","")&amp;IF(O163&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P163&gt;0,"szVoice="""&amp;P163&amp;""",","")&amp;IF(Q163&gt;0,"bTeamChannel=true,","")&amp;IF(R163&gt;0,"bWhisperChannel=true,","")&amp;IF(S163&gt;0,"bCenterAlarm=true,","")&amp;IF(T163&gt;0,"bScreenHead=true,","")&amp;IF(U163&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W163&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W163:AAH163)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="增援已至秋雨堡，速速进攻！",szTarget="浩气盟督廷卫",szNote="浩气·兵符增援·秋雨堡",col={100,100,255,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=8478,nFrame=8,szName="浩气·兵符增援·秋雨堡",nTime="10,浩气·兵符增援·秋雨堡;300,浩气·秋雨堡·兵符冷却;305,浩气·秋雨堡·可用兵符",nRefresh=1,key="兵符·秋雨堡",},},},</v>
       </c>
       <c r="W163" t="s">
@@ -40805,7 +41331,7 @@
         <v>1</v>
       </c>
       <c r="V195" t="str">
-        <f>IF(ISBLANK(B195)=FALSE,IF(ISBLANK(B194),"},["&amp;B195&amp;"]={","["&amp;B195&amp;"]={"),IF(AND(ISBLANK(B195),ISBLANK(D195),ISBLANK(N195),ISBLANK(O195),OR(ISBLANK(B194)=FALSE,ISBLANK(D194)=FALSE,ISBLANK(N194)=FALSE,ISBLANK(O194)=FALSE)),"},},}",IF(ISBLANK(D195),"","{szContent="""&amp;D195&amp;""","&amp;IF(C195&lt;&gt;"","szTarget="""&amp;C195&amp;""",","")&amp;IF(E195&lt;&gt;"","szNote="""&amp;E195&amp;""",","")&amp;IF(M195&lt;&gt;"","col={"&amp;M195&amp;"},","")&amp;IF(N195&gt;0,"bSearch=true,","")&amp;IF(O195&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P195&gt;0,"szVoice="""&amp;P195&amp;""",","")&amp;IF(Q195&gt;0,"bTeamChannel=true,","")&amp;IF(R195&gt;0,"bWhisperChannel=true,","")&amp;IF(S195&gt;0,"bCenterAlarm=true,","")&amp;IF(T195&gt;0,"bScreenHead=true,","")&amp;IF(U195&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W195&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W195:AAH195)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="31"/>
         <v>{szContent="可恶！",szTarget="%",szNote="{$sender}·退场",col={255,255,100,},[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=1465,szName="浩气盟大将",nTime=-2,nRefresh=2,key="守备首领·浩气盟大将",},{nClass=14,nIcon=1465,szName="恶人谷大将",nTime=-2,nRefresh=2,key="守备首领·恶人谷大将",},{nClass=14,nIcon=13,szName="{$sender}",nTime=-2,key="守备首领·{$sender}",},{nClass=14,nIcon=18829,nFrame=7,szName="浩气盟大将·退场",nTime=10,nRefresh=1,key="守备首领·浩气盟大将",},{nClass=14,nIcon=18830,nFrame=3,szName="恶人谷大将·退场",nTime=10,nRefresh=1,key="守备首领·恶人谷大将",},},},</v>
       </c>
       <c r="W195" t="s">
@@ -40839,7 +41365,7 @@
         <v>1</v>
       </c>
       <c r="V196" t="str">
-        <f>IF(ISBLANK(B196)=FALSE,IF(ISBLANK(B195),"},["&amp;B196&amp;"]={","["&amp;B196&amp;"]={"),IF(AND(ISBLANK(B196),ISBLANK(D196),ISBLANK(N196),ISBLANK(O196),OR(ISBLANK(B195)=FALSE,ISBLANK(D195)=FALSE,ISBLANK(N195)=FALSE,ISBLANK(O195)=FALSE)),"},},}",IF(ISBLANK(D196),"","{szContent="""&amp;D196&amp;""","&amp;IF(C196&lt;&gt;"","szTarget="""&amp;C196&amp;""",","")&amp;IF(E196&lt;&gt;"","szNote="""&amp;E196&amp;""",","")&amp;IF(M196&lt;&gt;"","col={"&amp;M196&amp;"},","")&amp;IF(N196&gt;0,"bSearch=true,","")&amp;IF(O196&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P196&gt;0,"szVoice="""&amp;P196&amp;""",","")&amp;IF(Q196&gt;0,"bTeamChannel=true,","")&amp;IF(R196&gt;0,"bWhisperChannel=true,","")&amp;IF(S196&gt;0,"bCenterAlarm=true,","")&amp;IF(T196&gt;0,"bScreenHead=true,","")&amp;IF(U196&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W196&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W196:AAH196)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="31"/>
         <v>{szContent="留下大量军功，请“恶人谷”侠士们前来拾取，切莫错过。",szTarget="%",col={255,100,100,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=3,szName="恶人谷·拾取首领掉落",nTime="300,恶人谷·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W196" t="s">
@@ -40864,7 +41390,7 @@
         <v>1</v>
       </c>
       <c r="V197" t="str">
-        <f>IF(ISBLANK(B197)=FALSE,IF(ISBLANK(B196),"},["&amp;B197&amp;"]={","["&amp;B197&amp;"]={"),IF(AND(ISBLANK(B197),ISBLANK(D197),ISBLANK(N197),ISBLANK(O197),OR(ISBLANK(B196)=FALSE,ISBLANK(D196)=FALSE,ISBLANK(N196)=FALSE,ISBLANK(O196)=FALSE)),"},},}",IF(ISBLANK(D197),"","{szContent="""&amp;D197&amp;""","&amp;IF(C197&lt;&gt;"","szTarget="""&amp;C197&amp;""",","")&amp;IF(E197&lt;&gt;"","szNote="""&amp;E197&amp;""",","")&amp;IF(M197&lt;&gt;"","col={"&amp;M197&amp;"},","")&amp;IF(N197&gt;0,"bSearch=true,","")&amp;IF(O197&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P197&gt;0,"szVoice="""&amp;P197&amp;""",","")&amp;IF(Q197&gt;0,"bTeamChannel=true,","")&amp;IF(R197&gt;0,"bWhisperChannel=true,","")&amp;IF(S197&gt;0,"bCenterAlarm=true,","")&amp;IF(T197&gt;0,"bScreenHead=true,","")&amp;IF(U197&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W197&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W197:AAH197)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="31"/>
         <v>{szContent="留下大量军功，请“浩气盟”侠士们前来拾取，切莫错过。",szTarget="%",col={100,100,255,},bSearch=true,[14]={},tCountdown={{nClass=14,nIcon=13,szName="狼牙先锋首领",nTime=-2,key="狼牙先锋首领",},{nClass=14,nIcon=13,nFrame=7,szName="浩气盟·拾取首领掉落",nTime="300,浩气盟·拾取首领掉落;600,狼牙先锋首领·刷新剩余;620,狼牙先锋首领·即将刷新;625,狼牙先锋首领·延迟刷新",nRefresh=300,key="狼牙先锋首领",},},},</v>
       </c>
       <c r="W197" t="s">
@@ -40894,7 +41420,7 @@
         <v>1</v>
       </c>
       <c r="V198" t="str">
-        <f>IF(ISBLANK(B198)=FALSE,IF(ISBLANK(B197),"},["&amp;B198&amp;"]={","["&amp;B198&amp;"]={"),IF(AND(ISBLANK(B198),ISBLANK(D198),ISBLANK(N198),ISBLANK(O198),OR(ISBLANK(B197)=FALSE,ISBLANK(D197)=FALSE,ISBLANK(N197)=FALSE,ISBLANK(O197)=FALSE)),"},},}",IF(ISBLANK(D198),"","{szContent="""&amp;D198&amp;""","&amp;IF(C198&lt;&gt;"","szTarget="""&amp;C198&amp;""",","")&amp;IF(E198&lt;&gt;"","szNote="""&amp;E198&amp;""",","")&amp;IF(M198&lt;&gt;"","col={"&amp;M198&amp;"},","")&amp;IF(N198&gt;0,"bSearch=true,","")&amp;IF(O198&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P198&gt;0,"szVoice="""&amp;P198&amp;""",","")&amp;IF(Q198&gt;0,"bTeamChannel=true,","")&amp;IF(R198&gt;0,"bWhisperChannel=true,","")&amp;IF(S198&gt;0,"bCenterAlarm=true,","")&amp;IF(T198&gt;0,"bScreenHead=true,","")&amp;IF(U198&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W198&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W198:AAH198)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="31"/>
         <v>{szContent="(.-)侠士([打开关闭]+)了【(.-)据点】城门！",szTarget="%",szNote="【{$1}】·{$2}·{$3}·城门",col={255,255,100,},bReg=true,[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=4839,nFrame=1,szName="关闭·{$3}·城门",nTime=10,key="打开·{$3}·城门",},{nClass=14,nIcon=2310,nFrame=1,szName="打开·{$3}·城门",nTime=10,key="关闭·{$3}·城门",},{nClass=14,nIcon=13,nFrame=-1,szName="{$2}·{$3}·城门",nTime=-1,key="{$2}·{$3}·城门",},},},</v>
       </c>
       <c r="W198" t="s">
@@ -40909,7 +41435,7 @@
     </row>
     <row r="199" spans="3:27">
       <c r="V199" t="str">
-        <f>IF(ISBLANK(B199)=FALSE,IF(ISBLANK(B198),"},["&amp;B199&amp;"]={","["&amp;B199&amp;"]={"),IF(AND(ISBLANK(B199),ISBLANK(D199),ISBLANK(N199),ISBLANK(O199),OR(ISBLANK(B198)=FALSE,ISBLANK(D198)=FALSE,ISBLANK(N198)=FALSE,ISBLANK(O198)=FALSE)),"},},}",IF(ISBLANK(D199),"","{szContent="""&amp;D199&amp;""","&amp;IF(C199&lt;&gt;"","szTarget="""&amp;C199&amp;""",","")&amp;IF(E199&lt;&gt;"","szNote="""&amp;E199&amp;""",","")&amp;IF(M199&lt;&gt;"","col={"&amp;M199&amp;"},","")&amp;IF(N199&gt;0,"bSearch=true,","")&amp;IF(O199&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(P199&gt;0,"szVoice="""&amp;P199&amp;""",","")&amp;IF(Q199&gt;0,"bTeamChannel=true,","")&amp;IF(R199&gt;0,"bWhisperChannel=true,","")&amp;IF(S199&gt;0,"bCenterAlarm=true,","")&amp;IF(T199&gt;0,"bScreenHead=true,","")&amp;IF(U199&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(W199&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,W199:AAH199)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="31"/>
         <v>},},}</v>
       </c>
     </row>
